--- a/salida/Recargas.xlsx
+++ b/salida/Recargas.xlsx
@@ -1336,11 +1336,11 @@
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">Cálculo!F30</f>
-        <v>1073.44515880377</v>
+        <v>1119.01482761851</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">Cálculo!I30</f>
-        <v>575.8235761071</v>
+        <v>599.546838706733</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>21</v>
@@ -1352,11 +1352,11 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">Cálculo!G30</f>
-        <v>583.719434863009</v>
+        <v>585.256044364544</v>
       </c>
       <c r="C8" s="7" t="n">
         <f aca="false">Cálculo!J30</f>
-        <v>321.26184967668</v>
+        <v>322.091098622045</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>21</v>
@@ -1368,11 +1368,11 @@
       </c>
       <c r="B9" s="7" t="n">
         <f aca="false">Importados!$P$22</f>
-        <v>1828</v>
+        <v>1833</v>
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">Importados!$P$56</f>
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>24</v>
@@ -1384,11 +1384,11 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">Cálculo!E44</f>
-        <v>107.121978748165</v>
+        <v>110.767552253345</v>
       </c>
       <c r="C10" s="7" t="n">
         <f aca="false">Cálculo!I44</f>
-        <v>57.883289303567</v>
+        <v>59.7811503115376</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>26</v>
@@ -1400,11 +1400,11 @@
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">Cálculo!B61</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">Cálculo!C61</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>28</v>
@@ -1432,11 +1432,11 @@
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">Cálculo!B64</f>
-        <v>0.923984721900265</v>
+        <v>0.956474196159033</v>
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">Cálculo!C64</f>
-        <v>0.896545923711903</v>
+        <v>0.93657890101826</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>28</v>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">Cálculo!E74</f>
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C14" s="9" t="n">
         <f aca="false">Cálculo!I74</f>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" s="11" t="n">
         <f aca="false">Cálculo!E75</f>
-        <v>156</v>
+        <v>160.8</v>
       </c>
       <c r="C15" s="11" t="n">
         <f aca="false">Cálculo!I75</f>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">Cálculo!E77</f>
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C16" s="9" t="n">
         <f aca="false">Cálculo!I77</f>
@@ -1907,52 +1907,52 @@
         <v>109</v>
       </c>
       <c r="B5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""parametros_recargas!E51:P68"")"),0.119933202334914)</f>
-        <v>0.119933202334914</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""parametros_recargas!E55:P72"")"),0.00749080356204596)</f>
+        <v>0.00749080356204596</v>
       </c>
       <c r="C5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0899878549699844)</f>
-        <v>0.0899878549699844</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0980789973414249)</f>
+        <v>0.0980789973414249</v>
       </c>
       <c r="D5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800060725150078)</f>
-        <v>0.0800060725150078</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0986610060682725)</f>
+        <v>0.0986610060682725</v>
       </c>
       <c r="E5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0750151812875195)</f>
-        <v>0.0750151812875195</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993660972474985)</f>
+        <v>0.0993660972474985</v>
       </c>
       <c r="F5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0700242900600312)</f>
-        <v>0.0700242900600312</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994029049644587)</f>
+        <v>0.0994029049644587</v>
       </c>
       <c r="G5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0700242900600312)</f>
-        <v>0.0700242900600312</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990676994264772)</f>
+        <v>0.0990676994264772</v>
       </c>
       <c r="H5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0750151812875195)</f>
-        <v>0.0750151812875195</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100122038394086)</f>
+        <v>0.100122038394086</v>
       </c>
       <c r="I5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0750151812875195)</f>
-        <v>0.0750151812875195</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993285448657443)</f>
+        <v>0.0993285448657443</v>
       </c>
       <c r="J5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0750151812875195)</f>
-        <v>0.0750151812875195</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994522656022319)</f>
+        <v>0.0994522656022319</v>
       </c>
       <c r="K5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0750151812875195)</f>
-        <v>0.0750151812875195</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990432318689603)</f>
+        <v>0.0990432318689603</v>
       </c>
       <c r="L5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0750151812875195)</f>
-        <v>0.0750151812875195</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0972817804891135)</f>
+        <v>0.0972817804891135</v>
       </c>
       <c r="M5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.119933202334914)</f>
-        <v>0.119933202334914</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0027046301696863)</f>
+        <v>0.0027046301696863</v>
       </c>
       <c r="N5" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""datos_base!K2:K18"")"),108842.626397553)</f>
@@ -2101,52 +2101,52 @@
         <v>111</v>
       </c>
       <c r="B7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0828991382713857)</f>
-        <v>0.0828991382713857</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0752806934699069)</f>
+        <v>0.0752806934699069</v>
       </c>
       <c r="C7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.115838094188612)</f>
-        <v>0.115838094188612</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.116386303068985)</f>
+        <v>0.116386303068985</v>
       </c>
       <c r="D7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.080193907522717)</f>
-        <v>0.080193907522717</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0814578576260751)</f>
+        <v>0.0814578576260751</v>
       </c>
       <c r="E7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0798557536791334)</f>
-        <v>0.0798557536791334</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0815056305150171)</f>
+        <v>0.0815056305150171</v>
       </c>
       <c r="F7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0795175998355498)</f>
-        <v>0.0795175998355498</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0815081243924422)</f>
+        <v>0.0815081243924422</v>
       </c>
       <c r="G7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0795175998355498)</f>
-        <v>0.0795175998355498</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0814854128093016)</f>
+        <v>0.0814854128093016</v>
       </c>
       <c r="H7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0798557536791334)</f>
-        <v>0.0798557536791334</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0815568487028296)</f>
+        <v>0.0815568487028296</v>
       </c>
       <c r="I7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0798557536791334)</f>
-        <v>0.0798557536791334</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0815030861834244)</f>
+        <v>0.0815030861834244</v>
       </c>
       <c r="J7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0798557536791334)</f>
-        <v>0.0798557536791334</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0815114687829777)</f>
+        <v>0.0815114687829777</v>
       </c>
       <c r="K7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0798557536791334)</f>
-        <v>0.0798557536791334</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0814837550295103)</f>
+        <v>0.0814837550295103</v>
       </c>
       <c r="L7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0798557536791334)</f>
-        <v>0.0798557536791334</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0813644093000141)</f>
+        <v>0.0813644093000141</v>
       </c>
       <c r="M7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0828991382713857)</f>
-        <v>0.0828991382713857</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0749564101195165)</f>
+        <v>0.0749564101195165</v>
       </c>
       <c r="N7" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56059.2707104735)</f>
@@ -2157,8 +2157,8 @@
         <v>1</v>
       </c>
       <c r="P7" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1010)</f>
-        <v>1010</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1015)</f>
+        <v>1015</v>
       </c>
       <c r="Q7" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69628)</f>
@@ -3556,52 +3556,52 @@
         <v>126</v>
       </c>
       <c r="B22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101766211787366)</f>
-        <v>0.101766211787366</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0403512821171889)</f>
+        <v>0.0403512821171889</v>
       </c>
       <c r="C22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.104101668275449)</f>
-        <v>0.104101668275449</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.108520970470319)</f>
+        <v>0.108520970470319</v>
       </c>
       <c r="D22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0799584071106368)</f>
-        <v>0.0799584071106368</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0901475479034248)</f>
+        <v>0.0901475479034248</v>
       </c>
       <c r="E22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0772324315260457)</f>
-        <v>0.0772324315260457</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905326617542125)</f>
+        <v>0.0905326617542125</v>
       </c>
       <c r="F22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0745064559414546)</f>
-        <v>0.0745064559414546</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905527657663388)</f>
+        <v>0.0905527657663388</v>
       </c>
       <c r="G22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0745064559414546)</f>
-        <v>0.0745064559414546</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0903696798061951)</f>
+        <v>0.0903696798061951</v>
       </c>
       <c r="H22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0772324315260457)</f>
-        <v>0.0772324315260457</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0909455493558567)</f>
+        <v>0.0909455493558567</v>
       </c>
       <c r="I22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0772324315260457)</f>
-        <v>0.0772324315260457</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905121510135173)</f>
+        <v>0.0905121510135173</v>
       </c>
       <c r="J22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0772324315260457)</f>
-        <v>0.0772324315260457</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905797260600571)</f>
+        <v>0.0905797260600571</v>
       </c>
       <c r="K22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0772324315260457)</f>
-        <v>0.0772324315260457</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0903563158674985)</f>
+        <v>0.0903563158674985</v>
       </c>
       <c r="L22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0772324315260457)</f>
-        <v>0.0772324315260457</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0893942284895046)</f>
+        <v>0.0893942284895046</v>
       </c>
       <c r="M22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101766211787366)</f>
-        <v>0.101766211787366</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0377371213958866)</f>
+        <v>0.0377371213958866</v>
       </c>
       <c r="N22" s="7" t="n">
         <f aca="false">SUM(N5:N21)</f>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="P22" s="7" t="n">
         <f aca="false">SUM(P5:P21)</f>
-        <v>1828</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3709,52 +3709,52 @@
         <v>101</v>
       </c>
       <c r="B28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""parametros_recargas!E35:P41"")"),0.12)</f>
-        <v>0.12</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""parametros_recargas!E35:P41"")"),0.00735238492719494)</f>
+        <v>0.00735238492719494</v>
       </c>
       <c r="C28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.09)</f>
-        <v>0.09</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0981059093482913)</f>
+        <v>0.0981059093482913</v>
       </c>
       <c r="D28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0986889802872471)</f>
+        <v>0.0986889802872471</v>
       </c>
       <c r="E28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.075)</f>
-        <v>0.075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993953583138234)</f>
+        <v>0.0993953583138234</v>
       </c>
       <c r="F28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07)</f>
-        <v>0.07</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994322332077878)</f>
+        <v>0.0994322332077878</v>
       </c>
       <c r="G28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07)</f>
-        <v>0.07</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990964158931013)</f>
+        <v>0.0990964158931013</v>
       </c>
       <c r="H28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.075)</f>
-        <v>0.075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100152679112986)</f>
+        <v>0.100152679112986</v>
       </c>
       <c r="I28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.075)</f>
-        <v>0.075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993577373959928)</f>
+        <v>0.0993577373959928</v>
       </c>
       <c r="J28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.075)</f>
-        <v>0.075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994816839326416)</f>
+        <v>0.0994816839326416</v>
       </c>
       <c r="K28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.075)</f>
-        <v>0.075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990719036803504)</f>
+        <v>0.0990719036803504</v>
       </c>
       <c r="L28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.075)</f>
-        <v>0.075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0973072375119662)</f>
+        <v>0.0973072375119662</v>
       </c>
       <c r="M28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.12)</f>
-        <v>0.12</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.00255747638861682)</f>
+        <v>0.00255747638861682</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4159,52 +4159,52 @@
         <v>109</v>
       </c>
       <c r="B39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""parametros_recargas!E51:P68"")"),0.119942566698092)</f>
-        <v>0.119942566698092</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""parametros_recargas!E55:P72"")"),0.00747139865671394)</f>
+        <v>0.00747139865671394</v>
       </c>
       <c r="C39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0899895575814713)</f>
-        <v>0.0899895575814713</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0980827701350671)</f>
+        <v>0.0980827701350671</v>
       </c>
       <c r="D39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800052212092643)</f>
-        <v>0.0800052212092643</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0986649277734065)</f>
+        <v>0.0986649277734065</v>
       </c>
       <c r="E39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0750130530231608)</f>
-        <v>0.0750130530231608</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993701993557339)</f>
+        <v>0.0993701993557339</v>
       </c>
       <c r="F39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0700208848370573)</f>
-        <v>0.0700208848370573</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994070164902368)</f>
+        <v>0.0994070164902368</v>
       </c>
       <c r="G39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0700208848370573)</f>
-        <v>0.0700208848370573</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990717251872927)</f>
+        <v>0.0990717251872927</v>
       </c>
       <c r="H39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0750130530231608)</f>
-        <v>0.0750130530231608</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100126333915785)</f>
+        <v>0.100126333915785</v>
       </c>
       <c r="I39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0750130530231608)</f>
-        <v>0.0750130530231608</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993326373659087)</f>
+        <v>0.0993326373659087</v>
       </c>
       <c r="J39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0750130530231608)</f>
-        <v>0.0750130530231608</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994563897573158)</f>
+        <v>0.0994563897573158</v>
       </c>
       <c r="K39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0750130530231608)</f>
-        <v>0.0750130530231608</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990472513695595)</f>
+        <v>0.0990472513695595</v>
       </c>
       <c r="L39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0750130530231608)</f>
-        <v>0.0750130530231608</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0972853493085793)</f>
+        <v>0.0972853493085793</v>
       </c>
       <c r="M39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.119942566698092)</f>
-        <v>0.119942566698092</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.00268400068440077)</f>
+        <v>0.00268400068440077</v>
       </c>
       <c r="N39" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""datos_base!K2:K18"")"),56575.8368575054)</f>
@@ -4353,52 +4353,52 @@
         <v>111</v>
       </c>
       <c r="B41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0823827818974594)</f>
-        <v>0.0823827818974594</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0744731592432624)</f>
+        <v>0.0744731592432624</v>
       </c>
       <c r="C41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.122577805221806)</f>
-        <v>0.122577805221806</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.123146966709803)</f>
+        <v>0.123146966709803</v>
       </c>
       <c r="D41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0795741569126926)</f>
-        <v>0.0795741569126926</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.080886415337057)</f>
+        <v>0.080886415337057</v>
       </c>
       <c r="E41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0792230787895967)</f>
-        <v>0.0792230787895967</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809360141114104)</f>
+        <v>0.0809360141114104</v>
       </c>
       <c r="F41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0788720006665009)</f>
-        <v>0.0788720006665009</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809386033051228)</f>
+        <v>0.0809386033051228</v>
       </c>
       <c r="G41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0788720006665009)</f>
-        <v>0.0788720006665009</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809150236826142)</f>
+        <v>0.0809150236826142</v>
       </c>
       <c r="H41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0792230787895967)</f>
-        <v>0.0792230787895967</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809891898643607)</f>
+        <v>0.0809891898643607</v>
       </c>
       <c r="I41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0792230787895967)</f>
-        <v>0.0792230787895967</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809333725351661)</f>
+        <v>0.0809333725351661</v>
       </c>
       <c r="J41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0792230787895967)</f>
-        <v>0.0792230787895967</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809420755186563)</f>
+        <v>0.0809420755186563</v>
       </c>
       <c r="K41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0792230787895967)</f>
-        <v>0.0792230787895967</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809133025422851)</f>
+        <v>0.0809133025422851</v>
       </c>
       <c r="L41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0792230787895967)</f>
-        <v>0.0792230787895967</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0807893954050276)</f>
+        <v>0.0807893954050276</v>
       </c>
       <c r="M41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0823827818974594)</f>
-        <v>0.0823827818974594</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741364817452343)</f>
+        <v>0.0741364817452343</v>
       </c>
       <c r="N41" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29139.3203107948)</f>
@@ -4409,8 +4409,8 @@
         <v>1</v>
       </c>
       <c r="P41" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),551)</f>
-        <v>551</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),554)</f>
+        <v>554</v>
       </c>
       <c r="Q41" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36760)</f>
@@ -5808,52 +5808,52 @@
         <v>126</v>
       </c>
       <c r="B56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101494630758993)</f>
-        <v>0.101494630758993</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0399853669657492)</f>
+        <v>0.0399853669657492</v>
       </c>
       <c r="C56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.107432404543694)</f>
-        <v>0.107432404543694</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111858494843661)</f>
+        <v>0.111858494843661</v>
       </c>
       <c r="D56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0796533290133718)</f>
-        <v>0.0796533290133718</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0898581204576652)</f>
+        <v>0.0898581204576652</v>
       </c>
       <c r="E56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0769231662951691)</f>
-        <v>0.0769231662951691</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0902438258482885)</f>
+        <v>0.0902438258482885</v>
       </c>
       <c r="F56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741930035769664)</f>
-        <v>0.0741930035769664</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0902639607404363)</f>
+        <v>0.0902639607404363</v>
       </c>
       <c r="G56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741930035769664)</f>
-        <v>0.0741930035769664</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0900805935578995)</f>
+        <v>0.0900805935578995</v>
       </c>
       <c r="H56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0769231662951691)</f>
-        <v>0.0769231662951691</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0906573476506073)</f>
+        <v>0.0906573476506073</v>
       </c>
       <c r="I56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0769231662951691)</f>
-        <v>0.0769231662951691</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0902232836028314)</f>
+        <v>0.0902232836028314</v>
       </c>
       <c r="J56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0769231662951691)</f>
-        <v>0.0769231662951691</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0902909624455131)</f>
+        <v>0.0902909624455131</v>
       </c>
       <c r="K56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0769231662951691)</f>
-        <v>0.0769231662951691</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0900672090920209)</f>
+        <v>0.0900672090920209</v>
       </c>
       <c r="L56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0769231662951691)</f>
-        <v>0.0769231662951691</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0891036439354216)</f>
+        <v>0.0891036439354216</v>
       </c>
       <c r="M56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101494630758993)</f>
-        <v>0.101494630758993</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0373671908599057)</f>
+        <v>0.0373671908599057</v>
       </c>
       <c r="N56" s="7" t="n">
         <f aca="false">SUM(N39:N55)</f>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="P56" s="7" t="n">
         <f aca="false">SUM(P39:P55)</f>
-        <v>1001</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5961,52 +5961,52 @@
         <v>101</v>
       </c>
       <c r="B62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""parametros_recargas!E35:P41"")"),0.12)</f>
-        <v>0.12</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""parametros_recargas!E35:P41"")"),0.00735238492719494)</f>
+        <v>0.00735238492719494</v>
       </c>
       <c r="C62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.09)</f>
-        <v>0.09</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0981059093482913)</f>
+        <v>0.0981059093482913</v>
       </c>
       <c r="D62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08)</f>
-        <v>0.08</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0986889802872471)</f>
+        <v>0.0986889802872471</v>
       </c>
       <c r="E62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.075)</f>
-        <v>0.075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993953583138234)</f>
+        <v>0.0993953583138234</v>
       </c>
       <c r="F62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07)</f>
-        <v>0.07</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994322332077878)</f>
+        <v>0.0994322332077878</v>
       </c>
       <c r="G62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07)</f>
-        <v>0.07</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990964158931013)</f>
+        <v>0.0990964158931013</v>
       </c>
       <c r="H62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.075)</f>
-        <v>0.075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100152679112986)</f>
+        <v>0.100152679112986</v>
       </c>
       <c r="I62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.075)</f>
-        <v>0.075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993577373959928)</f>
+        <v>0.0993577373959928</v>
       </c>
       <c r="J62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.075)</f>
-        <v>0.075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994816839326416)</f>
+        <v>0.0994816839326416</v>
       </c>
       <c r="K62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.075)</f>
-        <v>0.075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990719036803504)</f>
+        <v>0.0990719036803504</v>
       </c>
       <c r="L62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.075)</f>
-        <v>0.075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0973072375119662)</f>
+        <v>0.0973072375119662</v>
       </c>
       <c r="M62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.12)</f>
-        <v>0.12</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.00255747638861682)</f>
+        <v>0.00255747638861682</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6440,11 +6440,11 @@
       </c>
       <c r="B7" s="26" t="n">
         <f aca="false">INDEX(Importados!$B$22:$M$22,B5)</f>
-        <v>0.104101668275449</v>
+        <v>0.108520970470319</v>
       </c>
       <c r="C7" s="26" t="n">
         <f aca="false">INDEX(Importados!$B$56:$M$56,C5)</f>
-        <v>0.107432404543694</v>
+        <v>0.111858494843661</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="F13" s="29" t="n">
         <f aca="false">Importados!$N$5*INDEX(Importados!$B$5:$M$5,$B$5)/$B$8</f>
-        <v>489.72572394076</v>
+        <v>533.758783253965</v>
       </c>
       <c r="G13" s="29" t="n">
         <f aca="false">F13*Importados!$O$5</f>
@@ -6593,11 +6593,11 @@
       </c>
       <c r="H13" s="23" t="n">
         <f aca="false">F13/$C13</f>
-        <v>6.80174616584389</v>
+        <v>7.41331643408285</v>
       </c>
       <c r="I13" s="29" t="n">
         <f aca="false">Importados!$N$39*INDEX(Importados!$B$39:$M$39,$C$5)/$C$8</f>
-        <v>254.56172643042</v>
+        <v>277.455740084688</v>
       </c>
       <c r="J13" s="29" t="n">
         <f aca="false">I13*Importados!$O$39</f>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="K13" s="23" t="n">
         <f aca="false">I13/$C13</f>
-        <v>3.53557953375584</v>
+        <v>3.85355194562067</v>
       </c>
       <c r="M13" s="5" t="s">
         <v>151</v>
@@ -6673,27 +6673,27 @@
       </c>
       <c r="F15" s="29" t="n">
         <f aca="false">Importados!$N$7*INDEX(Importados!$B$7:$M$7,$B$5)/$B$8</f>
-        <v>324.689954035236</v>
+        <v>326.226563536772</v>
       </c>
       <c r="G15" s="29" t="n">
         <f aca="false">F15*Importados!$O$7</f>
-        <v>324.689954035236</v>
+        <v>326.226563536772</v>
       </c>
       <c r="H15" s="23" t="n">
         <f aca="false">F15/$C15</f>
-        <v>13.5287480848015</v>
+        <v>13.5927734806988</v>
       </c>
       <c r="I15" s="29" t="n">
         <f aca="false">Importados!$N$41*INDEX(Importados!$B$41:$M$41,$C$5)/$C$8</f>
-        <v>178.591696467621</v>
+        <v>179.420945412987</v>
       </c>
       <c r="J15" s="29" t="n">
         <f aca="false">I15*Importados!$O$41</f>
-        <v>178.591696467621</v>
+        <v>179.420945412987</v>
       </c>
       <c r="K15" s="23" t="n">
         <f aca="false">I15/$C15</f>
-        <v>7.44132068615088</v>
+        <v>7.47587272554111</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>151</v>
@@ -7321,27 +7321,27 @@
       </c>
       <c r="F30" s="30" t="n">
         <f aca="false">SUM(F13:F29)</f>
-        <v>1073.44515880377</v>
+        <v>1119.01482761851</v>
       </c>
       <c r="G30" s="30" t="n">
         <f aca="false">SUM(G13:G29)</f>
-        <v>583.719434863009</v>
+        <v>585.256044364544</v>
       </c>
       <c r="H30" s="30" t="n">
         <f aca="false">SUM(H13:H29)</f>
-        <v>37.3025755918414</v>
+        <v>37.9781712559777</v>
       </c>
       <c r="I30" s="30" t="n">
         <f aca="false">SUM(I13:I29)</f>
-        <v>575.8235761071</v>
+        <v>599.546838706733</v>
       </c>
       <c r="J30" s="30" t="n">
         <f aca="false">SUM(J13:J29)</f>
-        <v>321.26184967668</v>
+        <v>322.091098622045</v>
       </c>
       <c r="K30" s="30" t="n">
         <f aca="false">SUM(K13:K29)</f>
-        <v>20.2315375836849</v>
+        <v>20.58406203494</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7350,11 +7350,11 @@
       </c>
       <c r="F31" s="11" t="n">
         <f aca="false">SUMPRODUCT(F13:F29,$B$13:$B$29)/F30</f>
-        <v>6.85140037194582</v>
+        <v>6.65882736300077</v>
       </c>
       <c r="I31" s="11" t="n">
         <f aca="false">SUMPRODUCT(I13:I29,$B$13:$B$29)/I30</f>
-        <v>6.94428580605528</v>
+        <v>6.75381882934406</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="C37" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$28:$M$28,$B$5)*SUMPRODUCT(Importados!$N$5:$N$21,Importados!$Q$5:$Q$21/Importados!$X$5:$X$21)/$B$8</f>
-        <v>505.960530411216</v>
+        <v>551.530199225957</v>
       </c>
       <c r="D37" s="22" t="n">
         <f aca="false">Importados!Q$23</f>
@@ -7437,15 +7437,15 @@
       </c>
       <c r="E37" s="28" t="n">
         <f aca="false">2*C37/D37</f>
-        <v>40.4768424328973</v>
+        <v>44.1224159380766</v>
       </c>
       <c r="F37" s="28" t="n">
         <f aca="false">E37*(Supuestos!$B$16+Supuestos!$B$17)/60+2*C37*$B37/60</f>
-        <v>32.0441669260437</v>
+        <v>34.9302459509773</v>
       </c>
       <c r="G37" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$62:$M$62,$C$5)*SUMPRODUCT(Importados!$N$39:$N$55,Importados!$Q$39:$Q$55/Importados!$X$39:$X$55)/$C$8</f>
-        <v>263.399643670702</v>
+        <v>287.122906270335</v>
       </c>
       <c r="H37" s="22" t="n">
         <f aca="false">Importados!Q$57</f>
@@ -7453,11 +7453,11 @@
       </c>
       <c r="I37" s="28" t="n">
         <f aca="false">2*G37/H37</f>
-        <v>21.0719714936561</v>
+        <v>22.9698325016268</v>
       </c>
       <c r="J37" s="28" t="n">
         <f aca="false">I37*(Supuestos!$B$16+Supuestos!$B$17)/60+2*G37*$B37/60</f>
-        <v>16.6819774324778</v>
+        <v>18.1844507304545</v>
       </c>
       <c r="M37" s="5" t="s">
         <v>164</v>
@@ -7727,27 +7727,27 @@
       </c>
       <c r="C44" s="30" t="n">
         <f aca="false">SUM(C37:C43)</f>
-        <v>1073.44515880377</v>
+        <v>1119.01482761851</v>
       </c>
       <c r="E44" s="30" t="n">
         <f aca="false">SUM(E37:E43)</f>
-        <v>107.121978748165</v>
+        <v>110.767552253345</v>
       </c>
       <c r="F44" s="30" t="n">
         <f aca="false">SUM(F37:F43)</f>
-        <v>99.2379374565358</v>
+        <v>102.124016481469</v>
       </c>
       <c r="G44" s="30" t="n">
         <f aca="false">SUM(G37:G43)</f>
-        <v>575.823576107101</v>
+        <v>599.546838706733</v>
       </c>
       <c r="I44" s="30" t="n">
         <f aca="false">SUM(I37:I43)</f>
-        <v>57.883289303567</v>
+        <v>59.7811503115376</v>
       </c>
       <c r="J44" s="30" t="n">
         <f aca="false">SUM(J37:J43)</f>
-        <v>53.7409442783928</v>
+        <v>55.2434175763695</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7784,11 +7784,11 @@
       </c>
       <c r="B49" s="29" t="n">
         <f aca="false">F30</f>
-        <v>1073.44515880377</v>
+        <v>1119.01482761851</v>
       </c>
       <c r="C49" s="29" t="n">
         <f aca="false">I30</f>
-        <v>575.8235761071</v>
+        <v>599.546838706733</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>168</v>
@@ -7809,11 +7809,11 @@
       </c>
       <c r="B50" s="29" t="n">
         <f aca="false">G30</f>
-        <v>583.719434863009</v>
+        <v>585.256044364544</v>
       </c>
       <c r="C50" s="29" t="n">
         <f aca="false">J30</f>
-        <v>321.26184967668</v>
+        <v>322.091098622045</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>168</v>
@@ -7834,11 +7834,11 @@
       </c>
       <c r="B51" s="29" t="n">
         <f aca="false">B49+B50</f>
-        <v>1657.16459366678</v>
+        <v>1704.27087198305</v>
       </c>
       <c r="C51" s="29" t="n">
         <f aca="false">C49+C50</f>
-        <v>897.085425783779</v>
+        <v>921.637937328778</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>170</v>
@@ -7859,11 +7859,11 @@
       </c>
       <c r="B52" s="28" t="n">
         <f aca="false">F31</f>
-        <v>6.85140037194582</v>
+        <v>6.65882736300077</v>
       </c>
       <c r="C52" s="28" t="n">
         <f aca="false">I31</f>
-        <v>6.94428580605528</v>
+        <v>6.75381882934406</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>171</v>
@@ -7884,11 +7884,11 @@
       </c>
       <c r="B53" s="31" t="n">
         <f aca="false">H30/F30</f>
-        <v>0.0347503319437491</v>
+        <v>0.0339389347831994</v>
       </c>
       <c r="C53" s="31" t="n">
         <f aca="false">K30/I30</f>
-        <v>0.035134958732433</v>
+        <v>0.0343327004764821</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>173</v>
@@ -7909,11 +7909,11 @@
       </c>
       <c r="B54" s="21" t="n">
         <f aca="false">Supuestos!$B$6/(B53*Supuestos!$B$22)</f>
-        <v>150.139322778076</v>
+        <v>153.728787826616</v>
       </c>
       <c r="C54" s="21" t="n">
         <f aca="false">Supuestos!$B$6/(C53*Supuestos!$B$22)</f>
-        <v>148.495728828953</v>
+        <v>151.965654665637</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>175</v>
@@ -7934,11 +7934,11 @@
       </c>
       <c r="B55" s="21" t="n">
         <f aca="false">Supuestos!$B$10/B52</f>
-        <v>241.702412660157</v>
+        <v>248.692436329169</v>
       </c>
       <c r="C55" s="21" t="n">
         <f aca="false">Supuestos!$B$10/C52</f>
-        <v>238.4694475789</v>
+        <v>245.194613868674</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>177</v>
@@ -7959,11 +7959,11 @@
       </c>
       <c r="B56" s="21" t="n">
         <f aca="false">MIN(B54,B55)</f>
-        <v>150.139322778076</v>
+        <v>153.728787826616</v>
       </c>
       <c r="C56" s="21" t="n">
         <f aca="false">MIN(C54,C55)</f>
-        <v>148.495728828953</v>
+        <v>151.965654665637</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>179</v>
@@ -7984,11 +7984,11 @@
       </c>
       <c r="B57" s="23" t="n">
         <f aca="false">B51/B56</f>
-        <v>11.0375121121085</v>
+        <v>11.086218112285</v>
       </c>
       <c r="C57" s="23" t="n">
         <f aca="false">C51/C56</f>
-        <v>6.04115305442286</v>
+        <v>6.06477785626375</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>181</v>
@@ -8009,11 +8009,11 @@
       </c>
       <c r="B58" s="28" t="n">
         <f aca="false">E44</f>
-        <v>107.121978748165</v>
+        <v>110.767552253345</v>
       </c>
       <c r="C58" s="28" t="n">
         <f aca="false">I44</f>
-        <v>57.883289303567</v>
+        <v>59.7811503115376</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>182</v>
@@ -8034,11 +8034,11 @@
       </c>
       <c r="B59" s="28" t="n">
         <f aca="false">F44</f>
-        <v>99.2379374565358</v>
+        <v>102.124016481469</v>
       </c>
       <c r="C59" s="28" t="n">
         <f aca="false">J44</f>
-        <v>53.7409442783928</v>
+        <v>55.2434175763695</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>182</v>
@@ -8059,11 +8059,11 @@
       </c>
       <c r="B60" s="23" t="n">
         <f aca="false">B59/($B$9-Supuestos!$B$15)</f>
-        <v>16.539656242756</v>
+        <v>17.0206694135782</v>
       </c>
       <c r="C60" s="23" t="n">
         <f aca="false">C59/($C$9-Supuestos!$B$15)</f>
-        <v>8.95682404639879</v>
+        <v>9.20723626272825</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>185</v>
@@ -8084,11 +8084,11 @@
       </c>
       <c r="B61" s="9" t="n">
         <f aca="false">ROUNDUP(MAX(B57,B60),0)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C61" s="9" t="n">
         <f aca="false">ROUNDUP(MAX(C57,C60),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>186</v>
@@ -8109,11 +8109,11 @@
       </c>
       <c r="B62" s="28" t="n">
         <f aca="false">B61*Supuestos!$B$15+B59</f>
-        <v>124.737937456536</v>
+        <v>129.124016481469</v>
       </c>
       <c r="C62" s="28" t="n">
         <f aca="false">C61*Supuestos!$B$15+C59</f>
-        <v>67.2409442783928</v>
+        <v>70.2434175763695</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>188</v>
@@ -8159,11 +8159,11 @@
       </c>
       <c r="B64" s="32" t="n">
         <f aca="false">B62/(B63*$B$9*Supuestos!$B$14)</f>
-        <v>0.923984721900265</v>
+        <v>0.956474196159033</v>
       </c>
       <c r="C64" s="32" t="n">
         <f aca="false">C62/(C63*$C$9*Supuestos!$B$14)</f>
-        <v>0.896545923711903</v>
+        <v>0.93657890101826</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>191</v>
@@ -8184,11 +8184,11 @@
       </c>
       <c r="B65" s="21" t="n">
         <f aca="false">B51*B52/B61</f>
-        <v>667.876359613176</v>
+        <v>630.469195351441</v>
       </c>
       <c r="C65" s="21" t="n">
         <f aca="false">C51*C52/C61</f>
-        <v>692.17973212104</v>
+        <v>622.457565496893</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>193</v>
@@ -8290,11 +8290,11 @@
       </c>
       <c r="B70" s="21" t="n">
         <f aca="false">F30*Supuestos!$B$20</f>
-        <v>536.722579401884</v>
+        <v>559.507413809255</v>
       </c>
       <c r="C70" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*H13:H29)*Supuestos!$B$20*Supuestos!$B$22</f>
-        <v>17.7308598471581</v>
+        <v>18.1193273540365</v>
       </c>
       <c r="D70" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*H13:H29)*Supuestos!$B$20</f>
@@ -8302,15 +8302,15 @@
       </c>
       <c r="E70" s="22" t="n">
         <f aca="false">ROUNDUP(C70,0)+ROUNDUP(D70,0)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F70" s="21" t="n">
         <f aca="false">I30*Supuestos!$B$20</f>
-        <v>287.91178805355</v>
+        <v>299.773419353367</v>
       </c>
       <c r="G70" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*K13:K29)*Supuestos!$B$20*Supuestos!$B$22</f>
-        <v>9.63985334793126</v>
+        <v>9.84255490740292</v>
       </c>
       <c r="H70" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*K13:K29)*Supuestos!$B$20</f>
@@ -8330,11 +8330,11 @@
       </c>
       <c r="B71" s="21" t="n">
         <f aca="false">F30*Supuestos!$B$21</f>
-        <v>536.722579401884</v>
+        <v>559.507413809255</v>
       </c>
       <c r="C71" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*H13:H29)*Supuestos!$B$21*Supuestos!$B$22</f>
-        <v>17.7308598471581</v>
+        <v>18.1193273540365</v>
       </c>
       <c r="D71" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*H13:H29)*Supuestos!$B$21</f>
@@ -8342,15 +8342,15 @@
       </c>
       <c r="E71" s="22" t="n">
         <f aca="false">ROUNDUP(C71,0)+ROUNDUP(D71,0)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F71" s="21" t="n">
         <f aca="false">I30*Supuestos!$B$21</f>
-        <v>287.91178805355</v>
+        <v>299.773419353367</v>
       </c>
       <c r="G71" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*K13:K29)*Supuestos!$B$21*Supuestos!$B$22</f>
-        <v>9.63985334793126</v>
+        <v>9.84255490740292</v>
       </c>
       <c r="H71" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*K13:K29)*Supuestos!$B$21</f>
@@ -8370,11 +8370,11 @@
       </c>
       <c r="B72" s="21" t="n">
         <f aca="false">G30</f>
-        <v>583.719434863009</v>
+        <v>585.256044364544</v>
       </c>
       <c r="C72" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*G13:G29/$C$13:$C$29)</f>
-        <v>24.0345318292138</v>
+        <v>24.0985572251111</v>
       </c>
       <c r="D72" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*G13:G29/$C$13:$C$29)</f>
@@ -8386,11 +8386,11 @@
       </c>
       <c r="F72" s="21" t="n">
         <f aca="false">J30</f>
-        <v>321.26184967668</v>
+        <v>322.091098622045</v>
       </c>
       <c r="G72" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*J13:J29/$C$13:$C$29)</f>
-        <v>13.2293828104724</v>
+        <v>13.2639348498627</v>
       </c>
       <c r="H72" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*J13:J29/$C$13:$C$29)</f>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="E74" s="9" t="n">
         <f aca="false">SUM(E70:E73)</f>
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I74" s="9" t="n">
         <f aca="false">SUM(I70:I73)</f>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="E75" s="11" t="n">
         <f aca="false">E74*Supuestos!$B$26</f>
-        <v>156</v>
+        <v>160.8</v>
       </c>
       <c r="I75" s="11" t="n">
         <f aca="false">I74*Supuestos!$B$26</f>
@@ -8470,11 +8470,11 @@
       </c>
       <c r="E76" s="7" t="n">
         <f aca="false">Importados!$P$22</f>
-        <v>1828</v>
+        <v>1833</v>
       </c>
       <c r="I76" s="7" t="n">
         <f aca="false">Importados!$P$56</f>
-        <v>1001</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="E77" s="9" t="n">
         <f aca="false">ROUNDUP(SUM(C70:C72),0)+B63*Supuestos!$B$6+E73*Supuestos!$B$25</f>
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I77" s="9" t="n">
         <f aca="false">ROUNDUP(SUM(G70:G72),0)+C63*Supuestos!$B$6+I73*Supuestos!$B$25</f>

--- a/salida/Recargas.xlsx
+++ b/salida/Recargas.xlsx
@@ -24,12 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="195">
   <si>
     <t xml:space="preserve">Links de los IMPORTRANGE</t>
   </si>
   <si>
-    <t xml:space="preserve">Pegar en la columna B el link del Google Sheet de cada archivo; todas las fórmulas IMPORTRANGE leen el link de esta hoja. Hasta que se pegue, esas celdas muestran el último valor conocido o un error de referencia.</t>
+    <t xml:space="preserve">Pegar en B el link de cada Google Sheet: todos los IMPORTRANGE lo leen de acá.</t>
   </si>
   <si>
     <t xml:space="preserve">Archivo</t>
@@ -47,19 +47,16 @@
     <t xml:space="preserve">PEGAR ACÁ EL LINK DEL GOOGLE SHEET</t>
   </si>
   <si>
-    <t xml:space="preserve">datos_base, PROY_Indexado, parametros_recargas y sobrestock_sustitutos de la planta comercial (ver la hoja Importados)</t>
+    <t xml:space="preserve">Lo que trae la hoja Importados</t>
   </si>
   <si>
     <t xml:space="preserve">Dimensionamiento Recargas Planta Industrial</t>
   </si>
   <si>
-    <t xml:space="preserve">lo mismo de la planta industrial</t>
-  </si>
-  <si>
     <t xml:space="preserve">Recargas — logística de las dos plantas (mes pico de 2035)</t>
   </si>
   <si>
-    <t xml:space="preserve">Importados trae la demanda de cada Dimensionamiento; Supuestos tiene el camión, el recorrido y el pulmón; Cálculo hace las cuentas con las dos plantas lado a lado.</t>
+    <t xml:space="preserve">Desarrollo y fuentes en el Word de justificación de recargas · § 10</t>
   </si>
   <si>
     <t xml:space="preserve">Concepto</t>
@@ -131,28 +128,13 @@
     <t xml:space="preserve">Jaulas A y B a tener</t>
   </si>
   <si>
-    <t xml:space="preserve">Qué cambió respecto del Recargas.xlsx anterior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Demanda por IMPORTRANGE de cada planta (antes: 127.340 fijos de una sola planta); PBA Interior afuera.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Estacionalidad por rubro con fuente (VTV para automotor, inicio de clases para educación; el resto parejo por IRAM 3517-2 9.2.1 y 9.4.14) en lugar del perfil supuesto; sin factor de día pico.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Sustitutos del Dimensionamiento (lote, días en planta y ciclo por rubro): un solo número en los dos archivos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Camión con baranda rebatible y jaulas del Word de recargas en vez de Kangoo / Master; pesos del BOM y del Word de carros.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supuestos de logística (cada uno con su fuente o criterio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La demanda, la estacionalidad, el mix, el lote y los sustitutos no se cargan acá: vienen de Importados. Peso y u. por jaula de cada tipo y minutos por rubro están en Cálculo, junto a su uso.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Camión (Word de recargas)</t>
+    <t xml:space="preserve">Supuestos de logística</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demanda, estacionalidad, mix, lote y sustitutos vienen de Importados · § 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Camión</t>
   </si>
   <si>
     <t xml:space="preserve">Valor</t>
@@ -164,46 +146,58 @@
     <t xml:space="preserve">Vehículo</t>
   </si>
   <si>
-    <t xml:space="preserve">Iveco cabina simple con caja de baranda rebatible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Word de recargas: jaulas palletizables 1,2 × 1,0 m que se cargan y descargan con autoelevador por el costado</t>
+    <t xml:space="preserve">Iveco Daily 55C17 con caja de baranda rebatible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Word de recargas · § 10.1</t>
   </si>
   <si>
     <t xml:space="preserve">Carga útil (kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">Word de recargas: capacidad aprox. 2 t (pico de carga 1,2 t)</t>
+    <t xml:space="preserve">Word de recargas: aprox. 2 t</t>
   </si>
   <si>
     <t xml:space="preserve">Posiciones de jaula 1,2 × 1,0 m en la caja</t>
   </si>
   <si>
-    <t xml:space="preserve">Criterio: 2 a lo ancho × 3 a lo largo en una caja de unos 3,7 × 2,1 m sobre el chasis Daily de 3.450 mm entre ejes (Autocosmos, Daily 55C17: largo total 5.803 mm). Confirmar con el carrocero</t>
+    <t xml:space="preserve">2 × 3 en caja de 3,7 × 2,1 m · § 10.1</t>
   </si>
   <si>
     <t xml:space="preserve">Personas a bordo (chofer + ayudante)</t>
   </si>
   <si>
-    <t xml:space="preserve">Criterio del grupo (Recargas.xlsx original)</t>
+    <t xml:space="preserve">Retiro y colocación de sustitutos · § 10.1</t>
   </si>
   <si>
     <t xml:space="preserve">Peso por persona (kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">Tara de jaulas y cinchas (% de la carga útil)</t>
+    <t xml:space="preserve">Masa normalizada por ocupante (Dir. 2007/46/CE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peso de una jaula (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaula plegable 1,2 × 1,0 m (Palletower Hypacage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tara de las jaulas (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Posiciones × peso de jaula</t>
   </si>
   <si>
     <t xml:space="preserve">Carga neta por viaje (kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">Carga útil − personas − tara</t>
+    <t xml:space="preserve">Carga útil − personas − jaulas</t>
   </si>
   <si>
     <t xml:space="preserve">Precio del camión con caja (ARS)</t>
   </si>
   <si>
-    <t xml:space="preserve">A cotizar (concesionario Iveco + carrocero)</t>
+    <t xml:space="preserve">A cotizar</t>
   </si>
   <si>
     <t xml:space="preserve">2. Recorrido</t>
@@ -212,67 +206,73 @@
     <t xml:space="preserve">Turnos de logística por día</t>
   </si>
   <si>
-    <t xml:space="preserve">Criterio del grupo (Recargas.xlsx original): el camión sale a la mañana y a la tarde</t>
+    <t xml:space="preserve">Los mismos de la planta (Ley 11.544) · § 10.2</t>
   </si>
   <si>
     <t xml:space="preserve">Ida y vuelta planta ↔ zona de clientes (h por viaje)</t>
   </si>
   <si>
-    <t xml:space="preserve">Criterio del grupo (Recargas.xlsx original): clientes en AMBA, ~25 km por tramo</t>
+    <t xml:space="preserve">2 × 25 km (TomTom 2024) · § 10.2</t>
   </si>
   <si>
     <t xml:space="preserve">Tiempo fijo por parada (min)</t>
   </si>
   <si>
-    <t xml:space="preserve">Criterio del grupo: estacionar, presentarse, remito y firma</t>
+    <t xml:space="preserve">Criterio · § 10.2</t>
   </si>
   <si>
     <t xml:space="preserve">Manejo entre paradas (min)</t>
   </si>
   <si>
+    <t xml:space="preserve">5 km a 20 km/h (TomTom 2024) · § 10.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocupación máxima de la flota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El mismo límite de los puestos · § 8</t>
+  </si>
+  <si>
     <t xml:space="preserve">3. Pulmón</t>
   </si>
   <si>
     <t xml:space="preserve">Días de llegada que esperan en recepción</t>
   </si>
   <si>
-    <t xml:space="preserve">Criterio del grupo: lo que trae un turno entra al proceso en el turno siguiente</t>
+    <t xml:space="preserve">Entra en el turno siguiente · § 10.3</t>
   </si>
   <si>
     <t xml:space="preserve">Días de recargados que esperan el recorrido</t>
   </si>
   <si>
-    <t xml:space="preserve">Criterio del grupo: salen en el turno siguiente</t>
+    <t xml:space="preserve">Sale en el turno siguiente · § 10.3</t>
   </si>
   <si>
     <t xml:space="preserve">Factor de jaulas a medio llenar</t>
   </si>
   <si>
-    <t xml:space="preserve">Criterio del grupo: las jaulas se separan por cliente y familia de agente (Word: agrupados por cliente)</t>
+    <t xml:space="preserve">Jaulas por cliente y agente · § 10.3</t>
   </si>
   <si>
     <t xml:space="preserve">Jaulas vacías de reserva (% de las ocupadas)</t>
   </si>
   <si>
-    <t xml:space="preserve">Criterio del grupo</t>
+    <t xml:space="preserve">Criterio · § 10.3</t>
   </si>
   <si>
     <t xml:space="preserve">Niveles de la estantería de sustitutos</t>
   </si>
   <si>
-    <t xml:space="preserve">Criterio del grupo: los sustitutos van en estantería; los rodantes, en el piso</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jaulas vacías apiladas por posición</t>
   </si>
   <si>
-    <t xml:space="preserve">Criterio del grupo: de a 2 con transpaleta</t>
+    <t xml:space="preserve">Hypacage: apilable de a 4</t>
   </si>
   <si>
     <t xml:space="preserve">Superficie por posición con pasillo (m²)</t>
   </si>
   <si>
-    <t xml:space="preserve">Posición de 1,2 × 1,0 m × 2 (pasillo de transpaleta compartido por dos filas)</t>
+    <t xml:space="preserve">Pasillo compartido por dos filas</t>
   </si>
   <si>
     <t xml:space="preserve">Importados de los Dimensionamientos de recargas (IMPORTRANGE; el link va en la hoja Links)</t>
@@ -425,27 +425,18 @@
     <t xml:space="preserve">Logística en el mes pico de 2035 (las dos plantas lado a lado)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cada planta se dimensiona en su mes pico: el de mayor % de recargas del año en su perfil mensual (estacionalidad por rubro del Dimensionamiento).</t>
+    <t xml:space="preserve">Cada planta en su mes pico · § 10</t>
   </si>
   <si>
     <t xml:space="preserve">1. Mes pico</t>
   </si>
   <si>
-    <t xml:space="preserve">Cómo se calcula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N° del mes pico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mes con el mayor % en la fila Toda la planta de Importados</t>
+    <t xml:space="preserve">N° del mes pico (mayor % de Toda la planta)</t>
   </si>
   <si>
     <t xml:space="preserve">% de las recargas del año en el mes pico</t>
   </si>
   <si>
-    <t xml:space="preserve">Importado</t>
-  </si>
-  <si>
     <t xml:space="preserve">2. Por tipo</t>
   </si>
   <si>
@@ -476,10 +467,13 @@
     <t xml:space="preserve">Jaulas por día</t>
   </si>
   <si>
+    <t xml:space="preserve">§ 10.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">A</t>
   </si>
   <si>
-    <t xml:space="preserve">BOM FLAMA, peso de catálogo</t>
+    <t xml:space="preserve">BOM FLAMA</t>
   </si>
   <si>
     <t xml:space="preserve">B</t>
@@ -488,7 +482,7 @@
     <t xml:space="preserve">Rodantes</t>
   </si>
   <si>
-    <t xml:space="preserve">Word de carros, Tabla 0 (carro terminado)</t>
+    <t xml:space="preserve">Word de carros, Tabla 0</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
@@ -497,16 +491,13 @@
     <t xml:space="preserve">Peso medio por u. (kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">u/día = recargas 2035 × % del tipo en el mes pico ÷ días del mes. u. por jaula: Word de recargas (A: 72 de 1 kg; B: 30 de 2,5 kg, 24 de 5 kg o 16 de 10 kg); el resto por tamaño parecido.</t>
-  </si>
-  <si>
     <t xml:space="preserve">3. Por rubro</t>
   </si>
   <si>
     <t xml:space="preserve">min por u. en el cliente</t>
   </si>
   <si>
-    <t xml:space="preserve">Fuente de los minutos</t>
+    <t xml:space="preserve">Fuente</t>
   </si>
   <si>
     <t xml:space="preserve">Rubro</t>
@@ -518,102 +509,51 @@
     <t xml:space="preserve">Horas de parada</t>
   </si>
   <si>
-    <t xml:space="preserve">Recargas.xlsx del grupo (Supuestos E84:E90), criterio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">u/día del rubro = estacionalidad del rubro en el mes pico × recargas 2035 del rubro ÷ días del mes (suma lo mismo que la tabla por tipo). Paradas = 2 por cliente (retiro con sustituto y devolución). Horas = paradas × (parada + manejo) + 2 manipulaciones por u. en el cliente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Camión y viajes</t>
+    <t xml:space="preserve">Criterio · § 10.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Camión y viajes (§ 10.5)</t>
   </si>
   <si>
     <t xml:space="preserve">Equipos que se retiran por día (u)</t>
   </si>
   <si>
-    <t xml:space="preserve">Total por tipo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Carga por sentido por día (u)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sale con recargados + sustitutos y vuelve con lo retirado + sustitutos devueltos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabla por tipo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jaulas por u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Jaulas por día ÷ u/día (cada tipo en su jaula)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Capacidad por viaje por espacio (u)</t>
   </si>
   <si>
-    <t xml:space="preserve">Posiciones de la caja ÷ (jaulas por u. × factor de jaulas a medio llenar)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Capacidad por viaje por peso (u)</t>
   </si>
   <si>
-    <t xml:space="preserve">Carga neta ÷ peso medio</t>
-  </si>
-  <si>
     <t xml:space="preserve">Capacidad por viaje (u)</t>
   </si>
   <si>
-    <t xml:space="preserve">La menor de las dos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Viajes por día por carga</t>
   </si>
   <si>
-    <t xml:space="preserve">Carga por sentido ÷ capacidad por viaje</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total por rubro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Horas de parada y manipuleo por día</t>
   </si>
   <si>
     <t xml:space="preserve">Viajes por día por tiempo</t>
   </si>
   <si>
-    <t xml:space="preserve">Horas de parada ÷ (horas del turno − ida y vuelta): cada viaje entra en un turno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El mayor de los dos, redondeado</t>
-  </si>
-  <si>
     <t xml:space="preserve">Horas de camión por día</t>
   </si>
   <si>
-    <t xml:space="preserve">Viajes × ida y vuelta + horas de parada y manipuleo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Camiones necesarios</t>
   </si>
   <si>
-    <t xml:space="preserve">Horas de camión ÷ (horas por turno × turnos de logística)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas de camión ÷ horas disponibles</t>
-  </si>
-  <si>
     <t xml:space="preserve">Peso por viaje (kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">Control: tiene que quedar por debajo de la carga neta</t>
-  </si>
-  <si>
     <t xml:space="preserve">Inversión en camiones (ARS)</t>
   </si>
   <si>
-    <t xml:space="preserve">Camiones × precio (Supuestos)</t>
-  </si>
-  <si>
     <t xml:space="preserve">5. Pulmón</t>
   </si>
   <si>
@@ -659,7 +599,7 @@
     <t xml:space="preserve">—</t>
   </si>
   <si>
-    <t xml:space="preserve">Apiladas de a 2, junto a despacho</t>
+    <t xml:space="preserve">Apiladas, junto a despacho</t>
   </si>
   <si>
     <t xml:space="preserve">Total de posiciones</t>
@@ -875,15 +815,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1247,7 +1187,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1206,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -1276,31 +1216,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="7" t="n">
         <f aca="false">Importados!$N$22</f>
@@ -1311,208 +1251,183 @@
         <v>107197.372813695</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="8" t="str">
         <f aca="false">Cálculo!B6</f>
-        <v>Feb</v>
+        <v>Ene</v>
       </c>
       <c r="C6" s="8" t="str">
         <f aca="false">Cálculo!C6</f>
-        <v>Feb</v>
+        <v>Ene</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">Cálculo!F30</f>
-        <v>1119.01482761851</v>
+        <v>1050.21469306323</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">Cálculo!I30</f>
-        <v>599.546838706733</v>
+        <v>544.079465849846</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">Cálculo!G30</f>
-        <v>585.256044364544</v>
+        <v>397.522456343171</v>
       </c>
       <c r="C8" s="7" t="n">
         <f aca="false">Cálculo!J30</f>
-        <v>322.091098622045</v>
+        <v>204.786911560761</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="7" t="n">
         <f aca="false">Importados!$P$22</f>
-        <v>1833</v>
+        <v>1757</v>
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">Importados!$P$56</f>
-        <v>1004</v>
+        <v>985</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">Cálculo!E44</f>
-        <v>110.767552253345</v>
+        <v>202.933635977327</v>
       </c>
       <c r="C10" s="7" t="n">
         <f aca="false">Cálculo!I44</f>
-        <v>59.7811503115376</v>
+        <v>104.932589629389</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">Cálculo!B61</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">Cálculo!C61</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">Cálculo!B63</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C12" s="9" t="n">
         <f aca="false">Cálculo!C63</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">Cálculo!B64</f>
-        <v>0.956474196159033</v>
+        <v>0.884975066104527</v>
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">Cálculo!C64</f>
-        <v>0.93657890101826</v>
+        <v>0.801437510401173</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">Cálculo!E74</f>
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C14" s="9" t="n">
         <f aca="false">Cálculo!I74</f>
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" s="11" t="n">
         <f aca="false">Cálculo!E75</f>
-        <v>160.8</v>
+        <v>127.2</v>
       </c>
       <c r="C15" s="11" t="n">
         <f aca="false">Cálculo!I75</f>
-        <v>86.4</v>
+        <v>69.6</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">Cálculo!E77</f>
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="C16" s="9" t="n">
         <f aca="false">Cálculo!I77</f>
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1531,263 +1446,286 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B5" s="13" t="n">
         <v>2000</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B6" s="14" t="n">
         <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B7" s="14" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B8" s="14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="15" t="n">
-        <v>0.1</v>
+        <v>50</v>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>75</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="16" t="n">
-        <f aca="false">(B5-B7*B8)*(1-B9)</f>
-        <v>1656</v>
+        <v>52</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <f aca="false">B6*B9</f>
+        <v>450</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <f aca="false">B5-B7*B8-B10</f>
+        <v>1400</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>62</v>
+      <c r="B14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="17" t="n">
-        <v>1.5</v>
+        <v>59</v>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>2</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>20</v>
+        <v>61</v>
+      </c>
+      <c r="B16" s="16" t="n">
+        <v>1.5</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="B19" s="17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>72</v>
+      <c r="B21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="18" t="n">
-        <v>1.15</v>
+        <v>70</v>
+      </c>
+      <c r="B22" s="16" t="n">
+        <v>0.5</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" s="15" t="n">
-        <v>0.15</v>
+        <v>72</v>
+      </c>
+      <c r="B23" s="16" t="n">
+        <v>0.5</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" s="14" t="n">
-        <v>3</v>
+        <v>74</v>
+      </c>
+      <c r="B24" s="18" t="n">
+        <v>1.15</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B25" s="14" t="n">
-        <v>2</v>
+        <v>76</v>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>0.15</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B26" s="19" t="n">
+      <c r="B28" s="19" t="n">
         <f aca="false">1.2*1*2</f>
         <v>2.4</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1907,52 +1845,52 @@
         <v>109</v>
       </c>
       <c r="B5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""parametros_recargas!E55:P72"")"),0.00749080356204596)</f>
-        <v>0.00749080356204596</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""parametros_recargas!E55:P72"")"),0.119933202334914)</f>
+        <v>0.119933202334914</v>
       </c>
       <c r="C5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0980789973414249)</f>
-        <v>0.0980789973414249</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
+        <v>0.0760133595330172</v>
       </c>
       <c r="D5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0986610060682725)</f>
-        <v>0.0986610060682725</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
+        <v>0.0760133595330172</v>
       </c>
       <c r="E5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993660972474985)</f>
-        <v>0.0993660972474985</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
+        <v>0.0760133595330172</v>
       </c>
       <c r="F5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994029049644587)</f>
-        <v>0.0994029049644587</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
+        <v>0.0760133595330172</v>
       </c>
       <c r="G5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990676994264772)</f>
-        <v>0.0990676994264772</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
+        <v>0.0760133595330172</v>
       </c>
       <c r="H5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100122038394086)</f>
-        <v>0.100122038394086</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
+        <v>0.0760133595330172</v>
       </c>
       <c r="I5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993285448657443)</f>
-        <v>0.0993285448657443</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
+        <v>0.0760133595330172</v>
       </c>
       <c r="J5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994522656022319)</f>
-        <v>0.0994522656022319</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
+        <v>0.0760133595330172</v>
       </c>
       <c r="K5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990432318689603)</f>
-        <v>0.0990432318689603</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
+        <v>0.0760133595330172</v>
       </c>
       <c r="L5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0972817804891135)</f>
-        <v>0.0972817804891135</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
+        <v>0.0760133595330172</v>
       </c>
       <c r="M5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0027046301696863)</f>
-        <v>0.0027046301696863</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.119933202334914)</f>
+        <v>0.119933202334914</v>
       </c>
       <c r="N5" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""datos_base!K2:K18"")"),108842.626397553)</f>
@@ -2004,52 +1942,52 @@
         <v>110</v>
       </c>
       <c r="B6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0786972325544767)</f>
-        <v>0.0786972325544767</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
+        <v>0.0789430506992025</v>
       </c>
       <c r="C6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.134330441900756)</f>
-        <v>0.134330441900756</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.131626442308772)</f>
+        <v>0.131626442308772</v>
       </c>
       <c r="D6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0786972325544767)</f>
-        <v>0.0786972325544767</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
+        <v>0.0789430506992025</v>
       </c>
       <c r="E6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0786972325544767)</f>
-        <v>0.0786972325544767</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
+        <v>0.0789430506992025</v>
       </c>
       <c r="F6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0786972325544767)</f>
-        <v>0.0786972325544767</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
+        <v>0.0789430506992025</v>
       </c>
       <c r="G6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0786972325544767)</f>
-        <v>0.0786972325544767</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
+        <v>0.0789430506992025</v>
       </c>
       <c r="H6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0786972325544767)</f>
-        <v>0.0786972325544767</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
+        <v>0.0789430506992025</v>
       </c>
       <c r="I6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0786972325544767)</f>
-        <v>0.0786972325544767</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
+        <v>0.0789430506992025</v>
       </c>
       <c r="J6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0786972325544767)</f>
-        <v>0.0786972325544767</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
+        <v>0.0789430506992025</v>
       </c>
       <c r="K6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0786972325544767)</f>
-        <v>0.0786972325544767</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
+        <v>0.0789430506992025</v>
       </c>
       <c r="L6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0786972325544767)</f>
-        <v>0.0786972325544767</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
+        <v>0.0789430506992025</v>
       </c>
       <c r="M6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0786972325544767)</f>
-        <v>0.0786972325544767</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
+        <v>0.0789430506992025</v>
       </c>
       <c r="N6" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9216.54014430766)</f>
@@ -2060,8 +1998,8 @@
         <v>1</v>
       </c>
       <c r="P6" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),186)</f>
-        <v>186</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),185)</f>
+        <v>185</v>
       </c>
       <c r="Q6" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2101,52 +2039,52 @@
         <v>111</v>
       </c>
       <c r="B7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0752806934699069)</f>
-        <v>0.0752806934699069</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0830536456103754)</f>
+        <v>0.0830536456103754</v>
       </c>
       <c r="C7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.116386303068985)</f>
-        <v>0.116386303068985</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.113191682697692)</f>
+        <v>0.113191682697692</v>
       </c>
       <c r="D7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0814578576260751)</f>
-        <v>0.0814578576260751</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
+        <v>0.0800778917868397</v>
       </c>
       <c r="E7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0815056305150171)</f>
-        <v>0.0815056305150171</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
+        <v>0.0800778917868397</v>
       </c>
       <c r="F7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0815081243924422)</f>
-        <v>0.0815081243924422</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
+        <v>0.0800778917868397</v>
       </c>
       <c r="G7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0814854128093016)</f>
-        <v>0.0814854128093016</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
+        <v>0.0800778917868397</v>
       </c>
       <c r="H7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0815568487028296)</f>
-        <v>0.0815568487028296</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
+        <v>0.0800778917868397</v>
       </c>
       <c r="I7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0815030861834244)</f>
-        <v>0.0815030861834244</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
+        <v>0.0800778917868397</v>
       </c>
       <c r="J7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0815114687829777)</f>
-        <v>0.0815114687829777</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
+        <v>0.0800778917868397</v>
       </c>
       <c r="K7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0814837550295103)</f>
-        <v>0.0814837550295103</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
+        <v>0.0800778917868397</v>
       </c>
       <c r="L7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0813644093000141)</f>
-        <v>0.0813644093000141</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
+        <v>0.0800778917868397</v>
       </c>
       <c r="M7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0749564101195165)</f>
-        <v>0.0749564101195165</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0830536456103754)</f>
+        <v>0.0830536456103754</v>
       </c>
       <c r="N7" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56059.2707104735)</f>
@@ -2157,8 +2095,8 @@
         <v>1</v>
       </c>
       <c r="P7" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1015)</f>
-        <v>1015</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),967)</f>
+        <v>967</v>
       </c>
       <c r="Q7" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69628)</f>
@@ -2198,52 +2136,52 @@
         <v>112</v>
       </c>
       <c r="B8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778654184776741)</f>
-        <v>0.0778654184776741</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
+        <v>0.078155341572415</v>
       </c>
       <c r="C8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.143480396745585)</f>
-        <v>0.143480396745585</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.140291242703435)</f>
+        <v>0.140291242703435</v>
       </c>
       <c r="D8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778654184776741)</f>
-        <v>0.0778654184776741</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
+        <v>0.078155341572415</v>
       </c>
       <c r="E8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778654184776741)</f>
-        <v>0.0778654184776741</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
+        <v>0.078155341572415</v>
       </c>
       <c r="F8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778654184776741)</f>
-        <v>0.0778654184776741</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
+        <v>0.078155341572415</v>
       </c>
       <c r="G8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778654184776741)</f>
-        <v>0.0778654184776741</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
+        <v>0.078155341572415</v>
       </c>
       <c r="H8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778654184776741)</f>
-        <v>0.0778654184776741</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
+        <v>0.078155341572415</v>
       </c>
       <c r="I8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778654184776741)</f>
-        <v>0.0778654184776741</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
+        <v>0.078155341572415</v>
       </c>
       <c r="J8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778654184776741)</f>
-        <v>0.0778654184776741</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
+        <v>0.078155341572415</v>
       </c>
       <c r="K8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778654184776741)</f>
-        <v>0.0778654184776741</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
+        <v>0.078155341572415</v>
       </c>
       <c r="L8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778654184776741)</f>
-        <v>0.0778654184776741</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
+        <v>0.078155341572415</v>
       </c>
       <c r="M8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778654184776741)</f>
-        <v>0.0778654184776741</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
+        <v>0.078155341572415</v>
       </c>
       <c r="N8" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3319.32790518283)</f>
@@ -2254,8 +2192,8 @@
         <v>1</v>
       </c>
       <c r="P8" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),72)</f>
-        <v>72</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73)</f>
+        <v>73</v>
       </c>
       <c r="Q8" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2295,52 +2233,52 @@
         <v>113</v>
       </c>
       <c r="B9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800765970881449)</f>
-        <v>0.0800765970881449</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
+        <v>0.0802492777307454</v>
       </c>
       <c r="C9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.119157432030406)</f>
-        <v>0.119157432030406</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1172579449618)</f>
+        <v>0.1172579449618</v>
       </c>
       <c r="D9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800765970881449)</f>
-        <v>0.0800765970881449</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
+        <v>0.0802492777307454</v>
       </c>
       <c r="E9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800765970881449)</f>
-        <v>0.0800765970881449</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
+        <v>0.0802492777307454</v>
       </c>
       <c r="F9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800765970881449)</f>
-        <v>0.0800765970881449</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
+        <v>0.0802492777307454</v>
       </c>
       <c r="G9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800765970881449)</f>
-        <v>0.0800765970881449</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
+        <v>0.0802492777307454</v>
       </c>
       <c r="H9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800765970881449)</f>
-        <v>0.0800765970881449</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
+        <v>0.0802492777307454</v>
       </c>
       <c r="I9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800765970881449)</f>
-        <v>0.0800765970881449</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
+        <v>0.0802492777307454</v>
       </c>
       <c r="J9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800765970881449)</f>
-        <v>0.0800765970881449</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
+        <v>0.0802492777307454</v>
       </c>
       <c r="K9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800765970881449)</f>
-        <v>0.0800765970881449</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
+        <v>0.0802492777307454</v>
       </c>
       <c r="L9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800765970881449)</f>
-        <v>0.0800765970881449</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
+        <v>0.0802492777307454</v>
       </c>
       <c r="M9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800765970881449)</f>
-        <v>0.0800765970881449</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
+        <v>0.0802492777307454</v>
       </c>
       <c r="N9" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4686.14321768856)</f>
@@ -2351,8 +2289,8 @@
         <v>1</v>
       </c>
       <c r="P9" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88)</f>
-        <v>88</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),86)</f>
+        <v>86</v>
       </c>
       <c r="Q9" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2448,8 +2386,8 @@
         <v>1</v>
       </c>
       <c r="P10" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15)</f>
-        <v>15</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12)</f>
+        <v>12</v>
       </c>
       <c r="Q10" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2545,8 +2483,8 @@
         <v>1</v>
       </c>
       <c r="P11" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8)</f>
-        <v>8</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6)</f>
+        <v>6</v>
       </c>
       <c r="Q11" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2642,8 +2580,8 @@
         <v>1</v>
       </c>
       <c r="P12" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5)</f>
-        <v>5</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4)</f>
+        <v>4</v>
       </c>
       <c r="Q12" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2683,52 +2621,52 @@
         <v>117</v>
       </c>
       <c r="B13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07684527070735)</f>
-        <v>0.07684527070735</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
+        <v>0.0771892846953241</v>
       </c>
       <c r="C13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.15470202221915)</f>
-        <v>0.15470202221915</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.150917868351435)</f>
+        <v>0.150917868351435</v>
       </c>
       <c r="D13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07684527070735)</f>
-        <v>0.07684527070735</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
+        <v>0.0771892846953241</v>
       </c>
       <c r="E13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07684527070735)</f>
-        <v>0.07684527070735</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
+        <v>0.0771892846953241</v>
       </c>
       <c r="F13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07684527070735)</f>
-        <v>0.07684527070735</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
+        <v>0.0771892846953241</v>
       </c>
       <c r="G13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07684527070735)</f>
-        <v>0.07684527070735</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
+        <v>0.0771892846953241</v>
       </c>
       <c r="H13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07684527070735)</f>
-        <v>0.07684527070735</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
+        <v>0.0771892846953241</v>
       </c>
       <c r="I13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07684527070735)</f>
-        <v>0.07684527070735</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
+        <v>0.0771892846953241</v>
       </c>
       <c r="J13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07684527070735)</f>
-        <v>0.07684527070735</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
+        <v>0.0771892846953241</v>
       </c>
       <c r="K13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07684527070735)</f>
-        <v>0.07684527070735</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
+        <v>0.0771892846953241</v>
       </c>
       <c r="L13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07684527070735)</f>
-        <v>0.07684527070735</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
+        <v>0.0771892846953241</v>
       </c>
       <c r="M13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07684527070735)</f>
-        <v>0.07684527070735</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
+        <v>0.0771892846953241</v>
       </c>
       <c r="N13" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2310.99407344162)</f>
@@ -2739,8 +2677,8 @@
         <v>1</v>
       </c>
       <c r="P13" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58)</f>
-        <v>58</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54)</f>
+        <v>54</v>
       </c>
       <c r="Q13" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2780,52 +2718,52 @@
         <v>118</v>
       </c>
       <c r="B14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07847146142097)</f>
-        <v>0.07847146142097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
+        <v>0.0787292505395418</v>
       </c>
       <c r="C14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.13681392436933)</f>
-        <v>0.13681392436933</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.13397824406504)</f>
+        <v>0.13397824406504</v>
       </c>
       <c r="D14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07847146142097)</f>
-        <v>0.07847146142097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
+        <v>0.0787292505395418</v>
       </c>
       <c r="E14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07847146142097)</f>
-        <v>0.07847146142097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
+        <v>0.0787292505395418</v>
       </c>
       <c r="F14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07847146142097)</f>
-        <v>0.07847146142097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
+        <v>0.0787292505395418</v>
       </c>
       <c r="G14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07847146142097)</f>
-        <v>0.07847146142097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
+        <v>0.0787292505395418</v>
       </c>
       <c r="H14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07847146142097)</f>
-        <v>0.07847146142097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
+        <v>0.0787292505395418</v>
       </c>
       <c r="I14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07847146142097)</f>
-        <v>0.07847146142097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
+        <v>0.0787292505395418</v>
       </c>
       <c r="J14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07847146142097)</f>
-        <v>0.07847146142097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
+        <v>0.0787292505395418</v>
       </c>
       <c r="K14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07847146142097)</f>
-        <v>0.07847146142097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
+        <v>0.0787292505395418</v>
       </c>
       <c r="L14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07847146142097)</f>
-        <v>0.07847146142097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
+        <v>0.0787292505395418</v>
       </c>
       <c r="M14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.07847146142097)</f>
-        <v>0.07847146142097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
+        <v>0.0787292505395418</v>
       </c>
       <c r="N14" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12606.7299522508)</f>
@@ -2836,8 +2774,8 @@
         <v>1</v>
       </c>
       <c r="P14" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),262)</f>
-        <v>262</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258)</f>
+        <v>258</v>
       </c>
       <c r="Q14" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2877,52 +2815,52 @@
         <v>119</v>
       </c>
       <c r="B15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826637580910584)</f>
-        <v>0.0826637580910584</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
+        <v>0.0826992607152812</v>
       </c>
       <c r="C15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.090698660998357)</f>
-        <v>0.090698660998357</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0903081321319072)</f>
+        <v>0.0903081321319072</v>
       </c>
       <c r="D15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826637580910584)</f>
-        <v>0.0826637580910584</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
+        <v>0.0826992607152812</v>
       </c>
       <c r="E15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826637580910584)</f>
-        <v>0.0826637580910584</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
+        <v>0.0826992607152812</v>
       </c>
       <c r="F15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826637580910584)</f>
-        <v>0.0826637580910584</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
+        <v>0.0826992607152812</v>
       </c>
       <c r="G15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826637580910584)</f>
-        <v>0.0826637580910584</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
+        <v>0.0826992607152812</v>
       </c>
       <c r="H15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826637580910584)</f>
-        <v>0.0826637580910584</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
+        <v>0.0826992607152812</v>
       </c>
       <c r="I15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826637580910584)</f>
-        <v>0.0826637580910584</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
+        <v>0.0826992607152812</v>
       </c>
       <c r="J15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826637580910584)</f>
-        <v>0.0826637580910584</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
+        <v>0.0826992607152812</v>
       </c>
       <c r="K15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826637580910584)</f>
-        <v>0.0826637580910584</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
+        <v>0.0826992607152812</v>
       </c>
       <c r="L15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826637580910584)</f>
-        <v>0.0826637580910584</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
+        <v>0.0826992607152812</v>
       </c>
       <c r="M15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826637580910584)</f>
-        <v>0.0826637580910584</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
+        <v>0.0826992607152812</v>
       </c>
       <c r="N15" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4308.38387982745)</f>
@@ -2933,8 +2871,8 @@
         <v>1</v>
       </c>
       <c r="P15" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),68)</f>
-        <v>68</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),62)</f>
+        <v>62</v>
       </c>
       <c r="Q15" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -3030,8 +2968,8 @@
         <v>1</v>
       </c>
       <c r="P16" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12)</f>
-        <v>12</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10)</f>
+        <v>10</v>
       </c>
       <c r="Q16" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -3127,8 +3065,8 @@
         <v>1</v>
       </c>
       <c r="P17" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5)</f>
-        <v>5</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4)</f>
+        <v>4</v>
       </c>
       <c r="Q17" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -3168,52 +3106,52 @@
         <v>122</v>
       </c>
       <c r="B18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822263312114782)</f>
-        <v>0.0822263312114782</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
+        <v>0.0822850273487674</v>
       </c>
       <c r="C18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955103566737395)</f>
-        <v>0.0955103566737395</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0948646991635592)</f>
+        <v>0.0948646991635592</v>
       </c>
       <c r="D18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822263312114782)</f>
-        <v>0.0822263312114782</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
+        <v>0.0822850273487674</v>
       </c>
       <c r="E18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822263312114782)</f>
-        <v>0.0822263312114782</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
+        <v>0.0822850273487674</v>
       </c>
       <c r="F18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822263312114782)</f>
-        <v>0.0822263312114782</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
+        <v>0.0822850273487674</v>
       </c>
       <c r="G18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822263312114782)</f>
-        <v>0.0822263312114782</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
+        <v>0.0822850273487674</v>
       </c>
       <c r="H18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822263312114782)</f>
-        <v>0.0822263312114782</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
+        <v>0.0822850273487674</v>
       </c>
       <c r="I18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822263312114782)</f>
-        <v>0.0822263312114782</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
+        <v>0.0822850273487674</v>
       </c>
       <c r="J18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822263312114782)</f>
-        <v>0.0822263312114782</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
+        <v>0.0822850273487674</v>
       </c>
       <c r="K18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822263312114782)</f>
-        <v>0.0822263312114782</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
+        <v>0.0822850273487674</v>
       </c>
       <c r="L18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822263312114782)</f>
-        <v>0.0822263312114782</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
+        <v>0.0822850273487674</v>
       </c>
       <c r="M18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822263312114782)</f>
-        <v>0.0822263312114782</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
+        <v>0.0822850273487674</v>
       </c>
       <c r="N18" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),577.776131502584)</f>
@@ -3224,8 +3162,8 @@
         <v>1</v>
       </c>
       <c r="P18" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10)</f>
-        <v>10</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9)</f>
+        <v>9</v>
       </c>
       <c r="Q18" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -3265,52 +3203,52 @@
         <v>123</v>
       </c>
       <c r="B19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822261806345707)</f>
-        <v>0.0822261806345707</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
+        <v>0.0822848847558399</v>
       </c>
       <c r="C19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955120130197222)</f>
-        <v>0.0955120130197222</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0948662676857615)</f>
+        <v>0.0948662676857615</v>
       </c>
       <c r="D19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822261806345707)</f>
-        <v>0.0822261806345707</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
+        <v>0.0822848847558399</v>
       </c>
       <c r="E19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822261806345707)</f>
-        <v>0.0822261806345707</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
+        <v>0.0822848847558399</v>
       </c>
       <c r="F19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822261806345707)</f>
-        <v>0.0822261806345707</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
+        <v>0.0822848847558399</v>
       </c>
       <c r="G19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822261806345707)</f>
-        <v>0.0822261806345707</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
+        <v>0.0822848847558399</v>
       </c>
       <c r="H19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822261806345707)</f>
-        <v>0.0822261806345707</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
+        <v>0.0822848847558399</v>
       </c>
       <c r="I19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822261806345707)</f>
-        <v>0.0822261806345707</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
+        <v>0.0822848847558399</v>
       </c>
       <c r="J19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822261806345707)</f>
-        <v>0.0822261806345707</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
+        <v>0.0822848847558399</v>
       </c>
       <c r="K19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822261806345707)</f>
-        <v>0.0822261806345707</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
+        <v>0.0822848847558399</v>
       </c>
       <c r="L19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822261806345707)</f>
-        <v>0.0822261806345707</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
+        <v>0.0822848847558399</v>
       </c>
       <c r="M19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822261806345707)</f>
-        <v>0.0822261806345707</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
+        <v>0.0822848847558399</v>
       </c>
       <c r="N19" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1271.10748852936)</f>
@@ -3321,8 +3259,8 @@
         <v>1</v>
       </c>
       <c r="P19" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21)</f>
-        <v>21</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19)</f>
+        <v>19</v>
       </c>
       <c r="Q19" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -3362,52 +3300,52 @@
         <v>124</v>
       </c>
       <c r="B20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822265137471396)</f>
-        <v>0.0822265137471396</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
+        <v>0.0822852002059122</v>
       </c>
       <c r="C20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.095508348781465)</f>
-        <v>0.095508348781465</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0948627977349655)</f>
+        <v>0.0948627977349655</v>
       </c>
       <c r="D20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822265137471396)</f>
-        <v>0.0822265137471396</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
+        <v>0.0822852002059122</v>
       </c>
       <c r="E20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822265137471396)</f>
-        <v>0.0822265137471396</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
+        <v>0.0822852002059122</v>
       </c>
       <c r="F20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822265137471396)</f>
-        <v>0.0822265137471396</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
+        <v>0.0822852002059122</v>
       </c>
       <c r="G20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822265137471396)</f>
-        <v>0.0822265137471396</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
+        <v>0.0822852002059122</v>
       </c>
       <c r="H20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822265137471396)</f>
-        <v>0.0822265137471396</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
+        <v>0.0822852002059122</v>
       </c>
       <c r="I20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822265137471396)</f>
-        <v>0.0822265137471396</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
+        <v>0.0822852002059122</v>
       </c>
       <c r="J20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822265137471396)</f>
-        <v>0.0822265137471396</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
+        <v>0.0822852002059122</v>
       </c>
       <c r="K20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822265137471396)</f>
-        <v>0.0822265137471396</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
+        <v>0.0822852002059122</v>
       </c>
       <c r="L20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822265137471396)</f>
-        <v>0.0822265137471396</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
+        <v>0.0822852002059122</v>
       </c>
       <c r="M20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822265137471396)</f>
-        <v>0.0822265137471396</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
+        <v>0.0822852002059122</v>
       </c>
       <c r="N20" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.332543143421)</f>
@@ -3459,52 +3397,52 @@
         <v>125</v>
       </c>
       <c r="B21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822253559860661)</f>
-        <v>0.0822253559860661</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
+        <v>0.082284103832348</v>
       </c>
       <c r="C21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955210841532726)</f>
-        <v>0.0955210841532726</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0948748578441723)</f>
+        <v>0.0948748578441723</v>
       </c>
       <c r="D21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822253559860661)</f>
-        <v>0.0822253559860661</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
+        <v>0.082284103832348</v>
       </c>
       <c r="E21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822253559860661)</f>
-        <v>0.0822253559860661</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
+        <v>0.082284103832348</v>
       </c>
       <c r="F21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822253559860661)</f>
-        <v>0.0822253559860661</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
+        <v>0.082284103832348</v>
       </c>
       <c r="G21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822253559860661)</f>
-        <v>0.0822253559860661</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
+        <v>0.082284103832348</v>
       </c>
       <c r="H21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822253559860661)</f>
-        <v>0.0822253559860661</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
+        <v>0.082284103832348</v>
       </c>
       <c r="I21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822253559860661)</f>
-        <v>0.0822253559860661</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
+        <v>0.082284103832348</v>
       </c>
       <c r="J21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822253559860661)</f>
-        <v>0.0822253559860661</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
+        <v>0.082284103832348</v>
       </c>
       <c r="K21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822253559860661)</f>
-        <v>0.0822253559860661</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
+        <v>0.082284103832348</v>
       </c>
       <c r="L21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822253559860661)</f>
-        <v>0.0822253559860661</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
+        <v>0.082284103832348</v>
       </c>
       <c r="M21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822253559860661)</f>
-        <v>0.0822253559860661</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
+        <v>0.082284103832348</v>
       </c>
       <c r="N21" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),184.888361725934)</f>
@@ -3556,52 +3494,52 @@
         <v>126</v>
       </c>
       <c r="B22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0403512821171889)</f>
-        <v>0.0403512821171889</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101848800284409)</f>
+        <v>0.101848800284409</v>
       </c>
       <c r="C22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.108520970470319)</f>
-        <v>0.108520970470319</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955604631711142)</f>
+        <v>0.0955604631711142</v>
       </c>
       <c r="D22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0901475479034248)</f>
-        <v>0.0901475479034248</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
+        <v>0.0778602151400075</v>
       </c>
       <c r="E22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905326617542125)</f>
-        <v>0.0905326617542125</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
+        <v>0.0778602151400075</v>
       </c>
       <c r="F22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905527657663388)</f>
-        <v>0.0905527657663388</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
+        <v>0.0778602151400075</v>
       </c>
       <c r="G22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0903696798061951)</f>
-        <v>0.0903696798061951</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
+        <v>0.0778602151400075</v>
       </c>
       <c r="H22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0909455493558567)</f>
-        <v>0.0909455493558567</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
+        <v>0.0778602151400075</v>
       </c>
       <c r="I22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905121510135173)</f>
-        <v>0.0905121510135173</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
+        <v>0.0778602151400075</v>
       </c>
       <c r="J22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905797260600571)</f>
-        <v>0.0905797260600571</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
+        <v>0.0778602151400075</v>
       </c>
       <c r="K22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0903563158674985)</f>
-        <v>0.0903563158674985</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
+        <v>0.0778602151400075</v>
       </c>
       <c r="L22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0893942284895046)</f>
-        <v>0.0893942284895046</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
+        <v>0.0778602151400075</v>
       </c>
       <c r="M22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0377371213958866)</f>
-        <v>0.0377371213958866</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101848800284409)</f>
+        <v>0.101848800284409</v>
       </c>
       <c r="N22" s="7" t="n">
         <f aca="false">SUM(N5:N21)</f>
@@ -3609,7 +3547,7 @@
       </c>
       <c r="P22" s="7" t="n">
         <f aca="false">SUM(P5:P21)</f>
-        <v>1833</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3617,32 +3555,32 @@
         <v>127</v>
       </c>
       <c r="Q23" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""sobrestock_sustitutos!B18:H18"")"),25)</f>
-        <v>25</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""sobrestock_sustitutos!B18:H18"")"),9)</f>
+        <v>9</v>
       </c>
       <c r="R23" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14)</f>
-        <v>14</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15)</f>
+        <v>15</v>
       </c>
       <c r="S23" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18)</f>
-        <v>18</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12)</f>
+        <v>12</v>
       </c>
       <c r="T23" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20)</f>
-        <v>20</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11)</f>
+        <v>11</v>
       </c>
       <c r="U23" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45)</f>
-        <v>45</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10)</f>
+        <v>10</v>
       </c>
       <c r="V23" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35)</f>
-        <v>35</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),61)</f>
+        <v>61</v>
       </c>
       <c r="W23" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16)</f>
-        <v>16</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3709,52 +3647,52 @@
         <v>101</v>
       </c>
       <c r="B28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""parametros_recargas!E35:P41"")"),0.00735238492719494)</f>
-        <v>0.00735238492719494</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""parametros_recargas!E35:P41"")"),0.12)</f>
+        <v>0.12</v>
       </c>
       <c r="C28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0981059093482913)</f>
-        <v>0.0981059093482913</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="D28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0986889802872471)</f>
-        <v>0.0986889802872471</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="E28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993953583138234)</f>
-        <v>0.0993953583138234</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="F28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994322332077878)</f>
-        <v>0.0994322332077878</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="G28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990964158931013)</f>
-        <v>0.0990964158931013</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="H28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100152679112986)</f>
-        <v>0.100152679112986</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="I28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993577373959928)</f>
-        <v>0.0993577373959928</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="J28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994816839326416)</f>
-        <v>0.0994816839326416</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="K28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990719036803504)</f>
-        <v>0.0990719036803504</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="L28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0973072375119662)</f>
-        <v>0.0973072375119662</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="M28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.00255747638861682)</f>
-        <v>0.00255747638861682</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.12)</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3815,52 +3753,52 @@
         <v>103</v>
       </c>
       <c r="B30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
+        <v>0.0295134514379623</v>
       </c>
       <c r="C30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7085)</f>
-        <v>0.7085</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.675352034182415)</f>
+        <v>0.675352034182415</v>
       </c>
       <c r="D30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
+        <v>0.0295134514379623</v>
       </c>
       <c r="E30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
+        <v>0.0295134514379623</v>
       </c>
       <c r="F30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
+        <v>0.0295134514379623</v>
       </c>
       <c r="G30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
+        <v>0.0295134514379623</v>
       </c>
       <c r="H30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
+        <v>0.0295134514379623</v>
       </c>
       <c r="I30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
+        <v>0.0295134514379623</v>
       </c>
       <c r="J30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
+        <v>0.0295134514379623</v>
       </c>
       <c r="K30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
+        <v>0.0295134514379623</v>
       </c>
       <c r="L30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
+        <v>0.0295134514379623</v>
       </c>
       <c r="M30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
+        <v>0.0295134514379623</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4159,52 +4097,52 @@
         <v>109</v>
       </c>
       <c r="B39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""parametros_recargas!E55:P72"")"),0.00747139865671394)</f>
-        <v>0.00747139865671394</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""parametros_recargas!E55:P72"")"),0.119942566698092)</f>
+        <v>0.119942566698092</v>
       </c>
       <c r="C39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0980827701350671)</f>
-        <v>0.0980827701350671</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
+        <v>0.0760114866603815</v>
       </c>
       <c r="D39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0986649277734065)</f>
-        <v>0.0986649277734065</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
+        <v>0.0760114866603815</v>
       </c>
       <c r="E39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993701993557339)</f>
-        <v>0.0993701993557339</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
+        <v>0.0760114866603815</v>
       </c>
       <c r="F39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994070164902368)</f>
-        <v>0.0994070164902368</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
+        <v>0.0760114866603815</v>
       </c>
       <c r="G39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990717251872927)</f>
-        <v>0.0990717251872927</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
+        <v>0.0760114866603815</v>
       </c>
       <c r="H39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100126333915785)</f>
-        <v>0.100126333915785</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
+        <v>0.0760114866603815</v>
       </c>
       <c r="I39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993326373659087)</f>
-        <v>0.0993326373659087</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
+        <v>0.0760114866603815</v>
       </c>
       <c r="J39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994563897573158)</f>
-        <v>0.0994563897573158</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
+        <v>0.0760114866603815</v>
       </c>
       <c r="K39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990472513695595)</f>
-        <v>0.0990472513695595</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
+        <v>0.0760114866603815</v>
       </c>
       <c r="L39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0972853493085793)</f>
-        <v>0.0972853493085793</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
+        <v>0.0760114866603815</v>
       </c>
       <c r="M39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.00268400068440077)</f>
-        <v>0.00268400068440077</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.119942566698092)</f>
+        <v>0.119942566698092</v>
       </c>
       <c r="N39" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""datos_base!K2:K18"")"),56575.8368575054)</f>
@@ -4256,52 +4194,52 @@
         <v>110</v>
       </c>
       <c r="B40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779283688144388)</f>
-        <v>0.0779283688144388</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
+        <v>0.0779725990367327</v>
       </c>
       <c r="C40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.142787943041173)</f>
-        <v>0.142787943041173</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.14230141059594)</f>
+        <v>0.14230141059594</v>
       </c>
       <c r="D40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779283688144388)</f>
-        <v>0.0779283688144388</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
+        <v>0.0779725990367327</v>
       </c>
       <c r="E40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779283688144388)</f>
-        <v>0.0779283688144388</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
+        <v>0.0779725990367327</v>
       </c>
       <c r="F40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779283688144388)</f>
-        <v>0.0779283688144388</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
+        <v>0.0779725990367327</v>
       </c>
       <c r="G40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779283688144388)</f>
-        <v>0.0779283688144388</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
+        <v>0.0779725990367327</v>
       </c>
       <c r="H40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779283688144388)</f>
-        <v>0.0779283688144388</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
+        <v>0.0779725990367327</v>
       </c>
       <c r="I40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779283688144388)</f>
-        <v>0.0779283688144388</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
+        <v>0.0779725990367327</v>
       </c>
       <c r="J40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779283688144388)</f>
-        <v>0.0779283688144388</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
+        <v>0.0779725990367327</v>
       </c>
       <c r="K40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779283688144388)</f>
-        <v>0.0779283688144388</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
+        <v>0.0779725990367327</v>
       </c>
       <c r="L40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779283688144388)</f>
-        <v>0.0779283688144388</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
+        <v>0.0779725990367327</v>
       </c>
       <c r="M40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779283688144388)</f>
-        <v>0.0779283688144388</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
+        <v>0.0779725990367327</v>
       </c>
       <c r="N40" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4790.71011839089)</f>
@@ -4312,8 +4250,8 @@
         <v>1</v>
       </c>
       <c r="P40" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103)</f>
-        <v>103</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104)</f>
+        <v>104</v>
       </c>
       <c r="Q40" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -4353,52 +4291,52 @@
         <v>111</v>
       </c>
       <c r="B41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0744731592432624)</f>
-        <v>0.0744731592432624</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824116289014618)</f>
+        <v>0.0824116289014618</v>
       </c>
       <c r="C41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.123146966709803)</f>
-        <v>0.123146966709803</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.121277469433113)</f>
+        <v>0.121277469433113</v>
       </c>
       <c r="D41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.080886415337057)</f>
-        <v>0.080886415337057</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
+        <v>0.0793221414182182</v>
       </c>
       <c r="E41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809360141114104)</f>
-        <v>0.0809360141114104</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
+        <v>0.0793221414182182</v>
       </c>
       <c r="F41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809386033051228)</f>
-        <v>0.0809386033051228</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
+        <v>0.0793221414182182</v>
       </c>
       <c r="G41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809150236826142)</f>
-        <v>0.0809150236826142</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
+        <v>0.0793221414182182</v>
       </c>
       <c r="H41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809891898643607)</f>
-        <v>0.0809891898643607</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
+        <v>0.0793221414182182</v>
       </c>
       <c r="I41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809333725351661)</f>
-        <v>0.0809333725351661</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
+        <v>0.0793221414182182</v>
       </c>
       <c r="J41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809420755186563)</f>
-        <v>0.0809420755186563</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
+        <v>0.0793221414182182</v>
       </c>
       <c r="K41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809133025422851)</f>
-        <v>0.0809133025422851</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
+        <v>0.0793221414182182</v>
       </c>
       <c r="L41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0807893954050276)</f>
-        <v>0.0807893954050276</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
+        <v>0.0793221414182182</v>
       </c>
       <c r="M41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741364817452343)</f>
-        <v>0.0741364817452343</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824116289014618)</f>
+        <v>0.0824116289014618</v>
       </c>
       <c r="N41" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29139.3203107948)</f>
@@ -4409,8 +4347,8 @@
         <v>1</v>
       </c>
       <c r="P41" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),554)</f>
-        <v>554</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),540)</f>
+        <v>540</v>
       </c>
       <c r="Q41" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36760)</f>
@@ -4450,52 +4388,52 @@
         <v>112</v>
       </c>
       <c r="B42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770431705097184)</f>
-        <v>0.0770431705097184</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
+        <v>0.0770946445386376</v>
       </c>
       <c r="C42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.152525124393098)</f>
-        <v>0.152525124393098</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.151958910074986)</f>
+        <v>0.151958910074986</v>
       </c>
       <c r="D42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770431705097184)</f>
-        <v>0.0770431705097184</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
+        <v>0.0770946445386376</v>
       </c>
       <c r="E42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770431705097184)</f>
-        <v>0.0770431705097184</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
+        <v>0.0770946445386376</v>
       </c>
       <c r="F42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770431705097184)</f>
-        <v>0.0770431705097184</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
+        <v>0.0770946445386376</v>
       </c>
       <c r="G42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770431705097184)</f>
-        <v>0.0770431705097184</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
+        <v>0.0770946445386376</v>
       </c>
       <c r="H42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770431705097184)</f>
-        <v>0.0770431705097184</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
+        <v>0.0770946445386376</v>
       </c>
       <c r="I42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770431705097184)</f>
-        <v>0.0770431705097184</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
+        <v>0.0770946445386376</v>
       </c>
       <c r="J42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770431705097184)</f>
-        <v>0.0770431705097184</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
+        <v>0.0770946445386376</v>
       </c>
       <c r="K42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770431705097184)</f>
-        <v>0.0770431705097184</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
+        <v>0.0770946445386376</v>
       </c>
       <c r="L42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770431705097184)</f>
-        <v>0.0770431705097184</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
+        <v>0.0770946445386376</v>
       </c>
       <c r="M42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770431705097184)</f>
-        <v>0.0770431705097184</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
+        <v>0.0770946445386376</v>
       </c>
       <c r="N42" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1725.36955653994)</f>
@@ -4506,8 +4444,8 @@
         <v>1</v>
       </c>
       <c r="P42" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40)</f>
-        <v>40</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),41)</f>
+        <v>41</v>
       </c>
       <c r="Q42" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -4547,52 +4485,52 @@
         <v>113</v>
       </c>
       <c r="B43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793497958252236)</f>
-        <v>0.0793497958252236</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
+        <v>0.0793823941427303</v>
       </c>
       <c r="C43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.127152245922541)</f>
-        <v>0.127152245922541</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.126793664429966)</f>
+        <v>0.126793664429966</v>
       </c>
       <c r="D43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793497958252236)</f>
-        <v>0.0793497958252236</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
+        <v>0.0793823941427303</v>
       </c>
       <c r="E43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793497958252236)</f>
-        <v>0.0793497958252236</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
+        <v>0.0793823941427303</v>
       </c>
       <c r="F43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793497958252236)</f>
-        <v>0.0793497958252236</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
+        <v>0.0793823941427303</v>
       </c>
       <c r="G43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793497958252236)</f>
-        <v>0.0793497958252236</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
+        <v>0.0793823941427303</v>
       </c>
       <c r="H43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793497958252236)</f>
-        <v>0.0793497958252236</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
+        <v>0.0793823941427303</v>
       </c>
       <c r="I43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793497958252236)</f>
-        <v>0.0793497958252236</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
+        <v>0.0793823941427303</v>
       </c>
       <c r="J43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793497958252236)</f>
-        <v>0.0793497958252236</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
+        <v>0.0793823941427303</v>
       </c>
       <c r="K43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793497958252236)</f>
-        <v>0.0793497958252236</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
+        <v>0.0793823941427303</v>
       </c>
       <c r="L43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793497958252236)</f>
-        <v>0.0793497958252236</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
+        <v>0.0793823941427303</v>
       </c>
       <c r="M43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793497958252236)</f>
-        <v>0.0793497958252236</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
+        <v>0.0793823941427303</v>
       </c>
       <c r="N43" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2435.83311933763)</f>
@@ -4700,8 +4638,8 @@
         <v>1</v>
       </c>
       <c r="P44" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8)</f>
-        <v>8</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6)</f>
+        <v>6</v>
       </c>
       <c r="Q44" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -4797,8 +4735,8 @@
         <v>1</v>
       </c>
       <c r="P45" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5)</f>
-        <v>5</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4)</f>
+        <v>4</v>
       </c>
       <c r="Q45" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -4894,8 +4832,8 @@
         <v>1</v>
       </c>
       <c r="P46" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3)</f>
-        <v>3</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2)</f>
+        <v>2</v>
       </c>
       <c r="Q46" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -4935,52 +4873,52 @@
         <v>117</v>
       </c>
       <c r="B47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0757619225700752)</f>
-        <v>0.0757619225700752</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
+        <v>0.0758238813821944</v>
       </c>
       <c r="C47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.166618851729173)</f>
-        <v>0.166618851729173</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.165937304795862)</f>
+        <v>0.165937304795862</v>
       </c>
       <c r="D47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0757619225700752)</f>
-        <v>0.0757619225700752</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
+        <v>0.0758238813821944</v>
       </c>
       <c r="E47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0757619225700752)</f>
-        <v>0.0757619225700752</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
+        <v>0.0758238813821944</v>
       </c>
       <c r="F47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0757619225700752)</f>
-        <v>0.0757619225700752</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
+        <v>0.0758238813821944</v>
       </c>
       <c r="G47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0757619225700752)</f>
-        <v>0.0757619225700752</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
+        <v>0.0758238813821944</v>
       </c>
       <c r="H47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0757619225700752)</f>
-        <v>0.0757619225700752</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
+        <v>0.0758238813821944</v>
       </c>
       <c r="I47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0757619225700752)</f>
-        <v>0.0757619225700752</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
+        <v>0.0758238813821944</v>
       </c>
       <c r="J47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0757619225700752)</f>
-        <v>0.0757619225700752</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
+        <v>0.0758238813821944</v>
       </c>
       <c r="K47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0757619225700752)</f>
-        <v>0.0757619225700752</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
+        <v>0.0758238813821944</v>
       </c>
       <c r="L47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0757619225700752)</f>
-        <v>0.0757619225700752</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
+        <v>0.0758238813821944</v>
       </c>
       <c r="M47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0757619225700752)</f>
-        <v>0.0757619225700752</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
+        <v>0.0758238813821944</v>
       </c>
       <c r="N47" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1201.24282190818)</f>
@@ -4991,8 +4929,8 @@
         <v>1</v>
       </c>
       <c r="P47" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32)</f>
-        <v>32</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31)</f>
+        <v>31</v>
       </c>
       <c r="Q47" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -5032,52 +4970,52 @@
         <v>118</v>
       </c>
       <c r="B48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776096914243875)</f>
-        <v>0.0776096914243875</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
+        <v>0.0776565294661689</v>
       </c>
       <c r="C48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.146293394331737)</f>
-        <v>0.146293394331737</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.145778175872141)</f>
+        <v>0.145778175872141</v>
       </c>
       <c r="D48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776096914243875)</f>
-        <v>0.0776096914243875</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
+        <v>0.0776565294661689</v>
       </c>
       <c r="E48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776096914243875)</f>
-        <v>0.0776096914243875</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
+        <v>0.0776565294661689</v>
       </c>
       <c r="F48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776096914243875)</f>
-        <v>0.0776096914243875</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
+        <v>0.0776565294661689</v>
       </c>
       <c r="G48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776096914243875)</f>
-        <v>0.0776096914243875</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
+        <v>0.0776565294661689</v>
       </c>
       <c r="H48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776096914243875)</f>
-        <v>0.0776096914243875</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
+        <v>0.0776565294661689</v>
       </c>
       <c r="I48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776096914243875)</f>
-        <v>0.0776096914243875</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
+        <v>0.0776565294661689</v>
       </c>
       <c r="J48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776096914243875)</f>
-        <v>0.0776096914243875</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
+        <v>0.0776565294661689</v>
       </c>
       <c r="K48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776096914243875)</f>
-        <v>0.0776096914243875</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
+        <v>0.0776565294661689</v>
       </c>
       <c r="L48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776096914243875)</f>
-        <v>0.0776096914243875</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
+        <v>0.0776565294661689</v>
       </c>
       <c r="M48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776096914243875)</f>
-        <v>0.0776096914243875</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
+        <v>0.0776565294661689</v>
       </c>
       <c r="N48" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6552.91332717418)</f>
@@ -5088,8 +5026,8 @@
         <v>1</v>
       </c>
       <c r="P48" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),145)</f>
-        <v>145</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146)</f>
+        <v>146</v>
       </c>
       <c r="Q48" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -5129,52 +5067,52 @@
         <v>119</v>
       </c>
       <c r="B49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824893752171108)</f>
-        <v>0.0824893752171108</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
+        <v>0.0824962815446097</v>
       </c>
       <c r="C49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0926168726117811)</f>
-        <v>0.0926168726117811</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0925409030092935)</f>
+        <v>0.0925409030092935</v>
       </c>
       <c r="D49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824893752171108)</f>
-        <v>0.0824893752171108</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
+        <v>0.0824962815446097</v>
       </c>
       <c r="E49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824893752171108)</f>
-        <v>0.0824893752171108</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
+        <v>0.0824962815446097</v>
       </c>
       <c r="F49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824893752171108)</f>
-        <v>0.0824893752171108</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
+        <v>0.0824962815446097</v>
       </c>
       <c r="G49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824893752171108)</f>
-        <v>0.0824893752171108</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
+        <v>0.0824962815446097</v>
       </c>
       <c r="H49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824893752171108)</f>
-        <v>0.0824893752171108</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
+        <v>0.0824962815446097</v>
       </c>
       <c r="I49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824893752171108)</f>
-        <v>0.0824893752171108</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
+        <v>0.0824962815446097</v>
       </c>
       <c r="J49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824893752171108)</f>
-        <v>0.0824893752171108</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
+        <v>0.0824962815446097</v>
       </c>
       <c r="K49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824893752171108)</f>
-        <v>0.0824893752171108</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
+        <v>0.0824962815446097</v>
       </c>
       <c r="L49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824893752171108)</f>
-        <v>0.0824893752171108</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
+        <v>0.0824962815446097</v>
       </c>
       <c r="M49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824893752171108)</f>
-        <v>0.0824893752171108</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
+        <v>0.0824962815446097</v>
       </c>
       <c r="N49" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2239.47576029921)</f>
@@ -5185,8 +5123,8 @@
         <v>1</v>
       </c>
       <c r="P49" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35)</f>
-        <v>35</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33)</f>
+        <v>33</v>
       </c>
       <c r="Q49" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -5379,8 +5317,8 @@
         <v>1</v>
       </c>
       <c r="P51" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3)</f>
-        <v>3</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2)</f>
+        <v>2</v>
       </c>
       <c r="Q51" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -5420,52 +5358,52 @@
         <v>122</v>
       </c>
       <c r="B52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081905278187681)</f>
-        <v>0.081905278187681</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
+        <v>0.0819169643322097</v>
       </c>
       <c r="C52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990419399355086)</f>
-        <v>0.0990419399355086</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0989133923456932)</f>
+        <v>0.0989133923456932</v>
       </c>
       <c r="D52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081905278187681)</f>
-        <v>0.081905278187681</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
+        <v>0.0819169643322097</v>
       </c>
       <c r="E52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081905278187681)</f>
-        <v>0.081905278187681</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
+        <v>0.0819169643322097</v>
       </c>
       <c r="F52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081905278187681)</f>
-        <v>0.081905278187681</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
+        <v>0.0819169643322097</v>
       </c>
       <c r="G52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081905278187681)</f>
-        <v>0.081905278187681</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
+        <v>0.0819169643322097</v>
       </c>
       <c r="H52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081905278187681)</f>
-        <v>0.081905278187681</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
+        <v>0.0819169643322097</v>
       </c>
       <c r="I52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081905278187681)</f>
-        <v>0.081905278187681</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
+        <v>0.0819169643322097</v>
       </c>
       <c r="J52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081905278187681)</f>
-        <v>0.081905278187681</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
+        <v>0.0819169643322097</v>
       </c>
       <c r="K52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081905278187681)</f>
-        <v>0.081905278187681</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
+        <v>0.0819169643322097</v>
       </c>
       <c r="L52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081905278187681)</f>
-        <v>0.081905278187681</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
+        <v>0.0819169643322097</v>
       </c>
       <c r="M52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081905278187681)</f>
-        <v>0.081905278187681</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
+        <v>0.0819169643322097</v>
       </c>
       <c r="N52" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),300.325058646191)</f>
@@ -5517,52 +5455,52 @@
         <v>123</v>
       </c>
       <c r="B53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819058949205491)</f>
-        <v>0.0819058949205491</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
+        <v>0.0819175760181933</v>
       </c>
       <c r="C53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990351558739593)</f>
-        <v>0.0990351558739593</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0989066637998739)</f>
+        <v>0.0989066637998739</v>
       </c>
       <c r="D53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819058949205491)</f>
-        <v>0.0819058949205491</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
+        <v>0.0819175760181933</v>
       </c>
       <c r="E53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819058949205491)</f>
-        <v>0.0819058949205491</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
+        <v>0.0819175760181933</v>
       </c>
       <c r="F53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819058949205491)</f>
-        <v>0.0819058949205491</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
+        <v>0.0819175760181933</v>
       </c>
       <c r="G53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819058949205491)</f>
-        <v>0.0819058949205491</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
+        <v>0.0819175760181933</v>
       </c>
       <c r="H53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819058949205491)</f>
-        <v>0.0819058949205491</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
+        <v>0.0819175760181933</v>
       </c>
       <c r="I53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819058949205491)</f>
-        <v>0.0819058949205491</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
+        <v>0.0819175760181933</v>
       </c>
       <c r="J53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819058949205491)</f>
-        <v>0.0819058949205491</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
+        <v>0.0819175760181933</v>
       </c>
       <c r="K53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819058949205491)</f>
-        <v>0.0819058949205491</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
+        <v>0.0819175760181933</v>
       </c>
       <c r="L53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819058949205491)</f>
-        <v>0.0819058949205491</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
+        <v>0.0819175760181933</v>
       </c>
       <c r="M53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819058949205491)</f>
-        <v>0.0819058949205491</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
+        <v>0.0819175760181933</v>
       </c>
       <c r="N53" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),660.71512861809)</f>
@@ -5614,52 +5552,52 @@
         <v>124</v>
       </c>
       <c r="B54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063723187725)</f>
-        <v>0.0819063723187725</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
+        <v>0.0819180495097435</v>
       </c>
       <c r="C54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990299044935024)</f>
-        <v>0.0990299044935024</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0989014553928212)</f>
+        <v>0.0989014553928212</v>
       </c>
       <c r="D54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063723187725)</f>
-        <v>0.0819063723187725</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
+        <v>0.0819180495097435</v>
       </c>
       <c r="E54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063723187725)</f>
-        <v>0.0819063723187725</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
+        <v>0.0819180495097435</v>
       </c>
       <c r="F54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063723187725)</f>
-        <v>0.0819063723187725</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
+        <v>0.0819180495097435</v>
       </c>
       <c r="G54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063723187725)</f>
-        <v>0.0819063723187725</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
+        <v>0.0819180495097435</v>
       </c>
       <c r="H54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063723187725)</f>
-        <v>0.0819063723187725</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
+        <v>0.0819180495097435</v>
       </c>
       <c r="I54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063723187725)</f>
-        <v>0.0819063723187725</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
+        <v>0.0819180495097435</v>
       </c>
       <c r="J54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063723187725)</f>
-        <v>0.0819063723187725</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
+        <v>0.0819180495097435</v>
       </c>
       <c r="K54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063723187725)</f>
-        <v>0.0819063723187725</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
+        <v>0.0819180495097435</v>
       </c>
       <c r="L54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063723187725)</f>
-        <v>0.0819063723187725</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
+        <v>0.0819180495097435</v>
       </c>
       <c r="M54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063723187725)</f>
-        <v>0.0819063723187725</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
+        <v>0.0819180495097435</v>
       </c>
       <c r="N54" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.156028161701)</f>
@@ -5711,52 +5649,52 @@
         <v>125</v>
       </c>
       <c r="B55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063113844052)</f>
-        <v>0.0819063113844052</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
+        <v>0.0819179890740179</v>
       </c>
       <c r="C55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990305747715433)</f>
-        <v>0.0990305747715433</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0989021201858035)</f>
+        <v>0.0989021201858035</v>
       </c>
       <c r="D55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063113844052)</f>
-        <v>0.0819063113844052</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
+        <v>0.0819179890740179</v>
       </c>
       <c r="E55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063113844052)</f>
-        <v>0.0819063113844052</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
+        <v>0.0819179890740179</v>
       </c>
       <c r="F55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063113844052)</f>
-        <v>0.0819063113844052</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
+        <v>0.0819179890740179</v>
       </c>
       <c r="G55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063113844052)</f>
-        <v>0.0819063113844052</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
+        <v>0.0819179890740179</v>
       </c>
       <c r="H55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063113844052)</f>
-        <v>0.0819063113844052</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
+        <v>0.0819179890740179</v>
       </c>
       <c r="I55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063113844052)</f>
-        <v>0.0819063113844052</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
+        <v>0.0819179890740179</v>
       </c>
       <c r="J55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063113844052)</f>
-        <v>0.0819063113844052</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
+        <v>0.0819179890740179</v>
       </c>
       <c r="K55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063113844052)</f>
-        <v>0.0819063113844052</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
+        <v>0.0819179890740179</v>
       </c>
       <c r="L55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063113844052)</f>
-        <v>0.0819063113844052</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
+        <v>0.0819179890740179</v>
       </c>
       <c r="M55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819063113844052)</f>
-        <v>0.0819063113844052</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
+        <v>0.0819179890740179</v>
       </c>
       <c r="N55" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),96.1040185823099)</f>
@@ -5808,52 +5746,52 @@
         <v>126</v>
       </c>
       <c r="B56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0399853669657492)</f>
-        <v>0.0399853669657492</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1015098507676)</f>
+        <v>0.1015098507676</v>
       </c>
       <c r="C56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111858494843661)</f>
-        <v>0.111858494843661</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0996205288380497)</f>
+        <v>0.0996205288380497</v>
       </c>
       <c r="D56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0898581204576652)</f>
-        <v>0.0898581204576652</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
+        <v>0.0774844188474166</v>
       </c>
       <c r="E56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0902438258482885)</f>
-        <v>0.0902438258482885</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
+        <v>0.0774844188474166</v>
       </c>
       <c r="F56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0902639607404363)</f>
-        <v>0.0902639607404363</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
+        <v>0.0774844188474166</v>
       </c>
       <c r="G56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0900805935578995)</f>
-        <v>0.0900805935578995</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
+        <v>0.0774844188474166</v>
       </c>
       <c r="H56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0906573476506073)</f>
-        <v>0.0906573476506073</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
+        <v>0.0774844188474166</v>
       </c>
       <c r="I56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0902232836028314)</f>
-        <v>0.0902232836028314</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
+        <v>0.0774844188474166</v>
       </c>
       <c r="J56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0902909624455131)</f>
-        <v>0.0902909624455131</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
+        <v>0.0774844188474166</v>
       </c>
       <c r="K56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0900672090920209)</f>
-        <v>0.0900672090920209</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
+        <v>0.0774844188474166</v>
       </c>
       <c r="L56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0891036439354216)</f>
-        <v>0.0891036439354216</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
+        <v>0.0774844188474166</v>
       </c>
       <c r="M56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0373671908599057)</f>
-        <v>0.0373671908599057</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1015098507676)</f>
+        <v>0.1015098507676</v>
       </c>
       <c r="N56" s="7" t="n">
         <f aca="false">SUM(N39:N55)</f>
@@ -5861,7 +5799,7 @@
       </c>
       <c r="P56" s="7" t="n">
         <f aca="false">SUM(P39:P55)</f>
-        <v>1004</v>
+        <v>985</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5869,32 +5807,32 @@
         <v>127</v>
       </c>
       <c r="Q57" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""sobrestock_sustitutos!B18:H18"")"),25)</f>
-        <v>25</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""sobrestock_sustitutos!B18:H18"")"),9)</f>
+        <v>9</v>
       </c>
       <c r="R57" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14)</f>
-        <v>14</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15)</f>
+        <v>15</v>
       </c>
       <c r="S57" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18)</f>
-        <v>18</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12)</f>
+        <v>12</v>
       </c>
       <c r="T57" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20)</f>
-        <v>20</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11)</f>
+        <v>11</v>
       </c>
       <c r="U57" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45)</f>
-        <v>45</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10)</f>
+        <v>10</v>
       </c>
       <c r="V57" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35)</f>
-        <v>35</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),61)</f>
+        <v>61</v>
       </c>
       <c r="W57" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16)</f>
-        <v>16</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5961,52 +5899,52 @@
         <v>101</v>
       </c>
       <c r="B62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""parametros_recargas!E35:P41"")"),0.00735238492719494)</f>
-        <v>0.00735238492719494</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""parametros_recargas!E35:P41"")"),0.12)</f>
+        <v>0.12</v>
       </c>
       <c r="C62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0981059093482913)</f>
-        <v>0.0981059093482913</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="D62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0986889802872471)</f>
-        <v>0.0986889802872471</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="E62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993953583138234)</f>
-        <v>0.0993953583138234</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="F62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994322332077878)</f>
-        <v>0.0994322332077878</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="G62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990964158931013)</f>
-        <v>0.0990964158931013</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="H62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100152679112986)</f>
-        <v>0.100152679112986</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="I62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993577373959928)</f>
-        <v>0.0993577373959928</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="J62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994816839326416)</f>
-        <v>0.0994816839326416</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="K62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0990719036803504)</f>
-        <v>0.0990719036803504</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="L62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0973072375119662)</f>
-        <v>0.0973072375119662</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
+        <v>0.076</v>
       </c>
       <c r="M62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.00255747638861682)</f>
-        <v>0.00255747638861682</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.12)</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6067,52 +6005,52 @@
         <v>103</v>
       </c>
       <c r="B64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
+        <v>0.0269650818628408</v>
       </c>
       <c r="C64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7085)</f>
-        <v>0.7085</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.703384099508751)</f>
+        <v>0.703384099508751</v>
       </c>
       <c r="D64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
+        <v>0.0269650818628408</v>
       </c>
       <c r="E64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
+        <v>0.0269650818628408</v>
       </c>
       <c r="F64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
+        <v>0.0269650818628408</v>
       </c>
       <c r="G64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
+        <v>0.0269650818628408</v>
       </c>
       <c r="H64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
+        <v>0.0269650818628408</v>
       </c>
       <c r="I64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
+        <v>0.0269650818628408</v>
       </c>
       <c r="J64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
+        <v>0.0269650818628408</v>
       </c>
       <c r="K64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
+        <v>0.0269650818628408</v>
       </c>
       <c r="L64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
+        <v>0.0269650818628408</v>
       </c>
       <c r="M64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0265)</f>
-        <v>0.0265</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
+        <v>0.0269650818628408</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6363,101 +6301,57 @@
         <v>133</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>134</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="6" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="B5" s="24" t="n">
         <f aca="false">MATCH(MAX(Importados!$B$22:$M$22),Importados!$B$22:$M$22,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="24" t="n">
         <f aca="false">MATCH(MAX(Importados!$B$56:$M$56),Importados!$B$56:$M$56,0)</f>
-        <v>2</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="25" t="str">
         <f aca="false">INDEX(Importados!$B$4:$M$4,B5)</f>
-        <v>Feb</v>
+        <v>Ene</v>
       </c>
       <c r="C6" s="25" t="str">
         <f aca="false">INDEX(Importados!$B$38:$M$38,C5)</f>
-        <v>Feb</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
+        <v>Ene</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B7" s="26" t="n">
         <f aca="false">INDEX(Importados!$B$22:$M$22,B5)</f>
-        <v>0.108520970470319</v>
+        <v>0.101848800284409</v>
       </c>
       <c r="C7" s="26" t="n">
         <f aca="false">INDEX(Importados!$B$56:$M$56,C5)</f>
-        <v>0.111858494843661</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>0.1015098507676</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>128</v>
       </c>
@@ -6469,20 +6363,8 @@
         <f aca="false">Importados!$B$58</f>
         <v>20</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>129</v>
       </c>
@@ -6494,78 +6376,68 @@
         <f aca="false">Importados!$B$59</f>
         <v>7.5</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="E11" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>144</v>
-      </c>
       <c r="F11" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
@@ -6578,14 +6450,14 @@
         <v>72</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E13" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="29" t="n">
         <f aca="false">Importados!$N$5*INDEX(Importados!$B$5:$M$5,$B$5)/$B$8</f>
-        <v>533.758783253965</v>
+        <v>652.692236720059</v>
       </c>
       <c r="G13" s="29" t="n">
         <f aca="false">F13*Importados!$O$5</f>
@@ -6593,11 +6465,11 @@
       </c>
       <c r="H13" s="23" t="n">
         <f aca="false">F13/$C13</f>
-        <v>7.41331643408285</v>
+        <v>9.06516995444526</v>
       </c>
       <c r="I13" s="29" t="n">
         <f aca="false">Importados!$N$39*INDEX(Importados!$B$39:$M$39,$C$5)/$C$8</f>
-        <v>277.455740084688</v>
+        <v>339.292554289086</v>
       </c>
       <c r="J13" s="29" t="n">
         <f aca="false">I13*Importados!$O$39</f>
@@ -6605,10 +6477,10 @@
       </c>
       <c r="K13" s="23" t="n">
         <f aca="false">I13/$C13</f>
-        <v>3.85355194562067</v>
+        <v>4.71239658734841</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6622,37 +6494,37 @@
         <v>30</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E14" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="29" t="n">
         <f aca="false">Importados!$N$6*INDEX(Importados!$B$6:$M$6,$B$5)/$B$8</f>
-        <v>61.9030955190453</v>
+        <v>36.3790897941657</v>
       </c>
       <c r="G14" s="29" t="n">
         <f aca="false">F14*Importados!$O$6</f>
-        <v>61.9030955190453</v>
+        <v>36.3790897941657</v>
       </c>
       <c r="H14" s="23" t="n">
         <f aca="false">F14/$C14</f>
-        <v>2.06343651730151</v>
+        <v>1.21263632647219</v>
       </c>
       <c r="I14" s="29" t="n">
         <f aca="false">Importados!$N$40*INDEX(Importados!$B$40:$M$40,$C$5)/$C$8</f>
-        <v>34.2027821755785</v>
+        <v>18.6772059581256</v>
       </c>
       <c r="J14" s="29" t="n">
         <f aca="false">I14*Importados!$O$40</f>
-        <v>34.2027821755785</v>
+        <v>18.6772059581256</v>
       </c>
       <c r="K14" s="23" t="n">
         <f aca="false">I14/$C14</f>
-        <v>1.14009273918595</v>
+        <v>0.622573531937519</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6666,37 +6538,37 @@
         <v>24</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E15" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="29" t="n">
         <f aca="false">Importados!$N$7*INDEX(Importados!$B$7:$M$7,$B$5)/$B$8</f>
-        <v>326.226563536772</v>
+        <v>232.796340138188</v>
       </c>
       <c r="G15" s="29" t="n">
         <f aca="false">F15*Importados!$O$7</f>
-        <v>326.226563536772</v>
+        <v>232.796340138188</v>
       </c>
       <c r="H15" s="23" t="n">
         <f aca="false">F15/$C15</f>
-        <v>13.5927734806988</v>
+        <v>9.69984750575784</v>
       </c>
       <c r="I15" s="29" t="n">
         <f aca="false">Importados!$N$41*INDEX(Importados!$B$41:$M$41,$C$5)/$C$8</f>
-        <v>179.420945412987</v>
+        <v>120.070942594702</v>
       </c>
       <c r="J15" s="29" t="n">
         <f aca="false">I15*Importados!$O$41</f>
-        <v>179.420945412987</v>
+        <v>120.070942594702</v>
       </c>
       <c r="K15" s="23" t="n">
         <f aca="false">I15/$C15</f>
-        <v>7.47587272554111</v>
+        <v>5.00295594144594</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6710,37 +6582,37 @@
         <v>16</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E16" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="29" t="n">
         <f aca="false">Importados!$N$8*INDEX(Importados!$B$8:$M$8,$B$5)/$B$8</f>
-        <v>23.8129242382162</v>
+        <v>12.9711603110206</v>
       </c>
       <c r="G16" s="29" t="n">
         <f aca="false">F16*Importados!$O$8</f>
-        <v>23.8129242382162</v>
+        <v>12.9711603110206</v>
       </c>
       <c r="H16" s="23" t="n">
         <f aca="false">F16/$C16</f>
-        <v>1.48830776488851</v>
+        <v>0.81069751943879</v>
       </c>
       <c r="I16" s="29" t="n">
         <f aca="false">Importados!$N$42*INDEX(Importados!$B$42:$M$42,$C$5)/$C$8</f>
-        <v>13.1581103117659</v>
+        <v>6.65083763296167</v>
       </c>
       <c r="J16" s="29" t="n">
         <f aca="false">I16*Importados!$O$42</f>
-        <v>13.1581103117659</v>
+        <v>6.65083763296167</v>
       </c>
       <c r="K16" s="23" t="n">
         <f aca="false">I16/$C16</f>
-        <v>0.822381894485371</v>
+        <v>0.415677352060105</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6754,37 +6626,37 @@
         <v>16</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E17" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="29" t="n">
         <f aca="false">Importados!$N$9*INDEX(Importados!$B$9:$M$9,$B$5)/$B$8</f>
-        <v>27.9194395973236</v>
+        <v>18.8029804281169</v>
       </c>
       <c r="G17" s="29" t="n">
         <f aca="false">F17*Importados!$O$9</f>
-        <v>27.9194395973236</v>
+        <v>18.8029804281169</v>
       </c>
       <c r="H17" s="23" t="n">
         <f aca="false">F17/$C17</f>
-        <v>1.74496497483273</v>
+        <v>1.17518627675731</v>
       </c>
       <c r="I17" s="29" t="n">
         <f aca="false">Importados!$N$43*INDEX(Importados!$B$43:$M$43,$C$5)/$C$8</f>
-        <v>15.4860825908144</v>
+        <v>9.6681132372588</v>
       </c>
       <c r="J17" s="29" t="n">
         <f aca="false">I17*Importados!$O$43</f>
-        <v>15.4860825908144</v>
+        <v>9.6681132372588</v>
       </c>
       <c r="K17" s="23" t="n">
         <f aca="false">I17/$C17</f>
-        <v>0.967880161925902</v>
+        <v>0.604257077328675</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6798,7 +6670,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E18" s="22" t="n">
         <v>0</v>
@@ -6828,7 +6700,7 @@
         <v>0.120431924155399</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6842,7 +6714,7 @@
         <v>2</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E19" s="22" t="n">
         <v>1</v>
@@ -6872,7 +6744,7 @@
         <v>0.5022225695944</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6886,7 +6758,7 @@
         <v>24</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E20" s="22" t="n">
         <v>0</v>
@@ -6916,7 +6788,7 @@
         <v>0.0241938117976814</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6927,40 +6799,40 @@
         <v>8.25</v>
       </c>
       <c r="C21" s="22" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E21" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="29" t="n">
         <f aca="false">Importados!$N$13*INDEX(Importados!$B$13:$M$13,$B$5)/$B$8</f>
-        <v>17.8757728248945</v>
+        <v>8.9191989732046</v>
       </c>
       <c r="G21" s="29" t="n">
         <f aca="false">F21*Importados!$O$13</f>
-        <v>17.8757728248945</v>
+        <v>8.9191989732046</v>
       </c>
       <c r="H21" s="23" t="n">
         <f aca="false">F21/$C21</f>
-        <v>0.893788641244724</v>
+        <v>0.557449935825287</v>
       </c>
       <c r="I21" s="29" t="n">
         <f aca="false">Importados!$N$47*INDEX(Importados!$B$47:$M$47,$C$5)/$C$8</f>
-        <v>10.0074849817126</v>
+        <v>4.55414466197892</v>
       </c>
       <c r="J21" s="29" t="n">
         <f aca="false">I21*Importados!$O$47</f>
-        <v>10.0074849817126</v>
+        <v>4.55414466197892</v>
       </c>
       <c r="K21" s="23" t="n">
         <f aca="false">I21/$C21</f>
-        <v>0.500374249085631</v>
+        <v>0.284634041373682</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6974,37 +6846,37 @@
         <v>30</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E22" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="29" t="n">
         <f aca="false">Importados!$N$14*INDEX(Importados!$B$14:$M$14,$B$5)/$B$8</f>
-        <v>86.2388099115904</v>
+        <v>49.625920044755</v>
       </c>
       <c r="G22" s="29" t="n">
         <f aca="false">F22*Importados!$O$14</f>
-        <v>86.2388099115904</v>
+        <v>49.625920044755</v>
       </c>
       <c r="H22" s="23" t="n">
         <f aca="false">F22/$C22</f>
-        <v>2.87462699705301</v>
+        <v>1.65419733482517</v>
       </c>
       <c r="I22" s="29" t="n">
         <f aca="false">Importados!$N$48*INDEX(Importados!$B$48:$M$48,$C$5)/$C$8</f>
-        <v>47.9323966696994</v>
+        <v>25.4438253440476</v>
       </c>
       <c r="J22" s="29" t="n">
         <f aca="false">I22*Importados!$O$48</f>
-        <v>47.9323966696994</v>
+        <v>25.4438253440476</v>
       </c>
       <c r="K22" s="23" t="n">
         <f aca="false">I22/$C22</f>
-        <v>1.59774655565665</v>
+        <v>0.848127511468254</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7015,40 +6887,40 @@
         <v>20</v>
       </c>
       <c r="C23" s="22" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E23" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="29" t="n">
         <f aca="false">Importados!$N$15*INDEX(Importados!$B$15:$M$15,$B$5)/$B$8</f>
-        <v>19.5382324483628</v>
+        <v>17.8150080869683</v>
       </c>
       <c r="G23" s="29" t="n">
         <f aca="false">F23*Importados!$O$15</f>
-        <v>19.5382324483628</v>
+        <v>17.8150080869683</v>
       </c>
       <c r="H23" s="23" t="n">
         <f aca="false">F23/$C23</f>
-        <v>0.97691162241814</v>
+        <v>1.11343800543552</v>
       </c>
       <c r="I23" s="29" t="n">
         <f aca="false">Importados!$N$49*INDEX(Importados!$B$49:$M$49,$C$5)/$C$8</f>
-        <v>10.3706620604402</v>
+        <v>9.23742114169862</v>
       </c>
       <c r="J23" s="29" t="n">
         <f aca="false">I23*Importados!$O$49</f>
-        <v>10.3706620604402</v>
+        <v>9.23742114169862</v>
       </c>
       <c r="K23" s="23" t="n">
         <f aca="false">I23/$C23</f>
-        <v>0.518533103022009</v>
+        <v>0.577338821356164</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7062,7 +6934,7 @@
         <v>24</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E24" s="22" t="n">
         <v>0</v>
@@ -7092,7 +6964,7 @@
         <v>0.0636492808294427</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7106,7 +6978,7 @@
         <v>16</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E25" s="22" t="n">
         <v>0</v>
@@ -7136,7 +7008,7 @@
         <v>0.0327784041775312</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7147,40 +7019,40 @@
         <v>53</v>
       </c>
       <c r="C26" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E26" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="29" t="n">
         <f aca="false">Importados!$N$18*INDEX(Importados!$B$18:$M$18,$B$5)/$B$8</f>
-        <v>2.75918021986926</v>
+        <v>2.37711623910776</v>
       </c>
       <c r="G26" s="29" t="n">
         <f aca="false">F26*Importados!$O$18</f>
-        <v>2.75918021986926</v>
+        <v>2.37711623910776</v>
       </c>
       <c r="H26" s="23" t="n">
         <f aca="false">F26/$C26</f>
-        <v>0.91972673995642</v>
+        <v>1.18855811955388</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">Importados!$N$52*INDEX(Importados!$B$52:$M$52,$C$5)/$C$8</f>
-        <v>1.48723882097821</v>
+        <v>1.23008585585944</v>
       </c>
       <c r="J26" s="29" t="n">
         <f aca="false">I26*Importados!$O$52</f>
-        <v>1.48723882097821</v>
+        <v>1.23008585585944</v>
       </c>
       <c r="K26" s="23" t="n">
         <f aca="false">I26/$C26</f>
-        <v>0.495746273659402</v>
+        <v>0.61504292792972</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7194,37 +7066,37 @@
         <v>2</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E27" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="29" t="n">
         <f aca="false">Importados!$N$19*INDEX(Importados!$B$19:$M$19,$B$5)/$B$8</f>
-        <v>6.07030174969413</v>
+        <v>5.22964666029617</v>
       </c>
       <c r="G27" s="29" t="n">
         <f aca="false">F27*Importados!$O$19</f>
-        <v>6.07030174969413</v>
+        <v>5.22964666029617</v>
       </c>
       <c r="H27" s="23" t="n">
         <f aca="false">F27/$C27</f>
-        <v>3.03515087484707</v>
+        <v>2.61482333014809</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">Importados!$N$53*INDEX(Importados!$B$53:$M$53,$C$5)/$C$8</f>
-        <v>3.27170128754878</v>
+        <v>2.70620908874714</v>
       </c>
       <c r="J27" s="29" t="n">
         <f aca="false">I27*Importados!$O$53</f>
-        <v>3.27170128754878</v>
+        <v>2.70620908874714</v>
       </c>
       <c r="K27" s="23" t="n">
         <f aca="false">I27/$C27</f>
-        <v>1.63585064377439</v>
+        <v>1.35310454437357</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7238,37 +7110,37 @@
         <v>2</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E28" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="29" t="n">
         <f aca="false">Importados!$N$20*INDEX(Importados!$B$20:$M$20,$B$5)/$B$8</f>
-        <v>1.32437866294963</v>
+        <v>1.14101819180856</v>
       </c>
       <c r="G28" s="29" t="n">
         <f aca="false">F28*Importados!$O$20</f>
-        <v>1.32437866294963</v>
+        <v>1.14101819180856</v>
       </c>
       <c r="H28" s="23" t="n">
         <f aca="false">F28/$C28</f>
-        <v>0.662189331474814</v>
+        <v>0.57050909590428</v>
       </c>
       <c r="I28" s="29" t="n">
         <f aca="false">Importados!$N$54*INDEX(Importados!$B$54:$M$54,$C$5)/$C$8</f>
-        <v>0.713787885050795</v>
+        <v>0.59044903260391</v>
       </c>
       <c r="J28" s="29" t="n">
         <f aca="false">I28*Importados!$O$54</f>
-        <v>0.713787885050795</v>
+        <v>0.59044903260391</v>
       </c>
       <c r="K28" s="23" t="n">
         <f aca="false">I28/$C28</f>
-        <v>0.356893942525397</v>
+        <v>0.295224516301955</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7282,101 +7154,96 @@
         <v>1</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E29" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="29" t="n">
         <f aca="false">Importados!$N$21*INDEX(Importados!$B$21:$M$21,$B$5)/$B$8</f>
-        <v>0.883036837969182</v>
+        <v>0.760668657682474</v>
       </c>
       <c r="G29" s="29" t="n">
         <f aca="false">F29*Importados!$O$21</f>
-        <v>0.883036837969182</v>
+        <v>0.760668657682474</v>
       </c>
       <c r="H29" s="23" t="n">
         <f aca="false">F29/$C29</f>
-        <v>0.883036837969182</v>
+        <v>0.760668657682474</v>
       </c>
       <c r="I29" s="29" t="n">
         <f aca="false">Importados!$N$55*INDEX(Importados!$B$55:$M$55,$C$5)/$C$8</f>
-        <v>0.475861809903061</v>
+        <v>0.393632397209744</v>
       </c>
       <c r="J29" s="29" t="n">
         <f aca="false">I29*Importados!$O$55</f>
-        <v>0.475861809903061</v>
+        <v>0.393632397209744</v>
       </c>
       <c r="K29" s="23" t="n">
         <f aca="false">I29/$C29</f>
-        <v>0.475861809903061</v>
+        <v>0.393632397209744</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F30" s="30" t="n">
         <f aca="false">SUM(F13:F29)</f>
-        <v>1119.01482761851</v>
+        <v>1050.21469306323</v>
       </c>
       <c r="G30" s="30" t="n">
         <f aca="false">SUM(G13:G29)</f>
-        <v>585.256044364544</v>
+        <v>397.522456343171</v>
       </c>
       <c r="H30" s="30" t="n">
         <f aca="false">SUM(H13:H29)</f>
-        <v>37.9781712559777</v>
+        <v>31.853123101456</v>
       </c>
       <c r="I30" s="30" t="n">
         <f aca="false">SUM(I13:I29)</f>
-        <v>599.546838706733</v>
+        <v>544.079465849846</v>
       </c>
       <c r="J30" s="30" t="n">
         <f aca="false">SUM(J13:J29)</f>
-        <v>322.091098622045</v>
+        <v>204.786911560761</v>
       </c>
       <c r="K30" s="30" t="n">
         <f aca="false">SUM(K13:K29)</f>
-        <v>20.58406203494</v>
+        <v>16.4682412406882</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F31" s="11" t="n">
         <f aca="false">SUMPRODUCT(F13:F29,$B$13:$B$29)/F30</f>
-        <v>6.65882736300077</v>
+        <v>5.61010110978076</v>
       </c>
       <c r="I31" s="11" t="n">
         <f aca="false">SUMPRODUCT(I13:I29,$B$13:$B$29)/I30</f>
-        <v>6.75381882934406</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>157</v>
+        <v>5.59545821055644</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
@@ -7384,37 +7251,37 @@
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
@@ -7429,38 +7296,38 @@
       </c>
       <c r="C37" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$28:$M$28,$B$5)*SUMPRODUCT(Importados!$N$5:$N$21,Importados!$Q$5:$Q$21/Importados!$X$5:$X$21)/$B$8</f>
-        <v>551.530199225957</v>
+        <v>674.614040548288</v>
       </c>
       <c r="D37" s="22" t="n">
         <f aca="false">Importados!Q$23</f>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E37" s="28" t="n">
         <f aca="false">2*C37/D37</f>
-        <v>44.1224159380766</v>
+        <v>149.914231232953</v>
       </c>
       <c r="F37" s="28" t="n">
-        <f aca="false">E37*(Supuestos!$B$16+Supuestos!$B$17)/60+2*C37*$B37/60</f>
-        <v>34.9302459509773</v>
+        <f aca="false">E37*(Supuestos!$B$17+Supuestos!$B$18)/60+2*C37*$B37/60</f>
+        <v>98.693535561694</v>
       </c>
       <c r="G37" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$62:$M$62,$C$5)*SUMPRODUCT(Importados!$N$39:$N$55,Importados!$Q$39:$Q$55/Importados!$X$39:$X$55)/$C$8</f>
-        <v>287.122906270335</v>
+        <v>351.199524894269</v>
       </c>
       <c r="H37" s="22" t="n">
         <f aca="false">Importados!Q$57</f>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="I37" s="28" t="n">
         <f aca="false">2*G37/H37</f>
-        <v>22.9698325016268</v>
+        <v>78.0443388653931</v>
       </c>
       <c r="J37" s="28" t="n">
-        <f aca="false">I37*(Supuestos!$B$16+Supuestos!$B$17)/60+2*G37*$B37/60</f>
-        <v>18.1844507304545</v>
+        <f aca="false">I37*(Supuestos!$B$17+Supuestos!$B$18)/60+2*G37*$B37/60</f>
+        <v>51.3791897530505</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7476,15 +7343,15 @@
       </c>
       <c r="D38" s="22" t="n">
         <f aca="false">Importados!R$23</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E38" s="28" t="n">
         <f aca="false">2*C38/D38</f>
-        <v>38.6347225371069</v>
+        <v>36.0590743679664</v>
       </c>
       <c r="F38" s="28" t="n">
-        <f aca="false">E38*(Supuestos!$B$16+Supuestos!$B$17)/60+2*C38*$B38/60</f>
-        <v>36.0590743679664</v>
+        <f aca="false">E38*(Supuestos!$B$17+Supuestos!$B$18)/60+2*C38*$B38/60</f>
+        <v>34.5566129359678</v>
       </c>
       <c r="G38" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$63:$M$63,$C$5)*SUMPRODUCT(Importados!$N$39:$N$55,Importados!$R$39:$R$55/Importados!$X$39:$X$55)/$C$8</f>
@@ -7492,18 +7359,18 @@
       </c>
       <c r="H38" s="22" t="n">
         <f aca="false">Importados!R$57</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I38" s="28" t="n">
         <f aca="false">2*G38/H38</f>
-        <v>19.9971195732696</v>
+        <v>18.663978268385</v>
       </c>
       <c r="J38" s="28" t="n">
-        <f aca="false">I38*(Supuestos!$B$16+Supuestos!$B$17)/60+2*G38*$B38/60</f>
-        <v>18.663978268385</v>
+        <f aca="false">I38*(Supuestos!$B$17+Supuestos!$B$18)/60+2*G38*$B38/60</f>
+        <v>17.8863125072023</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7515,38 +7382,38 @@
       </c>
       <c r="C39" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$30:$M$30,$B$5)*SUMPRODUCT(Importados!$N$5:$N$21,Importados!$S$5:$S$21/Importados!$X$5:$X$21)/$B$8</f>
-        <v>200.224580585876</v>
+        <v>8.34060470826765</v>
       </c>
       <c r="D39" s="22" t="n">
         <f aca="false">Importados!S$23</f>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E39" s="28" t="n">
         <f aca="false">2*C39/D39</f>
-        <v>22.2471756206529</v>
+        <v>1.39010078471128</v>
       </c>
       <c r="F39" s="28" t="n">
-        <f aca="false">E39*(Supuestos!$B$16+Supuestos!$B$17)/60+2*C39*$B39/60</f>
-        <v>22.9887481413414</v>
+        <f aca="false">E39*(Supuestos!$B$17+Supuestos!$B$18)/60+2*C39*$B39/60</f>
+        <v>1.22792235982829</v>
       </c>
       <c r="G39" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$64:$M$64,$C$5)*SUMPRODUCT(Importados!$N$39:$N$55,Importados!$S$39:$S$55/Importados!$X$39:$X$55)/$C$8</f>
-        <v>124.273776310191</v>
+        <v>4.72978482937001</v>
       </c>
       <c r="H39" s="22" t="n">
         <f aca="false">Importados!S$57</f>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I39" s="28" t="n">
         <f aca="false">2*G39/H39</f>
-        <v>13.808197367799</v>
+        <v>0.788297471561669</v>
       </c>
       <c r="J39" s="28" t="n">
-        <f aca="false">I39*(Supuestos!$B$16+Supuestos!$B$17)/60+2*G39*$B39/60</f>
-        <v>14.2684706133922</v>
+        <f aca="false">I39*(Supuestos!$B$17+Supuestos!$B$18)/60+2*G39*$B39/60</f>
+        <v>0.696329433212807</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7562,15 +7429,15 @@
       </c>
       <c r="D40" s="22" t="n">
         <f aca="false">Importados!T$23</f>
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E40" s="28" t="n">
         <f aca="false">2*C40/D40</f>
-        <v>1.5933847507444</v>
+        <v>2.89706318317163</v>
       </c>
       <c r="F40" s="28" t="n">
-        <f aca="false">E40*(Supuestos!$B$16+Supuestos!$B$17)/60+2*C40*$B40/60</f>
-        <v>1.72616681330643</v>
+        <f aca="false">E40*(Supuestos!$B$17+Supuestos!$B$18)/60+2*C40*$B40/60</f>
+        <v>2.48664589888898</v>
       </c>
       <c r="G40" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$65:$M$65,$C$5)*SUMPRODUCT(Importados!$N$39:$N$55,Importados!$T$39:$T$55/Importados!$X$39:$X$55)/$C$8</f>
@@ -7578,18 +7445,18 @@
       </c>
       <c r="H40" s="22" t="n">
         <f aca="false">Importados!T$57</f>
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I40" s="28" t="n">
         <f aca="false">2*G40/H40</f>
-        <v>0.932221450894524</v>
+        <v>1.6949480925355</v>
       </c>
       <c r="J40" s="28" t="n">
-        <f aca="false">I40*(Supuestos!$B$16+Supuestos!$B$17)/60+2*G40*$B40/60</f>
-        <v>1.0099065718024</v>
+        <f aca="false">I40*(Supuestos!$B$17+Supuestos!$B$18)/60+2*G40*$B40/60</f>
+        <v>1.45483044609297</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7605,15 +7472,15 @@
       </c>
       <c r="D41" s="22" t="n">
         <f aca="false">Importados!U$23</f>
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E41" s="28" t="n">
         <f aca="false">2*C41/D41</f>
-        <v>2.39140487506909</v>
+        <v>10.7613219378109</v>
       </c>
       <c r="F41" s="28" t="n">
-        <f aca="false">E41*(Supuestos!$B$16+Supuestos!$B$17)/60+2*C41*$B41/60</f>
-        <v>4.08531666157637</v>
+        <f aca="false">E41*(Supuestos!$B$17+Supuestos!$B$18)/60+2*C41*$B41/60</f>
+        <v>8.9677682815091</v>
       </c>
       <c r="G41" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$66:$M$66,$C$5)*SUMPRODUCT(Importados!$N$39:$N$55,Importados!$U$39:$U$55/Importados!$X$39:$X$55)/$C$8</f>
@@ -7621,18 +7488,18 @@
       </c>
       <c r="H41" s="22" t="n">
         <f aca="false">Importados!U$57</f>
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="I41" s="28" t="n">
         <f aca="false">2*G41/H41</f>
-        <v>1.01724655958759</v>
+        <v>4.57760951814415</v>
       </c>
       <c r="J41" s="28" t="n">
-        <f aca="false">I41*(Supuestos!$B$16+Supuestos!$B$17)/60+2*G41*$B41/60</f>
-        <v>1.73779620596213</v>
+        <f aca="false">I41*(Supuestos!$B$17+Supuestos!$B$18)/60+2*G41*$B41/60</f>
+        <v>3.81467459845346</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7648,15 +7515,15 @@
       </c>
       <c r="D42" s="22" t="n">
         <f aca="false">Importados!V$23</f>
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E42" s="28" t="n">
         <f aca="false">2*C42/D42</f>
-        <v>1.35252048388112</v>
+        <v>0.776036343210476</v>
       </c>
       <c r="F42" s="28" t="n">
-        <f aca="false">E42*(Supuestos!$B$16+Supuestos!$B$17)/60+2*C42*$B42/60</f>
-        <v>1.97242570565996</v>
+        <f aca="false">E42*(Supuestos!$B$17+Supuestos!$B$18)/60+2*C42*$B42/60</f>
+        <v>1.63614329026875</v>
       </c>
       <c r="G42" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$67:$M$67,$C$5)*SUMPRODUCT(Importados!$N$39:$N$55,Importados!$V$39:$V$55/Importados!$X$39:$X$55)/$C$8</f>
@@ -7664,18 +7531,18 @@
       </c>
       <c r="H42" s="22" t="n">
         <f aca="false">Importados!V$57</f>
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="I42" s="28" t="n">
         <f aca="false">2*G42/H42</f>
-        <v>0.790294120713048</v>
+        <v>0.453447446310765</v>
       </c>
       <c r="J42" s="28" t="n">
-        <f aca="false">I42*(Supuestos!$B$16+Supuestos!$B$17)/60+2*G42*$B42/60</f>
-        <v>1.1525122593732</v>
+        <f aca="false">I42*(Supuestos!$B$17+Supuestos!$B$18)/60+2*G42*$B42/60</f>
+        <v>0.956018365971863</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7691,15 +7558,15 @@
       </c>
       <c r="D43" s="22" t="n">
         <f aca="false">Importados!W$23</f>
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E43" s="28" t="n">
         <f aca="false">2*C43/D43</f>
-        <v>0.42592804781363</v>
+        <v>1.13580812750301</v>
       </c>
       <c r="F43" s="28" t="n">
-        <f aca="false">E43*(Supuestos!$B$16+Supuestos!$B$17)/60+2*C43*$B43/60</f>
-        <v>0.362038840641586</v>
+        <f aca="false">E43*(Supuestos!$B$17+Supuestos!$B$18)/60+2*C43*$B43/60</f>
+        <v>0.776135553793726</v>
       </c>
       <c r="G43" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$68:$M$68,$C$5)*SUMPRODUCT(Importados!$N$39:$N$55,Importados!$W$39:$W$55/Importados!$X$39:$X$55)/$C$8</f>
@@ -7707,539 +7574,306 @@
       </c>
       <c r="H43" s="22" t="n">
         <f aca="false">Importados!W$57</f>
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I43" s="28" t="n">
         <f aca="false">2*G43/H43</f>
-        <v>0.26623873764709</v>
+        <v>0.709969967058907</v>
       </c>
       <c r="J43" s="28" t="n">
-        <f aca="false">I43*(Supuestos!$B$16+Supuestos!$B$17)/60+2*G43*$B43/60</f>
-        <v>0.226302927000027</v>
+        <f aca="false">I43*(Supuestos!$B$17+Supuestos!$B$18)/60+2*G43*$B43/60</f>
+        <v>0.48514614415692</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C44" s="30" t="n">
         <f aca="false">SUM(C37:C43)</f>
-        <v>1119.01482761851</v>
+        <v>1050.21469306323</v>
       </c>
       <c r="E44" s="30" t="n">
         <f aca="false">SUM(E37:E43)</f>
-        <v>110.767552253345</v>
+        <v>202.933635977327</v>
       </c>
       <c r="F44" s="30" t="n">
         <f aca="false">SUM(F37:F43)</f>
-        <v>102.124016481469</v>
+        <v>148.344763881951</v>
       </c>
       <c r="G44" s="30" t="n">
         <f aca="false">SUM(G37:G43)</f>
-        <v>599.546838706733</v>
+        <v>544.079465849848</v>
       </c>
       <c r="I44" s="30" t="n">
         <f aca="false">SUM(I37:I43)</f>
-        <v>59.7811503115376</v>
+        <v>104.932589629389</v>
       </c>
       <c r="J44" s="30" t="n">
         <f aca="false">SUM(J37:J43)</f>
-        <v>55.2434175763695</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>76.6725012481408</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B48" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B49" s="29" t="n">
         <f aca="false">F30</f>
-        <v>1119.01482761851</v>
+        <v>1050.21469306323</v>
       </c>
       <c r="C49" s="29" t="n">
         <f aca="false">I30</f>
-        <v>599.546838706733</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="5"/>
-      <c r="M49" s="5"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>544.079465849846</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B50" s="29" t="n">
         <f aca="false">G30</f>
-        <v>585.256044364544</v>
+        <v>397.522456343171</v>
       </c>
       <c r="C50" s="29" t="n">
         <f aca="false">J30</f>
-        <v>322.091098622045</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>204.786911560761</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B51" s="29" t="n">
         <f aca="false">B49+B50</f>
-        <v>1704.27087198305</v>
+        <v>1447.7371494064</v>
       </c>
       <c r="C51" s="29" t="n">
         <f aca="false">C49+C50</f>
-        <v>921.637937328778</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>748.866377410607</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B52" s="28" t="n">
         <f aca="false">F31</f>
-        <v>6.65882736300077</v>
+        <v>5.61010110978076</v>
       </c>
       <c r="C52" s="28" t="n">
         <f aca="false">I31</f>
-        <v>6.75381882934406</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="5"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>5.59545821055644</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B53" s="31" t="n">
         <f aca="false">H30/F30</f>
-        <v>0.0339389347831994</v>
+        <v>0.0303301061314881</v>
       </c>
       <c r="C53" s="31" t="n">
         <f aca="false">K30/I30</f>
-        <v>0.0343327004764821</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5"/>
-      <c r="M53" s="5"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>0.0302680808123589</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="B54" s="21" t="n">
-        <f aca="false">Supuestos!$B$6/(B53*Supuestos!$B$22)</f>
-        <v>153.728787826616</v>
+        <f aca="false">Supuestos!$B$6/(B53*Supuestos!$B$24)</f>
+        <v>172.020212581163</v>
       </c>
       <c r="C54" s="21" t="n">
-        <f aca="false">Supuestos!$B$6/(C53*Supuestos!$B$22)</f>
-        <v>151.965654665637</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
-      <c r="M54" s="5"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">Supuestos!$B$6/(C53*Supuestos!$B$24)</f>
+        <v>172.372716218515</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B55" s="21" t="n">
-        <f aca="false">Supuestos!$B$10/B52</f>
-        <v>248.692436329169</v>
+        <f aca="false">Supuestos!$B$11/B52</f>
+        <v>249.549869530732</v>
       </c>
       <c r="C55" s="21" t="n">
-        <f aca="false">Supuestos!$B$10/C52</f>
-        <v>245.194613868674</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
-      <c r="K55" s="5"/>
-      <c r="L55" s="5"/>
-      <c r="M55" s="5"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">Supuestos!$B$11/C52</f>
+        <v>250.202923034748</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B56" s="21" t="n">
         <f aca="false">MIN(B54,B55)</f>
-        <v>153.728787826616</v>
+        <v>172.020212581163</v>
       </c>
       <c r="C56" s="21" t="n">
         <f aca="false">MIN(C54,C55)</f>
-        <v>151.965654665637</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="5"/>
-      <c r="M56" s="5"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>172.372716218515</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B57" s="23" t="n">
         <f aca="false">B51/B56</f>
-        <v>11.086218112285</v>
+        <v>8.41608743346555</v>
       </c>
       <c r="C57" s="23" t="n">
         <f aca="false">C51/C56</f>
-        <v>6.06477785626375</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5"/>
-      <c r="L57" s="5"/>
-      <c r="M57" s="5"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>4.34446003891518</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B58" s="28" t="n">
         <f aca="false">E44</f>
-        <v>110.767552253345</v>
+        <v>202.933635977327</v>
       </c>
       <c r="C58" s="28" t="n">
         <f aca="false">I44</f>
-        <v>59.7811503115376</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="5"/>
-      <c r="K58" s="5"/>
-      <c r="L58" s="5"/>
-      <c r="M58" s="5"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>104.932589629389</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="B59" s="28" t="n">
         <f aca="false">F44</f>
-        <v>102.124016481469</v>
+        <v>148.344763881951</v>
       </c>
       <c r="C59" s="28" t="n">
         <f aca="false">J44</f>
-        <v>55.2434175763695</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
-      <c r="K59" s="5"/>
-      <c r="L59" s="5"/>
-      <c r="M59" s="5"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>76.6725012481408</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="B60" s="23" t="n">
-        <f aca="false">B59/($B$9-Supuestos!$B$15)</f>
-        <v>17.0206694135782</v>
+        <f aca="false">B59/($B$9-Supuestos!$B$16)</f>
+        <v>24.7241273136584</v>
       </c>
       <c r="C60" s="23" t="n">
-        <f aca="false">C59/($C$9-Supuestos!$B$15)</f>
-        <v>9.20723626272825</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="5"/>
-      <c r="M60" s="5"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">C59/($C$9-Supuestos!$B$16)</f>
+        <v>12.7787502080235</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B61" s="9" t="n">
         <f aca="false">ROUNDUP(MAX(B57,B60),0)</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C61" s="9" t="n">
         <f aca="false">ROUNDUP(MAX(C57,C60),0)</f>
-        <v>10</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="5"/>
-      <c r="M61" s="5"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="B62" s="28" t="n">
-        <f aca="false">B61*Supuestos!$B$15+B59</f>
-        <v>129.124016481469</v>
+        <f aca="false">B61*Supuestos!$B$16+B59</f>
+        <v>185.844763881951</v>
       </c>
       <c r="C62" s="28" t="n">
-        <f aca="false">C61*Supuestos!$B$15+C59</f>
-        <v>70.2434175763695</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
-      <c r="K62" s="5"/>
-      <c r="L62" s="5"/>
-      <c r="M62" s="5"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">C61*Supuestos!$B$16+C59</f>
+        <v>96.1725012481408</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="B63" s="9" t="n">
-        <f aca="false">ROUNDUP(B62/($B$9*Supuestos!$B$14),0)</f>
-        <v>9</v>
+        <f aca="false">ROUNDUP(B62/($B$9*Supuestos!$B$15*Supuestos!$B$19),0)</f>
+        <v>14</v>
       </c>
       <c r="C63" s="9" t="n">
-        <f aca="false">ROUNDUP(C62/($C$9*Supuestos!$B$14),0)</f>
-        <v>5</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
-      <c r="M63" s="5"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">ROUNDUP(C62/($C$9*Supuestos!$B$15*Supuestos!$B$19),0)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B64" s="32" t="n">
-        <f aca="false">B62/(B63*$B$9*Supuestos!$B$14)</f>
-        <v>0.956474196159033</v>
+        <f aca="false">B62/(B63*$B$9*Supuestos!$B$15)</f>
+        <v>0.884975066104527</v>
       </c>
       <c r="C64" s="32" t="n">
-        <f aca="false">C62/(C63*$C$9*Supuestos!$B$14)</f>
-        <v>0.93657890101826</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
-      <c r="K64" s="5"/>
-      <c r="L64" s="5"/>
-      <c r="M64" s="5"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">C62/(C63*$C$9*Supuestos!$B$15)</f>
+        <v>0.801437510401173</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B65" s="21" t="n">
         <f aca="false">B51*B52/B61</f>
-        <v>630.469195351441</v>
+        <v>324.878071542227</v>
       </c>
       <c r="C65" s="21" t="n">
         <f aca="false">C51*C52/C61</f>
-        <v>622.457565496893</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
-      <c r="K65" s="5"/>
-      <c r="L65" s="5"/>
-      <c r="M65" s="5"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>322.326963083987</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="B66" s="21" t="str">
-        <f aca="false">IF(Supuestos!$B$11="","a cotizar",B63*Supuestos!$B$11)</f>
+        <f aca="false">IF(Supuestos!$B$12="","a cotizar",B63*Supuestos!$B$12)</f>
         <v>a cotizar</v>
       </c>
       <c r="C66" s="21" t="str">
-        <f aca="false">IF(Supuestos!$B$11="","a cotizar",C63*Supuestos!$B$11)</f>
+        <f aca="false">IF(Supuestos!$B$12="","a cotizar",C63*Supuestos!$B$12)</f>
         <v>a cotizar</v>
       </c>
-      <c r="D66" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5"/>
-      <c r="L66" s="5"/>
-      <c r="M66" s="5"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
       <c r="F68" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G68" s="6"/>
       <c r="H68" s="6"/>
@@ -8248,36 +7882,36 @@
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
       <c r="M68" s="6" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="J69" s="6"/>
       <c r="K69" s="6"/>
@@ -8286,182 +7920,182 @@
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="B70" s="21" t="n">
-        <f aca="false">F30*Supuestos!$B$20</f>
-        <v>559.507413809255</v>
+        <f aca="false">F30*Supuestos!$B$22</f>
+        <v>525.107346531615</v>
       </c>
       <c r="C70" s="28" t="n">
-        <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*H13:H29)*Supuestos!$B$20*Supuestos!$B$22</f>
-        <v>18.1193273540365</v>
+        <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*H13:H29)*Supuestos!$B$22*Supuestos!$B$24</f>
+        <v>14.8076127992378</v>
       </c>
       <c r="D70" s="28" t="n">
-        <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*H13:H29)*Supuestos!$B$20</f>
-        <v>3.23314879839187</v>
+        <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*H13:H29)*Supuestos!$B$22</f>
+        <v>3.05037650791249</v>
       </c>
       <c r="E70" s="22" t="n">
         <f aca="false">ROUNDUP(C70,0)+ROUNDUP(D70,0)</f>
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F70" s="21" t="n">
-        <f aca="false">I30*Supuestos!$B$20</f>
-        <v>299.773419353367</v>
+        <f aca="false">I30*Supuestos!$B$22</f>
+        <v>272.039732924923</v>
       </c>
       <c r="G70" s="28" t="n">
-        <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*K13:K29)*Supuestos!$B$20*Supuestos!$B$22</f>
-        <v>9.84255490740292</v>
+        <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*K13:K29)*Supuestos!$B$22*Supuestos!$B$24</f>
+        <v>7.65268321403531</v>
       </c>
       <c r="H70" s="28" t="n">
-        <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*K13:K29)*Supuestos!$B$20</f>
-        <v>1.73328761972833</v>
+        <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*K13:K29)*Supuestos!$B$22</f>
+        <v>1.57961347770469</v>
       </c>
       <c r="I70" s="22" t="n">
         <f aca="false">ROUNDUP(G70,0)+ROUNDUP(H70,0)</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M70" s="5" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="B71" s="21" t="n">
-        <f aca="false">F30*Supuestos!$B$21</f>
-        <v>559.507413809255</v>
+        <f aca="false">F30*Supuestos!$B$23</f>
+        <v>525.107346531615</v>
       </c>
       <c r="C71" s="28" t="n">
-        <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*H13:H29)*Supuestos!$B$21*Supuestos!$B$22</f>
-        <v>18.1193273540365</v>
+        <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*H13:H29)*Supuestos!$B$23*Supuestos!$B$24</f>
+        <v>14.8076127992378</v>
       </c>
       <c r="D71" s="28" t="n">
-        <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*H13:H29)*Supuestos!$B$21</f>
-        <v>3.23314879839187</v>
+        <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*H13:H29)*Supuestos!$B$23</f>
+        <v>3.05037650791249</v>
       </c>
       <c r="E71" s="22" t="n">
         <f aca="false">ROUNDUP(C71,0)+ROUNDUP(D71,0)</f>
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F71" s="21" t="n">
-        <f aca="false">I30*Supuestos!$B$21</f>
-        <v>299.773419353367</v>
+        <f aca="false">I30*Supuestos!$B$23</f>
+        <v>272.039732924923</v>
       </c>
       <c r="G71" s="28" t="n">
-        <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*K13:K29)*Supuestos!$B$21*Supuestos!$B$22</f>
-        <v>9.84255490740292</v>
+        <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*K13:K29)*Supuestos!$B$23*Supuestos!$B$24</f>
+        <v>7.65268321403531</v>
       </c>
       <c r="H71" s="28" t="n">
-        <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*K13:K29)*Supuestos!$B$21</f>
-        <v>1.73328761972833</v>
+        <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*K13:K29)*Supuestos!$B$23</f>
+        <v>1.57961347770469</v>
       </c>
       <c r="I71" s="22" t="n">
         <f aca="false">ROUNDUP(G71,0)+ROUNDUP(H71,0)</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M71" s="5" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="B72" s="21" t="n">
         <f aca="false">G30</f>
-        <v>585.256044364544</v>
+        <v>397.522456343171</v>
       </c>
       <c r="C72" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*G13:G29/$C$13:$C$29)</f>
-        <v>24.0985572251111</v>
+        <v>16.6872001311857</v>
       </c>
       <c r="D72" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*G13:G29/$C$13:$C$29)</f>
-        <v>6.46629759678374</v>
+        <v>6.10075301582498</v>
       </c>
       <c r="E72" s="22" t="n">
-        <f aca="false">ROUNDUP(C72/Supuestos!$B$24,0)+ROUNDUP(D72,0)</f>
-        <v>16</v>
+        <f aca="false">ROUNDUP(C72/Supuestos!$B$26,0)+ROUNDUP(D72,0)</f>
+        <v>13</v>
       </c>
       <c r="F72" s="21" t="n">
         <f aca="false">J30</f>
-        <v>322.091098622045</v>
+        <v>204.786911560761</v>
       </c>
       <c r="G72" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*J13:J29/$C$13:$C$29)</f>
-        <v>13.2639348498627</v>
+        <v>8.59661769793039</v>
       </c>
       <c r="H72" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*J13:J29/$C$13:$C$29)</f>
-        <v>3.46657523945665</v>
+        <v>3.15922695540939</v>
       </c>
       <c r="I72" s="22" t="n">
-        <f aca="false">ROUNDUP(G72/Supuestos!$B$24,0)+ROUNDUP(H72,0)</f>
-        <v>9</v>
+        <f aca="false">ROUNDUP(G72/Supuestos!$B$26,0)+ROUNDUP(H72,0)</f>
+        <v>7</v>
       </c>
       <c r="M72" s="5" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="C73" s="28" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D73" s="28" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="E73" s="22" t="n">
-        <f aca="false">ROUNDUP(SUM(E70:E72)*Supuestos!$B$23/Supuestos!$B$25,0)</f>
-        <v>5</v>
+        <f aca="false">ROUNDUP(SUM(E70:E72)*Supuestos!$B$25/Supuestos!$B$27,0)</f>
+        <v>2</v>
       </c>
       <c r="F73" s="21" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="G73" s="28" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="H73" s="28" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="I73" s="22" t="n">
-        <f aca="false">ROUNDUP(SUM(I70:I72)*Supuestos!$B$23/Supuestos!$B$25,0)</f>
-        <v>3</v>
+        <f aca="false">ROUNDUP(SUM(I70:I72)*Supuestos!$B$25/Supuestos!$B$27,0)</f>
+        <v>2</v>
       </c>
       <c r="M73" s="5" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="E74" s="9" t="n">
         <f aca="false">SUM(E70:E73)</f>
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="I74" s="9" t="n">
         <f aca="false">SUM(I70:I73)</f>
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="E75" s="11" t="n">
-        <f aca="false">E74*Supuestos!$B$26</f>
-        <v>160.8</v>
+        <f aca="false">E74*Supuestos!$B$28</f>
+        <v>127.2</v>
       </c>
       <c r="I75" s="11" t="n">
-        <f aca="false">I74*Supuestos!$B$26</f>
-        <v>86.4</v>
+        <f aca="false">I74*Supuestos!$B$28</f>
+        <v>69.6</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8470,57 +8104,32 @@
       </c>
       <c r="E76" s="7" t="n">
         <f aca="false">Importados!$P$22</f>
-        <v>1833</v>
+        <v>1757</v>
       </c>
       <c r="I76" s="7" t="n">
         <f aca="false">Importados!$P$56</f>
-        <v>1004</v>
+        <v>985</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="E77" s="9" t="n">
-        <f aca="false">ROUNDUP(SUM(C70:C72),0)+B63*Supuestos!$B$6+E73*Supuestos!$B$25</f>
-        <v>125</v>
+        <f aca="false">ROUNDUP(SUM(C70:C72),0)+B63*Supuestos!$B$6+E73*Supuestos!$B$27</f>
+        <v>139</v>
       </c>
       <c r="I77" s="9" t="n">
-        <f aca="false">ROUNDUP(SUM(G70:G72),0)+C63*Supuestos!$B$6+I73*Supuestos!$B$25</f>
-        <v>69</v>
+        <f aca="false">ROUNDUP(SUM(G70:G72),0)+C63*Supuestos!$B$6+I73*Supuestos!$B$27</f>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="D4:M4"/>
-    <mergeCell ref="D5:M5"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="D7:M7"/>
-    <mergeCell ref="D8:M8"/>
-    <mergeCell ref="D9:M9"/>
+  <mergeCells count="6">
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="I11:K11"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="G35:J35"/>
-    <mergeCell ref="D48:M48"/>
-    <mergeCell ref="D49:M49"/>
-    <mergeCell ref="D50:M50"/>
-    <mergeCell ref="D51:M51"/>
-    <mergeCell ref="D52:M52"/>
-    <mergeCell ref="D53:M53"/>
-    <mergeCell ref="D54:M54"/>
-    <mergeCell ref="D55:M55"/>
-    <mergeCell ref="D56:M56"/>
-    <mergeCell ref="D57:M57"/>
-    <mergeCell ref="D58:M58"/>
-    <mergeCell ref="D59:M59"/>
-    <mergeCell ref="D60:M60"/>
-    <mergeCell ref="D61:M61"/>
-    <mergeCell ref="D62:M62"/>
-    <mergeCell ref="D63:M63"/>
-    <mergeCell ref="D64:M64"/>
-    <mergeCell ref="D65:M65"/>
-    <mergeCell ref="D66:M66"/>
     <mergeCell ref="B68:E68"/>
     <mergeCell ref="F68:I68"/>
   </mergeCells>

--- a/salida/Recargas.xlsx
+++ b/salida/Recargas.xlsx
@@ -1308,11 +1308,11 @@
       </c>
       <c r="B9" s="7" t="n">
         <f aca="false">Importados!$P$22</f>
-        <v>1757</v>
+        <v>1384</v>
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">Importados!$P$56</f>
-        <v>985</v>
+        <v>744</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>23</v>
@@ -1946,16 +1946,16 @@
         <v>0.0789430506992025</v>
       </c>
       <c r="C6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.131626442308772)</f>
-        <v>0.131626442308772</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0965041812357258)</f>
+        <v>0.0965041812357258</v>
       </c>
       <c r="D6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
-        <v>0.0789430506992025</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0965041812357258)</f>
+        <v>0.0965041812357258</v>
       </c>
       <c r="E6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
-        <v>0.0789430506992025</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0965041812357258)</f>
+        <v>0.0965041812357258</v>
       </c>
       <c r="F6" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
@@ -1998,8 +1998,8 @@
         <v>1</v>
       </c>
       <c r="P6" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),185)</f>
-        <v>185</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),136)</f>
+        <v>136</v>
       </c>
       <c r="Q6" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2043,16 +2043,16 @@
         <v>0.0830536456103754</v>
       </c>
       <c r="C7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.113191682697692)</f>
-        <v>0.113191682697692</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.091115822090457)</f>
+        <v>0.091115822090457</v>
       </c>
       <c r="D7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
-        <v>0.0800778917868397</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.091115822090457)</f>
+        <v>0.091115822090457</v>
       </c>
       <c r="E7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
-        <v>0.0800778917868397</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.091115822090457)</f>
+        <v>0.091115822090457</v>
       </c>
       <c r="F7" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
@@ -2095,8 +2095,8 @@
         <v>1</v>
       </c>
       <c r="P7" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),967)</f>
-        <v>967</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),778)</f>
+        <v>778</v>
       </c>
       <c r="Q7" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69628)</f>
@@ -2140,16 +2140,16 @@
         <v>0.078155341572415</v>
       </c>
       <c r="C8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.140291242703435)</f>
-        <v>0.140291242703435</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0988673086160884)</f>
+        <v>0.0988673086160884</v>
       </c>
       <c r="D8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
-        <v>0.078155341572415</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0988673086160884)</f>
+        <v>0.0988673086160884</v>
       </c>
       <c r="E8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
-        <v>0.078155341572415</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0988673086160884)</f>
+        <v>0.0988673086160884</v>
       </c>
       <c r="F8" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
@@ -2192,8 +2192,8 @@
         <v>1</v>
       </c>
       <c r="P8" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73)</f>
-        <v>73</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51)</f>
+        <v>51</v>
       </c>
       <c r="Q8" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2237,16 +2237,16 @@
         <v>0.0802492777307454</v>
       </c>
       <c r="C9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1172579449618)</f>
-        <v>0.1172579449618</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0925855001410971)</f>
+        <v>0.0925855001410971</v>
       </c>
       <c r="D9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
-        <v>0.0802492777307454</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0925855001410971)</f>
+        <v>0.0925855001410971</v>
       </c>
       <c r="E9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
-        <v>0.0802492777307454</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0925855001410971)</f>
+        <v>0.0925855001410971</v>
       </c>
       <c r="F9" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
@@ -2289,8 +2289,8 @@
         <v>1</v>
       </c>
       <c r="P9" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),86)</f>
-        <v>86</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),68)</f>
+        <v>68</v>
       </c>
       <c r="Q9" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2625,16 +2625,16 @@
         <v>0.0771892846953241</v>
       </c>
       <c r="C13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.150917868351435)</f>
-        <v>0.150917868351435</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101765479247361)</f>
+        <v>0.101765479247361</v>
       </c>
       <c r="D13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
-        <v>0.0771892846953241</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101765479247361)</f>
+        <v>0.101765479247361</v>
       </c>
       <c r="E13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
-        <v>0.0771892846953241</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101765479247361)</f>
+        <v>0.101765479247361</v>
       </c>
       <c r="F13" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
@@ -2677,8 +2677,8 @@
         <v>1</v>
       </c>
       <c r="P13" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54)</f>
-        <v>54</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37)</f>
+        <v>37</v>
       </c>
       <c r="Q13" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2722,16 +2722,16 @@
         <v>0.0787292505395418</v>
       </c>
       <c r="C14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.13397824406504)</f>
-        <v>0.13397824406504</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0971455817147079)</f>
+        <v>0.0971455817147079</v>
       </c>
       <c r="D14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
-        <v>0.0787292505395418</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0971455817147079)</f>
+        <v>0.0971455817147079</v>
       </c>
       <c r="E14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
-        <v>0.0787292505395418</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0971455817147079)</f>
+        <v>0.0971455817147079</v>
       </c>
       <c r="F14" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
@@ -2774,8 +2774,8 @@
         <v>1</v>
       </c>
       <c r="P14" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),258)</f>
-        <v>258</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),187)</f>
+        <v>187</v>
       </c>
       <c r="Q14" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2819,16 +2819,16 @@
         <v>0.0826992607152812</v>
       </c>
       <c r="C15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0903081321319072)</f>
-        <v>0.0903081321319072</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0852355511874899)</f>
+        <v>0.0852355511874899</v>
       </c>
       <c r="D15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
-        <v>0.0826992607152812</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0852355511874899)</f>
+        <v>0.0852355511874899</v>
       </c>
       <c r="E15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
-        <v>0.0826992607152812</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0852355511874899)</f>
+        <v>0.0852355511874899</v>
       </c>
       <c r="F15" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
@@ -2871,8 +2871,8 @@
         <v>1</v>
       </c>
       <c r="P15" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),62)</f>
-        <v>62</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58)</f>
+        <v>58</v>
       </c>
       <c r="Q15" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -3110,16 +3110,16 @@
         <v>0.0822850273487674</v>
       </c>
       <c r="C18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0948646991635592)</f>
-        <v>0.0948646991635592</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864782512870313)</f>
+        <v>0.0864782512870313</v>
       </c>
       <c r="D18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
-        <v>0.0822850273487674</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864782512870313)</f>
+        <v>0.0864782512870313</v>
       </c>
       <c r="E18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
-        <v>0.0822850273487674</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864782512870313)</f>
+        <v>0.0864782512870313</v>
       </c>
       <c r="F18" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
@@ -3162,8 +3162,8 @@
         <v>1</v>
       </c>
       <c r="P18" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9)</f>
-        <v>9</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8)</f>
+        <v>8</v>
       </c>
       <c r="Q18" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -3207,16 +3207,16 @@
         <v>0.0822848847558399</v>
       </c>
       <c r="C19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0948662676857615)</f>
-        <v>0.0948662676857615</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864786790658138)</f>
+        <v>0.0864786790658138</v>
       </c>
       <c r="D19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
-        <v>0.0822848847558399</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864786790658138)</f>
+        <v>0.0864786790658138</v>
       </c>
       <c r="E19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
-        <v>0.0822848847558399</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864786790658138)</f>
+        <v>0.0864786790658138</v>
       </c>
       <c r="F19" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
@@ -3259,8 +3259,8 @@
         <v>1</v>
       </c>
       <c r="P19" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19)</f>
-        <v>19</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18)</f>
+        <v>18</v>
       </c>
       <c r="Q19" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -3304,16 +3304,16 @@
         <v>0.0822852002059122</v>
       </c>
       <c r="C20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0948627977349655)</f>
-        <v>0.0948627977349655</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864777327155967)</f>
+        <v>0.0864777327155967</v>
       </c>
       <c r="D20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
-        <v>0.0822852002059122</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864777327155967)</f>
+        <v>0.0864777327155967</v>
       </c>
       <c r="E20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
-        <v>0.0822852002059122</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864777327155967)</f>
+        <v>0.0864777327155967</v>
       </c>
       <c r="F20" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
@@ -3356,8 +3356,8 @@
         <v>1</v>
       </c>
       <c r="P20" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5)</f>
-        <v>5</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4)</f>
+        <v>4</v>
       </c>
       <c r="Q20" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -3401,16 +3401,16 @@
         <v>0.082284103832348</v>
       </c>
       <c r="C21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0948748578441723)</f>
-        <v>0.0948748578441723</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864810218362894)</f>
+        <v>0.0864810218362894</v>
       </c>
       <c r="D21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
-        <v>0.082284103832348</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864810218362894)</f>
+        <v>0.0864810218362894</v>
       </c>
       <c r="E21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
-        <v>0.082284103832348</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864810218362894)</f>
+        <v>0.0864810218362894</v>
       </c>
       <c r="F21" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
@@ -3498,16 +3498,16 @@
         <v>0.101848800284409</v>
       </c>
       <c r="C22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955604631711142)</f>
-        <v>0.0955604631711142</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0837602978170431)</f>
+        <v>0.0837602978170431</v>
       </c>
       <c r="D22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
-        <v>0.0778602151400075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0837602978170431)</f>
+        <v>0.0837602978170431</v>
       </c>
       <c r="E22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
-        <v>0.0778602151400075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0837602978170431)</f>
+        <v>0.0837602978170431</v>
       </c>
       <c r="F22" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="P22" s="7" t="n">
         <f aca="false">SUM(P5:P21)</f>
-        <v>1757</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3757,16 +3757,16 @@
         <v>0.0295134514379623</v>
       </c>
       <c r="C30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.675352034182415)</f>
-        <v>0.675352034182415</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.244792979019447)</f>
+        <v>0.244792979019447</v>
       </c>
       <c r="D30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
-        <v>0.0295134514379623</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.244792979019447)</f>
+        <v>0.244792979019447</v>
       </c>
       <c r="E30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
-        <v>0.0295134514379623</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.244792979019447)</f>
+        <v>0.244792979019447</v>
       </c>
       <c r="F30" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
@@ -4198,16 +4198,16 @@
         <v>0.0779725990367327</v>
       </c>
       <c r="C40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.14230141059594)</f>
-        <v>0.14230141059594</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994155362231353)</f>
+        <v>0.0994155362231353</v>
       </c>
       <c r="D40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
-        <v>0.0779725990367327</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994155362231353)</f>
+        <v>0.0994155362231353</v>
       </c>
       <c r="E40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
-        <v>0.0779725990367327</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994155362231353)</f>
+        <v>0.0994155362231353</v>
       </c>
       <c r="F40" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
@@ -4250,8 +4250,8 @@
         <v>1</v>
       </c>
       <c r="P40" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104)</f>
-        <v>104</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73)</f>
+        <v>73</v>
       </c>
       <c r="Q40" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -4295,16 +4295,16 @@
         <v>0.0824116289014618</v>
       </c>
       <c r="C41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.121277469433113)</f>
-        <v>0.121277469433113</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0933072507565163)</f>
+        <v>0.0933072507565163</v>
       </c>
       <c r="D41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
-        <v>0.0793221414182182</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0933072507565163)</f>
+        <v>0.0933072507565163</v>
       </c>
       <c r="E41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
-        <v>0.0793221414182182</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0933072507565163)</f>
+        <v>0.0933072507565163</v>
       </c>
       <c r="F41" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
@@ -4347,8 +4347,8 @@
         <v>1</v>
       </c>
       <c r="P41" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),540)</f>
-        <v>540</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415)</f>
+        <v>415</v>
       </c>
       <c r="Q41" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36760)</f>
@@ -4392,16 +4392,16 @@
         <v>0.0770946445386376</v>
       </c>
       <c r="C42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.151958910074986)</f>
-        <v>0.151958910074986</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10204939971742)</f>
+        <v>0.10204939971742</v>
       </c>
       <c r="D42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
-        <v>0.0770946445386376</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10204939971742)</f>
+        <v>0.10204939971742</v>
       </c>
       <c r="E42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
-        <v>0.0770946445386376</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10204939971742)</f>
+        <v>0.10204939971742</v>
       </c>
       <c r="F42" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
@@ -4444,8 +4444,8 @@
         <v>1</v>
       </c>
       <c r="P42" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),41)</f>
-        <v>41</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28)</f>
+        <v>28</v>
       </c>
       <c r="Q42" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -4489,16 +4489,16 @@
         <v>0.0793823941427303</v>
       </c>
       <c r="C43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.126793664429966)</f>
-        <v>0.126793664429966</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0951861509051423)</f>
+        <v>0.0951861509051423</v>
       </c>
       <c r="D43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
-        <v>0.0793823941427303</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0951861509051423)</f>
+        <v>0.0951861509051423</v>
       </c>
       <c r="E43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
-        <v>0.0793823941427303</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0951861509051423)</f>
+        <v>0.0951861509051423</v>
       </c>
       <c r="F43" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
@@ -4541,8 +4541,8 @@
         <v>1</v>
       </c>
       <c r="P43" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49)</f>
-        <v>49</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37)</f>
+        <v>37</v>
       </c>
       <c r="Q43" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -4877,16 +4877,16 @@
         <v>0.0758238813821944</v>
       </c>
       <c r="C47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.165937304795862)</f>
-        <v>0.165937304795862</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10586168918675)</f>
+        <v>0.10586168918675</v>
       </c>
       <c r="D47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
-        <v>0.0758238813821944</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10586168918675)</f>
+        <v>0.10586168918675</v>
       </c>
       <c r="E47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
-        <v>0.0758238813821944</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10586168918675)</f>
+        <v>0.10586168918675</v>
       </c>
       <c r="F47" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
@@ -4929,8 +4929,8 @@
         <v>1</v>
       </c>
       <c r="P47" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31)</f>
-        <v>31</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20)</f>
+        <v>20</v>
       </c>
       <c r="Q47" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -4974,16 +4974,16 @@
         <v>0.0776565294661689</v>
       </c>
       <c r="C48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.145778175872141)</f>
-        <v>0.145778175872141</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100363744934826)</f>
+        <v>0.100363744934826</v>
       </c>
       <c r="D48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
-        <v>0.0776565294661689</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100363744934826)</f>
+        <v>0.100363744934826</v>
       </c>
       <c r="E48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
-        <v>0.0776565294661689</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100363744934826)</f>
+        <v>0.100363744934826</v>
       </c>
       <c r="F48" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
@@ -5026,8 +5026,8 @@
         <v>1</v>
       </c>
       <c r="P48" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146)</f>
-        <v>146</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101)</f>
+        <v>101</v>
       </c>
       <c r="Q48" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -5071,16 +5071,16 @@
         <v>0.0824962815446097</v>
       </c>
       <c r="C49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0925409030092935)</f>
-        <v>0.0925409030092935</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0858444886995043)</f>
+        <v>0.0858444886995043</v>
       </c>
       <c r="D49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
-        <v>0.0824962815446097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0858444886995043)</f>
+        <v>0.0858444886995043</v>
       </c>
       <c r="E49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
-        <v>0.0824962815446097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0858444886995043)</f>
+        <v>0.0858444886995043</v>
       </c>
       <c r="F49" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
@@ -5123,8 +5123,8 @@
         <v>1</v>
       </c>
       <c r="P49" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33)</f>
-        <v>33</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31)</f>
+        <v>31</v>
       </c>
       <c r="Q49" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -5362,16 +5362,16 @@
         <v>0.0819169643322097</v>
       </c>
       <c r="C52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0989133923456932)</f>
-        <v>0.0989133923456932</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875824403367042)</f>
+        <v>0.0875824403367042</v>
       </c>
       <c r="D52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
-        <v>0.0819169643322097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875824403367042)</f>
+        <v>0.0875824403367042</v>
       </c>
       <c r="E52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
-        <v>0.0819169643322097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875824403367042)</f>
+        <v>0.0875824403367042</v>
       </c>
       <c r="F52" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
@@ -5459,16 +5459,16 @@
         <v>0.0819175760181933</v>
       </c>
       <c r="C53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0989066637998739)</f>
-        <v>0.0989066637998739</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875806052787535)</f>
+        <v>0.0875806052787535</v>
       </c>
       <c r="D53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
-        <v>0.0819175760181933</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875806052787535)</f>
+        <v>0.0875806052787535</v>
       </c>
       <c r="E53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
-        <v>0.0819175760181933</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875806052787535)</f>
+        <v>0.0875806052787535</v>
       </c>
       <c r="F53" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
@@ -5511,8 +5511,8 @@
         <v>1</v>
       </c>
       <c r="P53" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11)</f>
-        <v>11</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10)</f>
+        <v>10</v>
       </c>
       <c r="Q53" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -5556,16 +5556,16 @@
         <v>0.0819180495097435</v>
       </c>
       <c r="C54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0989014553928212)</f>
-        <v>0.0989014553928212</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875791848041027)</f>
+        <v>0.0875791848041027</v>
       </c>
       <c r="D54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
-        <v>0.0819180495097435</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875791848041027)</f>
+        <v>0.0875791848041027</v>
       </c>
       <c r="E54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
-        <v>0.0819180495097435</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875791848041027)</f>
+        <v>0.0875791848041027</v>
       </c>
       <c r="F54" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
@@ -5608,8 +5608,8 @@
         <v>1</v>
       </c>
       <c r="P54" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3)</f>
-        <v>3</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2)</f>
+        <v>2</v>
       </c>
       <c r="Q54" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -5653,16 +5653,16 @@
         <v>0.0819179890740179</v>
       </c>
       <c r="C55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0989021201858035)</f>
-        <v>0.0989021201858035</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875793661112797)</f>
+        <v>0.0875793661112797</v>
       </c>
       <c r="D55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
-        <v>0.0819179890740179</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875793661112797)</f>
+        <v>0.0875793661112797</v>
       </c>
       <c r="E55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
-        <v>0.0819179890740179</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875793661112797)</f>
+        <v>0.0875793661112797</v>
       </c>
       <c r="F55" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
@@ -5750,16 +5750,16 @@
         <v>0.1015098507676</v>
       </c>
       <c r="C56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0996205288380497)</f>
-        <v>0.0996205288380497</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0848631221776276)</f>
+        <v>0.0848631221776276</v>
       </c>
       <c r="D56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
-        <v>0.0774844188474166</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0848631221776276)</f>
+        <v>0.0848631221776276</v>
       </c>
       <c r="E56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
-        <v>0.0774844188474166</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0848631221776276)</f>
+        <v>0.0848631221776276</v>
       </c>
       <c r="F56" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
@@ -5799,7 +5799,7 @@
       </c>
       <c r="P56" s="7" t="n">
         <f aca="false">SUM(P39:P55)</f>
-        <v>985</v>
+        <v>744</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6009,16 +6009,16 @@
         <v>0.0269650818628408</v>
       </c>
       <c r="C64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.703384099508751)</f>
-        <v>0.703384099508751</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.252438087744811)</f>
+        <v>0.252438087744811</v>
       </c>
       <c r="D64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
-        <v>0.0269650818628408</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.252438087744811)</f>
+        <v>0.252438087744811</v>
       </c>
       <c r="E64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
-        <v>0.0269650818628408</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.252438087744811)</f>
+        <v>0.252438087744811</v>
       </c>
       <c r="F64" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
@@ -8104,11 +8104,11 @@
       </c>
       <c r="E76" s="7" t="n">
         <f aca="false">Importados!$P$22</f>
-        <v>1757</v>
+        <v>1384</v>
       </c>
       <c r="I76" s="7" t="n">
         <f aca="false">Importados!$P$56</f>
-        <v>985</v>
+        <v>744</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/salida/Recargas.xlsx
+++ b/salida/Recargas.xlsx
@@ -41,7 +41,7 @@
     <t xml:space="preserve">Qué se importa</t>
   </si>
   <si>
-    <t xml:space="preserve">Dimensionamiento Recargas Planta Comercial</t>
+    <t xml:space="preserve">Aprovechamiento Recargas Planta Comercial</t>
   </si>
   <si>
     <t xml:space="preserve">PEGAR ACÁ EL LINK DEL GOOGLE SHEET</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Lo que trae la hoja Importados</t>
   </si>
   <si>
-    <t xml:space="preserve">Dimensionamiento Recargas Planta Industrial</t>
+    <t xml:space="preserve">Aprovechamiento Recargas Planta Industrial</t>
   </si>
   <si>
     <t xml:space="preserve">Recargas — logística de las dos plantas (mes pico de 2035)</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Stock de sustitutos (u)</t>
   </si>
   <si>
-    <t xml:space="preserve">Dimensionamiento, paso 3</t>
+    <t xml:space="preserve">Aprovechamiento, paso 3</t>
   </si>
   <si>
     <t xml:space="preserve">Paradas por día</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">Pasillo compartido por dos filas</t>
   </si>
   <si>
-    <t xml:space="preserve">Importados de los Dimensionamientos de recargas (IMPORTRANGE; el link va en la hoja Links)</t>
+    <t xml:space="preserve">Importados de los Aprovechamientos de recargas (IMPORTRANGE; el link va en la hoja Links)</t>
   </si>
   <si>
     <t xml:space="preserve">Planta comercial</t>
@@ -1260,11 +1260,11 @@
       </c>
       <c r="B6" s="8" t="str">
         <f aca="false">Cálculo!B6</f>
-        <v>Ene</v>
+        <v>Dic</v>
       </c>
       <c r="C6" s="8" t="str">
         <f aca="false">Cálculo!C6</f>
-        <v>Ene</v>
+        <v>Dic</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>18</v>
@@ -1276,11 +1276,11 @@
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">Cálculo!F30</f>
-        <v>1050.21469306323</v>
+        <v>1061.94364471736</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">Cálculo!I30</f>
-        <v>544.079465849846</v>
+        <v>552.297705704186</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>20</v>
@@ -1292,11 +1292,11 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">Cálculo!G30</f>
-        <v>397.522456343171</v>
+        <v>409.324808263162</v>
       </c>
       <c r="C8" s="7" t="n">
         <f aca="false">Cálculo!J30</f>
-        <v>204.786911560761</v>
+        <v>213.042982501654</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>20</v>
@@ -1308,11 +1308,11 @@
       </c>
       <c r="B9" s="7" t="n">
         <f aca="false">Importados!$P$22</f>
-        <v>1384</v>
+        <v>1498</v>
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">Importados!$P$56</f>
-        <v>744</v>
+        <v>785</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>23</v>
@@ -1324,11 +1324,11 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">Cálculo!E44</f>
-        <v>202.933635977327</v>
+        <v>203.873824185969</v>
       </c>
       <c r="C10" s="7" t="n">
         <f aca="false">Cálculo!I44</f>
-        <v>104.932589629389</v>
+        <v>105.685449564868</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>25</v>
@@ -1372,11 +1372,11 @@
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">Cálculo!B64</f>
-        <v>0.884975066104527</v>
+        <v>0.890469451056304</v>
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">Cálculo!C64</f>
-        <v>0.801437510401173</v>
+        <v>0.808620119744484</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>27</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">Cálculo!E74</f>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C14" s="9" t="n">
         <f aca="false">Cálculo!I74</f>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B15" s="11" t="n">
         <f aca="false">Cálculo!E75</f>
-        <v>127.2</v>
+        <v>132</v>
       </c>
       <c r="C15" s="11" t="n">
         <f aca="false">Cálculo!I75</f>
@@ -1420,11 +1420,11 @@
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">Cálculo!E77</f>
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="9" t="n">
         <f aca="false">Cálculo!I77</f>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>31</v>
@@ -1845,52 +1845,52 @@
         <v>109</v>
       </c>
       <c r="B5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""parametros_recargas!E55:P72"")"),0.119933202334914)</f>
-        <v>0.119933202334914</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""parametros_recargas!E55:P72"")"),0.119877958433184)</f>
+        <v>0.119877958433184</v>
       </c>
       <c r="C5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
-        <v>0.0760133595330172</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0954780457654631)</f>
+        <v>0.0954780457654631</v>
       </c>
       <c r="D5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
-        <v>0.0760133595330172</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711264175844748)</f>
+        <v>0.0711264175844748</v>
       </c>
       <c r="E5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
-        <v>0.0760133595330172</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711264175844748)</f>
+        <v>0.0711264175844748</v>
       </c>
       <c r="F5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
-        <v>0.0760133595330172</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711747020712071)</f>
+        <v>0.0711747020712071</v>
       </c>
       <c r="G5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
-        <v>0.0760133595330172</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711747020712071)</f>
+        <v>0.0711747020712071</v>
       </c>
       <c r="H5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
-        <v>0.0760133595330172</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0710911890912281)</f>
+        <v>0.0710911890912281</v>
       </c>
       <c r="I5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
-        <v>0.0760133595330172</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711747020712071)</f>
+        <v>0.0711747020712071</v>
       </c>
       <c r="J5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
-        <v>0.0760133595330172</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711681740744643)</f>
+        <v>0.0711681740744643</v>
       </c>
       <c r="K5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
-        <v>0.0760133595330172</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711681740744643)</f>
+        <v>0.0711681740744643</v>
       </c>
       <c r="L5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760133595330172)</f>
-        <v>0.0760133595330172</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955198022554526)</f>
+        <v>0.0955198022554526</v>
       </c>
       <c r="M5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.119933202334914)</f>
-        <v>0.119933202334914</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.119919714923173)</f>
+        <v>0.119919714923173</v>
       </c>
       <c r="N5" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""datos_base!K2:K18"")"),108842.626397553)</f>
@@ -1942,52 +1942,52 @@
         <v>110</v>
       </c>
       <c r="B6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
-        <v>0.0789430506992025</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0599939658092665)</f>
+        <v>0.0599939658092665</v>
       </c>
       <c r="C6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0965041812357258)</f>
-        <v>0.0965041812357258</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0599939658092665)</f>
+        <v>0.0599939658092665</v>
       </c>
       <c r="D6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0965041812357258)</f>
-        <v>0.0965041812357258</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0823418371052526)</f>
+        <v>0.0823418371052526</v>
       </c>
       <c r="E6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0965041812357258)</f>
-        <v>0.0965041812357258</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0958991878073455)</f>
+        <v>0.0958991878073455</v>
       </c>
       <c r="F6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
-        <v>0.0789430506992025</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10379748734495)</f>
+        <v>0.10379748734495</v>
       </c>
       <c r="G6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
-        <v>0.0789430506992025</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.102624553445736)</f>
+        <v>0.102624553445736</v>
       </c>
       <c r="H6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
-        <v>0.0789430506992025</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0742053590647476)</f>
+        <v>0.0742053590647476</v>
       </c>
       <c r="I6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
-        <v>0.0789430506992025</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0870020477881409)</f>
+        <v>0.0870020477881409</v>
       </c>
       <c r="J6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
-        <v>0.0789430506992025</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0871913152503224)</f>
+        <v>0.0871913152503224</v>
       </c>
       <c r="K6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
-        <v>0.0789430506992025</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0871913152503224)</f>
+        <v>0.0871913152503224</v>
       </c>
       <c r="L6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
-        <v>0.0789430506992025</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0792930157127176)</f>
+        <v>0.0792930157127176</v>
       </c>
       <c r="M6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789430506992025)</f>
-        <v>0.0789430506992025</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0804659496119317)</f>
+        <v>0.0804659496119317</v>
       </c>
       <c r="N6" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9216.54014430766)</f>
@@ -1998,8 +1998,8 @@
         <v>1</v>
       </c>
       <c r="P6" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),136)</f>
-        <v>136</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146)</f>
+        <v>146</v>
       </c>
       <c r="Q6" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2039,52 +2039,52 @@
         <v>111</v>
       </c>
       <c r="B7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0830536456103754)</f>
-        <v>0.0830536456103754</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0667556231939292)</f>
+        <v>0.0667556231939292</v>
       </c>
       <c r="C7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.091115822090457)</f>
-        <v>0.091115822090457</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0651024266252983)</f>
+        <v>0.0651024266252983</v>
       </c>
       <c r="D7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.091115822090457)</f>
-        <v>0.091115822090457</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0817858344236914)</f>
+        <v>0.0817858344236914</v>
       </c>
       <c r="E7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.091115822090457)</f>
-        <v>0.091115822090457</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0997196200427302)</f>
+        <v>0.0997196200427302</v>
       </c>
       <c r="F7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
-        <v>0.0800778917868397</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100089910575874)</f>
+        <v>0.100089910575874</v>
       </c>
       <c r="G7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
-        <v>0.0800778917868397</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0988243995547109)</f>
+        <v>0.0988243995547109</v>
       </c>
       <c r="H7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
-        <v>0.0800778917868397</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0797892781627565)</f>
+        <v>0.0797892781627565</v>
       </c>
       <c r="I7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
-        <v>0.0800778917868397</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0795925746996675)</f>
+        <v>0.0795925746996675</v>
       </c>
       <c r="J7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
-        <v>0.0800778917868397</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0807139532651435)</f>
+        <v>0.0807139532651435</v>
       </c>
       <c r="K7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
-        <v>0.0800778917868397</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0807139532651435)</f>
+        <v>0.0807139532651435</v>
       </c>
       <c r="L7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0800778917868397)</f>
-        <v>0.0800778917868397</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819968593006307)</f>
+        <v>0.0819968593006307</v>
       </c>
       <c r="M7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0830536456103754)</f>
-        <v>0.0830536456103754</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0849155668904246)</f>
+        <v>0.0849155668904246</v>
       </c>
       <c r="N7" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56059.2707104735)</f>
@@ -2095,8 +2095,8 @@
         <v>1</v>
       </c>
       <c r="P7" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),778)</f>
-        <v>778</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),855)</f>
+        <v>855</v>
       </c>
       <c r="Q7" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69628)</f>
@@ -2136,52 +2136,52 @@
         <v>112</v>
       </c>
       <c r="B8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
-        <v>0.078155341572415</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.064612341974598)</f>
+        <v>0.064612341974598</v>
       </c>
       <c r="C8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0988673086160884)</f>
-        <v>0.0988673086160884</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.064612341974598)</f>
+        <v>0.064612341974598</v>
       </c>
       <c r="D8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0988673086160884)</f>
-        <v>0.0988673086160884</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0831857089056497)</f>
+        <v>0.0831857089056497</v>
       </c>
       <c r="E8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0988673086160884)</f>
-        <v>0.0988673086160884</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101329540689849)</f>
+        <v>0.101329540689849</v>
       </c>
       <c r="F8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
-        <v>0.078155341572415</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10227719847342)</f>
+        <v>0.10227719847342</v>
       </c>
       <c r="G8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
-        <v>0.078155341572415</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993233886074831)</f>
+        <v>0.0993233886074831</v>
       </c>
       <c r="H8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
-        <v>0.078155341572415</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078066397641533)</f>
+        <v>0.078066397641533</v>
       </c>
       <c r="I8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
-        <v>0.078155341572415</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078743869594065)</f>
+        <v>0.078743869594065</v>
       </c>
       <c r="J8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
-        <v>0.078155341572415</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081697679460002)</f>
+        <v>0.081697679460002</v>
       </c>
       <c r="K8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
-        <v>0.078155341572415</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081697679460002)</f>
+        <v>0.081697679460002</v>
       </c>
       <c r="L8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
-        <v>0.078155341572415</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0807500216764314)</f>
+        <v>0.0807500216764314</v>
       </c>
       <c r="M8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078155341572415)</f>
-        <v>0.078155341572415</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0837038315423683)</f>
+        <v>0.0837038315423683</v>
       </c>
       <c r="N8" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3319.32790518283)</f>
@@ -2192,8 +2192,8 @@
         <v>1</v>
       </c>
       <c r="P8" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51)</f>
-        <v>51</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53)</f>
+        <v>53</v>
       </c>
       <c r="Q8" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2233,52 +2233,52 @@
         <v>113</v>
       </c>
       <c r="B9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
-        <v>0.0802492777307454</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0670768247329043)</f>
+        <v>0.0670768247329043</v>
       </c>
       <c r="C9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0925855001410971)</f>
-        <v>0.0925855001410971</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0670768247329043)</f>
+        <v>0.0670768247329043</v>
       </c>
       <c r="D9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0925855001410971)</f>
-        <v>0.0925855001410971</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0827868661277296)</f>
+        <v>0.0827868661277296</v>
       </c>
       <c r="E9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0925855001410971)</f>
-        <v>0.0925855001410971</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993493196011858)</f>
+        <v>0.0993493196011858</v>
       </c>
       <c r="F9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
-        <v>0.0802492777307454</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0999705290370024)</f>
+        <v>0.0999705290370024</v>
       </c>
       <c r="G9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
-        <v>0.0802492777307454</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0970461916480882)</f>
+        <v>0.0970461916480882</v>
       </c>
       <c r="H9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
-        <v>0.0802492777307454</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0788828581851096)</f>
+        <v>0.0788828581851096</v>
       </c>
       <c r="I9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
-        <v>0.0802492777307454</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0790330223001652)</f>
+        <v>0.0790330223001652</v>
       </c>
       <c r="J9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
-        <v>0.0802492777307454</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0817739112794073)</f>
+        <v>0.0817739112794073</v>
       </c>
       <c r="K9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
-        <v>0.0802492777307454</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0817739112794073)</f>
+        <v>0.0817739112794073</v>
       </c>
       <c r="L9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
-        <v>0.0802492777307454</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0811527018435908)</f>
+        <v>0.0811527018435908</v>
       </c>
       <c r="M9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0802492777307454)</f>
-        <v>0.0802492777307454</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.084077039232505)</f>
+        <v>0.084077039232505</v>
       </c>
       <c r="N9" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4686.14321768856)</f>
@@ -2289,8 +2289,8 @@
         <v>1</v>
       </c>
       <c r="P9" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),68)</f>
-        <v>68</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73)</f>
+        <v>73</v>
       </c>
       <c r="Q9" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2621,52 +2621,52 @@
         <v>117</v>
       </c>
       <c r="B13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
-        <v>0.0771892846953241</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0695355190499093)</f>
+        <v>0.0695355190499093</v>
       </c>
       <c r="C13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101765479247361)</f>
-        <v>0.101765479247361</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0695355190499093)</f>
+        <v>0.0695355190499093</v>
       </c>
       <c r="D13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101765479247361)</f>
-        <v>0.101765479247361</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0838248196490894)</f>
+        <v>0.0838248196490894</v>
       </c>
       <c r="E13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101765479247361)</f>
-        <v>0.101765479247361</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0948339806026096)</f>
+        <v>0.0948339806026096</v>
       </c>
       <c r="F13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
-        <v>0.0771892846953241</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0972184056200527)</f>
+        <v>0.0972184056200527</v>
       </c>
       <c r="G13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
-        <v>0.0771892846953241</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0952240073446056)</f>
+        <v>0.0952240073446056</v>
       </c>
       <c r="H13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
-        <v>0.0771892846953241</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0780009399043672)</f>
+        <v>0.0780009399043672</v>
       </c>
       <c r="I13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
-        <v>0.0771892846953241</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0813247334874215)</f>
+        <v>0.0813247334874215</v>
       </c>
       <c r="J13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
-        <v>0.0771892846953241</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833191317628686)</f>
+        <v>0.0833191317628686</v>
       </c>
       <c r="K13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
-        <v>0.0771892846953241</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833191317628686)</f>
+        <v>0.0833191317628686</v>
       </c>
       <c r="L13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
-        <v>0.0771892846953241</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809347067454255)</f>
+        <v>0.0809347067454255</v>
       </c>
       <c r="M13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771892846953241)</f>
-        <v>0.0771892846953241</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0829291050208727)</f>
+        <v>0.0829291050208727</v>
       </c>
       <c r="N13" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2310.99407344162)</f>
@@ -2677,8 +2677,8 @@
         <v>1</v>
       </c>
       <c r="P13" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37)</f>
-        <v>37</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35)</f>
+        <v>35</v>
       </c>
       <c r="Q13" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2718,52 +2718,52 @@
         <v>118</v>
       </c>
       <c r="B14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
-        <v>0.0787292505395418</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0616150736413202)</f>
+        <v>0.0616150736413202</v>
       </c>
       <c r="C14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0971455817147079)</f>
-        <v>0.0971455817147079</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0616150736413202)</f>
+        <v>0.0616150736413202</v>
       </c>
       <c r="D14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0971455817147079)</f>
-        <v>0.0971455817147079</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0829453490803136)</f>
+        <v>0.0829453490803136</v>
       </c>
       <c r="E14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0971455817147079)</f>
-        <v>0.0971455817147079</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.103007646651263)</f>
+        <v>0.103007646651263</v>
       </c>
       <c r="F14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
-        <v>0.0787292505395418</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.103425871740429)</f>
+        <v>0.103425871740429</v>
       </c>
       <c r="G14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
-        <v>0.0787292505395418</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.102109899624234)</f>
+        <v>0.102109899624234</v>
       </c>
       <c r="H14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
-        <v>0.0787292505395418</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0801282894274162)</f>
+        <v>0.0801282894274162</v>
       </c>
       <c r="I14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
-        <v>0.0787292505395418</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.079881877158212)</f>
+        <v>0.079881877158212</v>
       </c>
       <c r="J14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
-        <v>0.0787292505395418</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081197849274407)</f>
+        <v>0.081197849274407</v>
       </c>
       <c r="K14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
-        <v>0.0787292505395418</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081197849274407)</f>
+        <v>0.081197849274407</v>
       </c>
       <c r="L14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
-        <v>0.0787292505395418</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.080779624185241)</f>
+        <v>0.080779624185241</v>
       </c>
       <c r="M14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0787292505395418)</f>
-        <v>0.0787292505395418</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082095596301436)</f>
+        <v>0.082095596301436</v>
       </c>
       <c r="N14" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12606.7299522508)</f>
@@ -2774,8 +2774,8 @@
         <v>1</v>
       </c>
       <c r="P14" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),187)</f>
-        <v>187</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),199)</f>
+        <v>199</v>
       </c>
       <c r="Q14" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2815,52 +2815,52 @@
         <v>119</v>
       </c>
       <c r="B15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
-        <v>0.0826992607152812</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0761848278176029)</f>
+        <v>0.0761848278176029</v>
       </c>
       <c r="C15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0852355511874899)</f>
-        <v>0.0852355511874899</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0761848278176029)</f>
+        <v>0.0761848278176029</v>
       </c>
       <c r="D15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0852355511874899)</f>
-        <v>0.0852355511874899</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826686065765467)</f>
+        <v>0.0826686065765467</v>
       </c>
       <c r="E15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0852355511874899)</f>
-        <v>0.0852355511874899</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0916518877640263)</f>
+        <v>0.0916518877640263</v>
       </c>
       <c r="F15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
-        <v>0.0826992607152812</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0931955183643168)</f>
+        <v>0.0931955183643168</v>
       </c>
       <c r="G15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
-        <v>0.0826992607152812</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0888541224858191)</f>
+        <v>0.0888541224858191</v>
       </c>
       <c r="H15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
-        <v>0.0826992607152812</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0784912986070083)</f>
+        <v>0.0784912986070083</v>
       </c>
       <c r="I15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
-        <v>0.0826992607152812</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0795725784486681)</f>
+        <v>0.0795725784486681</v>
       </c>
       <c r="J15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
-        <v>0.0826992607152812</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0829855493601231)</f>
+        <v>0.0829855493601231</v>
       </c>
       <c r="K15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
-        <v>0.0826992607152812</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0829855493601231)</f>
+        <v>0.0829855493601231</v>
       </c>
       <c r="L15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
-        <v>0.0826992607152812</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0814419187598326)</f>
+        <v>0.0814419187598326</v>
       </c>
       <c r="M15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826992607152812)</f>
-        <v>0.0826992607152812</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0857833146383303)</f>
+        <v>0.0857833146383303</v>
       </c>
       <c r="N15" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4308.38387982745)</f>
@@ -2871,8 +2871,8 @@
         <v>1</v>
       </c>
       <c r="P15" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58)</f>
-        <v>58</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64)</f>
+        <v>64</v>
       </c>
       <c r="Q15" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -2912,12 +2912,12 @@
         <v>120</v>
       </c>
       <c r="B16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0890943915723948)</f>
+        <v>0.0890943915723948</v>
       </c>
       <c r="C16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0890943915723948)</f>
+        <v>0.0890943915723948</v>
       </c>
       <c r="D16" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
@@ -2932,16 +2932,16 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="G16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0775722750942719)</f>
+        <v>0.0775722750942719</v>
       </c>
       <c r="H16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0775722750942719)</f>
+        <v>0.0775722750942719</v>
       </c>
       <c r="I16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0775722750942719)</f>
+        <v>0.0775722750942719</v>
       </c>
       <c r="J16" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
@@ -2956,8 +2956,8 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="M16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0890943915723948)</f>
+        <v>0.0890943915723948</v>
       </c>
       <c r="N16" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),705.316446113659)</f>
@@ -2968,8 +2968,8 @@
         <v>1</v>
       </c>
       <c r="P16" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10)</f>
-        <v>10</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11)</f>
+        <v>11</v>
       </c>
       <c r="Q16" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -3106,52 +3106,52 @@
         <v>122</v>
       </c>
       <c r="B18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
-        <v>0.0822850273487674</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741713639081832)</f>
+        <v>0.0741713639081832</v>
       </c>
       <c r="C18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864782512870313)</f>
-        <v>0.0864782512870313</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741713639081832)</f>
+        <v>0.0741713639081832</v>
       </c>
       <c r="D18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864782512870313)</f>
-        <v>0.0864782512870313</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826308825789044)</f>
+        <v>0.0826308825789044</v>
       </c>
       <c r="E18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864782512870313)</f>
-        <v>0.0864782512870313</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0938477438743188)</f>
+        <v>0.0938477438743188</v>
       </c>
       <c r="F18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
-        <v>0.0822850273487674</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0943031990696216)</f>
+        <v>0.0943031990696216</v>
       </c>
       <c r="G18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
-        <v>0.0822850273487674</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905972862319092)</f>
+        <v>0.0905972862319092</v>
       </c>
       <c r="H18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
-        <v>0.0822850273487674</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782229570370311)</f>
+        <v>0.0782229570370311</v>
       </c>
       <c r="I18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
-        <v>0.0822850273487674</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0788873099187785)</f>
+        <v>0.0788873099187785</v>
       </c>
       <c r="J18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
-        <v>0.0822850273487674</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0825932227564908)</f>
+        <v>0.0825932227564908</v>
       </c>
       <c r="K18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
-        <v>0.0822850273487674</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0825932227564908)</f>
+        <v>0.0825932227564908</v>
       </c>
       <c r="L18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
-        <v>0.0822850273487674</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082137767561188)</f>
+        <v>0.082137767561188</v>
       </c>
       <c r="M18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822850273487674)</f>
-        <v>0.0822850273487674</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0858436803989003)</f>
+        <v>0.0858436803989003</v>
       </c>
       <c r="N18" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),577.776131502584)</f>
@@ -3162,8 +3162,8 @@
         <v>1</v>
       </c>
       <c r="P18" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8)</f>
-        <v>8</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9)</f>
+        <v>9</v>
       </c>
       <c r="Q18" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -3203,52 +3203,52 @@
         <v>123</v>
       </c>
       <c r="B19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
-        <v>0.0822848847558399</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741714575622674)</f>
+        <v>0.0741714575622674</v>
       </c>
       <c r="C19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864786790658138)</f>
-        <v>0.0864786790658138</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741714575622674)</f>
+        <v>0.0741714575622674</v>
       </c>
       <c r="D19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864786790658138)</f>
-        <v>0.0864786790658138</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08263095051887)</f>
+        <v>0.08263095051887</v>
       </c>
       <c r="E19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864786790658138)</f>
-        <v>0.0864786790658138</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0938477343304375)</f>
+        <v>0.0938477343304375</v>
       </c>
       <c r="F19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
-        <v>0.0822848847558399</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0943030721576538)</f>
+        <v>0.0943030721576538</v>
       </c>
       <c r="G19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
-        <v>0.0822848847558399</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905972613831472)</f>
+        <v>0.0905972613831472</v>
       </c>
       <c r="H19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
-        <v>0.0822848847558399</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782232108709845)</f>
+        <v>0.0782232108709845</v>
       </c>
       <c r="I19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
-        <v>0.0822848847558399</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0788872954792544)</f>
+        <v>0.0788872954792544</v>
       </c>
       <c r="J19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
-        <v>0.0822848847558399</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082593106253761)</f>
+        <v>0.082593106253761</v>
       </c>
       <c r="K19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
-        <v>0.0822848847558399</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082593106253761)</f>
+        <v>0.082593106253761</v>
       </c>
       <c r="L19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
-        <v>0.0822848847558399</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0821377684265447)</f>
+        <v>0.0821377684265447</v>
       </c>
       <c r="M19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822848847558399)</f>
-        <v>0.0822848847558399</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0858435792010512)</f>
+        <v>0.0858435792010512</v>
       </c>
       <c r="N19" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1271.10748852936)</f>
@@ -3259,8 +3259,8 @@
         <v>1</v>
       </c>
       <c r="P19" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18)</f>
-        <v>18</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19)</f>
+        <v>19</v>
       </c>
       <c r="Q19" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -3300,52 +3300,52 @@
         <v>124</v>
       </c>
       <c r="B20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
-        <v>0.0822852002059122</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741714711262728)</f>
+        <v>0.0741714711262728</v>
       </c>
       <c r="C20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864777327155967)</f>
-        <v>0.0864777327155967</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741714711262728)</f>
+        <v>0.0741714711262728</v>
       </c>
       <c r="D20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864777327155967)</f>
-        <v>0.0864777327155967</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826308668449537)</f>
+        <v>0.0826308668449537</v>
       </c>
       <c r="E20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864777327155967)</f>
-        <v>0.0864777327155967</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0938479481909226)</f>
+        <v>0.0938479481909226</v>
       </c>
       <c r="F20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
-        <v>0.0822852002059122</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0943030828496681)</f>
+        <v>0.0943030828496681</v>
       </c>
       <c r="G20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
-        <v>0.0822852002059122</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905972288565807)</f>
+        <v>0.0905972288565807</v>
       </c>
       <c r="H20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
-        <v>0.0822852002059122</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782233613395939)</f>
+        <v>0.0782233613395939</v>
       </c>
       <c r="I20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
-        <v>0.0822852002059122</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0788871138035579)</f>
+        <v>0.0788871138035579</v>
       </c>
       <c r="J20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
-        <v>0.0822852002059122</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0825929677966453)</f>
+        <v>0.0825929677966453</v>
       </c>
       <c r="K20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
-        <v>0.0822852002059122</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0825929677966453)</f>
+        <v>0.0825929677966453</v>
       </c>
       <c r="L20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
-        <v>0.0822852002059122</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0821378331378998)</f>
+        <v>0.0821378331378998</v>
       </c>
       <c r="M20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0822852002059122)</f>
-        <v>0.0822852002059122</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0858436871309872)</f>
+        <v>0.0858436871309872</v>
       </c>
       <c r="N20" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.332543143421)</f>
@@ -3356,8 +3356,8 @@
         <v>1</v>
       </c>
       <c r="P20" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4)</f>
-        <v>4</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5)</f>
+        <v>5</v>
       </c>
       <c r="Q20" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -3397,52 +3397,52 @@
         <v>125</v>
       </c>
       <c r="B21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
-        <v>0.082284103832348</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741721346584101)</f>
+        <v>0.0741721346584101</v>
       </c>
       <c r="C21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864810218362894)</f>
-        <v>0.0864810218362894</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741721346584101)</f>
+        <v>0.0741721346584101</v>
       </c>
       <c r="D21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864810218362894)</f>
-        <v>0.0864810218362894</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826312550911103)</f>
+        <v>0.0826312550911103</v>
       </c>
       <c r="E21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864810218362894)</f>
-        <v>0.0864810218362894</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0938475454254633)</f>
+        <v>0.0938475454254633</v>
       </c>
       <c r="F21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
-        <v>0.082284103832348</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0943026800842088)</f>
+        <v>0.0943026800842088</v>
       </c>
       <c r="G21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
-        <v>0.082284103832348</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905968260911214)</f>
+        <v>0.0905968260911214</v>
       </c>
       <c r="H21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
-        <v>0.082284103832348</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782234917229329)</f>
+        <v>0.0782234917229329</v>
       </c>
       <c r="I21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
-        <v>0.082284103832348</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0788869863240794)</f>
+        <v>0.0788869863240794</v>
       </c>
       <c r="J21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
-        <v>0.082284103832348</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0825928403171668)</f>
+        <v>0.0825928403171668</v>
       </c>
       <c r="K21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
-        <v>0.082284103832348</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0825928403171668)</f>
+        <v>0.0825928403171668</v>
       </c>
       <c r="L21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
-        <v>0.082284103832348</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0821377056584213)</f>
+        <v>0.0821377056584213</v>
       </c>
       <c r="M21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082284103832348)</f>
-        <v>0.082284103832348</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0858435596515087)</f>
+        <v>0.0858435596515087</v>
       </c>
       <c r="N21" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),184.888361725934)</f>
@@ -3494,52 +3494,52 @@
         <v>126</v>
       </c>
       <c r="B22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101848800284409)</f>
-        <v>0.101848800284409</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.094685974590863)</f>
+        <v>0.094685974590863</v>
       </c>
       <c r="C22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0837602978170431)</f>
-        <v>0.0837602978170431</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0813589828439731)</f>
+        <v>0.0813589828439731</v>
       </c>
       <c r="D22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0837602978170431)</f>
-        <v>0.0837602978170431</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0763711312806997)</f>
+        <v>0.0763711312806997</v>
       </c>
       <c r="E22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0837602978170431)</f>
-        <v>0.0837602978170431</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.084183445923961)</f>
+        <v>0.084183445923961</v>
       </c>
       <c r="F22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
-        <v>0.0778602151400075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0847815688752799)</f>
+        <v>0.0847815688752799</v>
       </c>
       <c r="G22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
-        <v>0.0778602151400075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0840164331631308)</f>
+        <v>0.0840164331631308</v>
       </c>
       <c r="H22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
-        <v>0.0778602151400075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0748812526033842)</f>
+        <v>0.0748812526033842</v>
       </c>
       <c r="I22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
-        <v>0.0778602151400075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0755102802186843)</f>
+        <v>0.0755102802186843</v>
       </c>
       <c r="J22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
-        <v>0.0778602151400075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0761652663624608)</f>
+        <v>0.0761652663624608</v>
       </c>
       <c r="K22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
-        <v>0.0778602151400075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0761652663624608)</f>
+        <v>0.0761652663624608</v>
       </c>
       <c r="L22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0778602151400075)</f>
-        <v>0.0778602151400075</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0888941351580317)</f>
+        <v>0.0888941351580317</v>
       </c>
       <c r="M22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101848800284409)</f>
-        <v>0.101848800284409</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.102986262617071)</f>
+        <v>0.102986262617071</v>
       </c>
       <c r="N22" s="7" t="n">
         <f aca="false">SUM(N5:N21)</f>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="P22" s="7" t="n">
         <f aca="false">SUM(P5:P21)</f>
-        <v>1384</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3651,44 +3651,44 @@
         <v>0.12</v>
       </c>
       <c r="C28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955555555555556)</f>
+        <v>0.0955555555555556</v>
       </c>
       <c r="D28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="E28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="F28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="G28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="H28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="I28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="J28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="K28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="L28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955555555555556)</f>
+        <v>0.0955555555555556</v>
       </c>
       <c r="M28" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.12)</f>
@@ -3700,52 +3700,52 @@
         <v>102</v>
       </c>
       <c r="B29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0540540540540541)</f>
+        <v>0.0540540540540541</v>
       </c>
       <c r="C29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0540540540540541)</f>
+        <v>0.0540540540540541</v>
       </c>
       <c r="D29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
+        <v>0.0810810810810811</v>
       </c>
       <c r="E29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.108108108108108)</f>
+        <v>0.108108108108108</v>
       </c>
       <c r="F29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.108108108108108)</f>
+        <v>0.108108108108108</v>
       </c>
       <c r="G29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.108108108108108)</f>
+        <v>0.108108108108108</v>
       </c>
       <c r="H29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
+        <v>0.0810810810810811</v>
       </c>
       <c r="I29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
+        <v>0.0810810810810811</v>
       </c>
       <c r="J29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
+        <v>0.0810810810810811</v>
       </c>
       <c r="K29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
+        <v>0.0810810810810811</v>
       </c>
       <c r="L29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
+        <v>0.0810810810810811</v>
       </c>
       <c r="M29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
+        <v>0.0810810810810811</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3753,52 +3753,52 @@
         <v>103</v>
       </c>
       <c r="B30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
-        <v>0.0295134514379623</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10126582278481)</f>
+        <v>0.10126582278481</v>
       </c>
       <c r="C30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.244792979019447)</f>
-        <v>0.244792979019447</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10126582278481)</f>
+        <v>0.10126582278481</v>
       </c>
       <c r="D30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.244792979019447)</f>
-        <v>0.244792979019447</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10126582278481)</f>
+        <v>0.10126582278481</v>
       </c>
       <c r="E30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.244792979019447)</f>
-        <v>0.244792979019447</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
       <c r="F30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
-        <v>0.0295134514379623</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
       <c r="G30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
-        <v>0.0295134514379623</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
       <c r="H30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
-        <v>0.0295134514379623</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0886075949367089)</f>
+        <v>0.0886075949367089</v>
       </c>
       <c r="I30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
-        <v>0.0295134514379623</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
       <c r="J30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
-        <v>0.0295134514379623</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
       <c r="K30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
-        <v>0.0295134514379623</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
       <c r="L30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
-        <v>0.0295134514379623</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
       <c r="M30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0295134514379623)</f>
-        <v>0.0295134514379623</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3806,52 +3806,52 @@
         <v>104</v>
       </c>
       <c r="B31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0526315789473684)</f>
+        <v>0.0526315789473684</v>
       </c>
       <c r="C31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0526315789473684)</f>
+        <v>0.0526315789473684</v>
       </c>
       <c r="D31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
+        <v>0.0789473684210526</v>
       </c>
       <c r="E31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
+        <v>0.0789473684210526</v>
       </c>
       <c r="F31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
+        <v>0.105263157894737</v>
       </c>
       <c r="G31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
+        <v>0.105263157894737</v>
       </c>
       <c r="H31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0526315789473684)</f>
+        <v>0.0526315789473684</v>
       </c>
       <c r="I31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
+        <v>0.105263157894737</v>
       </c>
       <c r="J31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
+        <v>0.105263157894737</v>
       </c>
       <c r="K31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
+        <v>0.105263157894737</v>
       </c>
       <c r="L31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
+        <v>0.0789473684210526</v>
       </c>
       <c r="M31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
+        <v>0.0789473684210526</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3912,12 +3912,12 @@
         <v>106</v>
       </c>
       <c r="B33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
+        <v>0.111111111111111</v>
       </c>
       <c r="C33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
+        <v>0.111111111111111</v>
       </c>
       <c r="D33" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
@@ -3932,16 +3932,16 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="G33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
+        <v>0.0555555555555556</v>
       </c>
       <c r="H33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
+        <v>0.0555555555555556</v>
       </c>
       <c r="I33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
+        <v>0.0555555555555556</v>
       </c>
       <c r="J33" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
@@ -3956,8 +3956,8 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="M33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
+        <v>0.111111111111111</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3965,12 +3965,12 @@
         <v>107</v>
       </c>
       <c r="B34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
+        <v>0.0555555555555556</v>
       </c>
       <c r="C34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
+        <v>0.0555555555555556</v>
       </c>
       <c r="D34" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
@@ -3981,20 +3981,20 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="F34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
+        <v>0.111111111111111</v>
       </c>
       <c r="G34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
+        <v>0.111111111111111</v>
       </c>
       <c r="H34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
+        <v>0.111111111111111</v>
       </c>
       <c r="I34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
+        <v>0.111111111111111</v>
       </c>
       <c r="J34" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
@@ -4005,12 +4005,12 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="L34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
+        <v>0.0555555555555556</v>
       </c>
       <c r="M34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
+        <v>0.0555555555555556</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4097,52 +4097,52 @@
         <v>109</v>
       </c>
       <c r="B39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""parametros_recargas!E55:P72"")"),0.119942566698092)</f>
-        <v>0.119942566698092</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""parametros_recargas!E55:P72"")"),0.119895289559294)</f>
+        <v>0.119895289559294</v>
       </c>
       <c r="C39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
-        <v>0.0760114866603815</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0954891339827875)</f>
+        <v>0.0954891339827875</v>
       </c>
       <c r="D39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
-        <v>0.0760114866603815</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.071124604952686)</f>
+        <v>0.071124604952686</v>
       </c>
       <c r="E39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
-        <v>0.0760114866603815</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.071124604952686)</f>
+        <v>0.071124604952686</v>
       </c>
       <c r="F39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
-        <v>0.0760114866603815</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711662314990906)</f>
+        <v>0.0711662314990906</v>
       </c>
       <c r="G39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
-        <v>0.0760114866603815</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711662314990906)</f>
+        <v>0.0711662314990906</v>
       </c>
       <c r="H39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
-        <v>0.0760114866603815</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0710984243903592)</f>
+        <v>0.0710984243903592</v>
       </c>
       <c r="I39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
-        <v>0.0760114866603815</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711662314990906)</f>
+        <v>0.0711662314990906</v>
       </c>
       <c r="J39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
-        <v>0.0760114866603815</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711585085070517)</f>
+        <v>0.0711585085070517</v>
       </c>
       <c r="K39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
-        <v>0.0760114866603815</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711585085070517)</f>
+        <v>0.0711585085070517</v>
       </c>
       <c r="L39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0760114866603815)</f>
-        <v>0.0760114866603815</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955230375371532)</f>
+        <v>0.0955230375371532</v>
       </c>
       <c r="M39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.119942566698092)</f>
-        <v>0.119942566698092</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.119929193113659)</f>
+        <v>0.119929193113659</v>
       </c>
       <c r="N39" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""datos_base!K2:K18"")"),56575.8368575054)</f>
@@ -4194,52 +4194,52 @@
         <v>110</v>
       </c>
       <c r="B40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
-        <v>0.0779725990367327</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0608346558815601)</f>
+        <v>0.0608346558815601</v>
       </c>
       <c r="C40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994155362231353)</f>
-        <v>0.0994155362231353</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0608346558815601)</f>
+        <v>0.0608346558815601</v>
       </c>
       <c r="D40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994155362231353)</f>
-        <v>0.0994155362231353</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082643351275423)</f>
+        <v>0.082643351275423</v>
       </c>
       <c r="E40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994155362231353)</f>
-        <v>0.0994155362231353</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0953382202836263)</f>
+        <v>0.0953382202836263</v>
       </c>
       <c r="F40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
-        <v>0.0779725990367327</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.103308847602848)</f>
+        <v>0.103308847602848</v>
       </c>
       <c r="G40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
-        <v>0.0779725990367327</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10204440072004)</f>
+        <v>0.10204440072004</v>
       </c>
       <c r="H40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
-        <v>0.0779725990367327</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0745034484311485)</f>
+        <v>0.0745034484311485</v>
       </c>
       <c r="I40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
-        <v>0.0779725990367327</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0869418857625907)</f>
+        <v>0.0869418857625907</v>
       </c>
       <c r="J40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
-        <v>0.0779725990367327</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0870568354792096)</f>
+        <v>0.0870568354792096</v>
       </c>
       <c r="K40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
-        <v>0.0779725990367327</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0870568354792096)</f>
+        <v>0.0870568354792096</v>
       </c>
       <c r="L40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
-        <v>0.0779725990367327</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0790862081599875)</f>
+        <v>0.0790862081599875</v>
       </c>
       <c r="M40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0779725990367327)</f>
-        <v>0.0779725990367327</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.080350655042796)</f>
+        <v>0.080350655042796</v>
       </c>
       <c r="N40" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4790.71011839089)</f>
@@ -4250,8 +4250,8 @@
         <v>1</v>
       </c>
       <c r="P40" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73)</f>
-        <v>73</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76)</f>
+        <v>76</v>
       </c>
       <c r="Q40" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -4291,52 +4291,52 @@
         <v>111</v>
       </c>
       <c r="B41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824116289014618)</f>
-        <v>0.0824116289014618</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0669778155176287)</f>
+        <v>0.0669778155176287</v>
       </c>
       <c r="C41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0933072507565163)</f>
-        <v>0.0933072507565163</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0652614335824934)</f>
+        <v>0.0652614335824934</v>
       </c>
       <c r="D41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0933072507565163)</f>
-        <v>0.0933072507565163</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819248891202413)</f>
+        <v>0.0819248891202413</v>
       </c>
       <c r="E41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0933072507565163)</f>
-        <v>0.0933072507565163</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0996461832727322)</f>
+        <v>0.0996461832727322</v>
       </c>
       <c r="F41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
-        <v>0.0793221414182182</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100150076298148)</f>
+        <v>0.100150076298148</v>
       </c>
       <c r="G41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
-        <v>0.0793221414182182</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0987344570187928)</f>
+        <v>0.0987344570187928</v>
       </c>
       <c r="H41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
-        <v>0.0793221414182182</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0795692614778467)</f>
+        <v>0.0795692614778467</v>
       </c>
       <c r="I41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
-        <v>0.0793221414182182</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0794428932919701)</f>
+        <v>0.0794428932919701</v>
       </c>
       <c r="J41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
-        <v>0.0793221414182182</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0806840028465543)</f>
+        <v>0.0806840028465543</v>
       </c>
       <c r="K41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
-        <v>0.0793221414182182</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0806840028465543)</f>
+        <v>0.0806840028465543</v>
       </c>
       <c r="L41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793221414182182)</f>
-        <v>0.0793221414182182</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0818964917562743)</f>
+        <v>0.0818964917562743</v>
       </c>
       <c r="M41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824116289014618)</f>
-        <v>0.0824116289014618</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0850284929707643)</f>
+        <v>0.0850284929707643</v>
       </c>
       <c r="N41" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29139.3203107948)</f>
@@ -4347,8 +4347,8 @@
         <v>1</v>
       </c>
       <c r="P41" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),415)</f>
-        <v>415</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),446)</f>
+        <v>446</v>
       </c>
       <c r="Q41" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36760)</f>
@@ -4388,52 +4388,52 @@
         <v>112</v>
       </c>
       <c r="B42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
-        <v>0.0770946445386376</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0656624516770873)</f>
+        <v>0.0656624516770873</v>
       </c>
       <c r="C42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10204939971742)</f>
-        <v>0.10204939971742</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0656624516770873)</f>
+        <v>0.0656624516770873</v>
       </c>
       <c r="D42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10204939971742)</f>
-        <v>0.10204939971742</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0834634227222184)</f>
+        <v>0.0834634227222184</v>
       </c>
       <c r="E42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10204939971742)</f>
-        <v>0.10204939971742</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100292059397134)</f>
+        <v>0.100292059397134</v>
       </c>
       <c r="F42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
-        <v>0.0770946445386376</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101604548245527)</f>
+        <v>0.101604548245527</v>
       </c>
       <c r="G42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
-        <v>0.0770946445386376</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0984624354955731)</f>
+        <v>0.0984624354955731</v>
       </c>
       <c r="H42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
-        <v>0.0770946445386376</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776078419879838)</f>
+        <v>0.0776078419879838</v>
       </c>
       <c r="I42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
-        <v>0.0770946445386376</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0788318405488818)</f>
+        <v>0.0788318405488818</v>
       </c>
       <c r="J42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
-        <v>0.0770946445386376</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819739532988352)</f>
+        <v>0.0819739532988352</v>
       </c>
       <c r="K42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
-        <v>0.0770946445386376</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819739532988352)</f>
+        <v>0.0819739532988352</v>
       </c>
       <c r="L42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
-        <v>0.0770946445386376</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0806614644504421)</f>
+        <v>0.0806614644504421</v>
       </c>
       <c r="M42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0770946445386376)</f>
-        <v>0.0770946445386376</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0838035772003955)</f>
+        <v>0.0838035772003955</v>
       </c>
       <c r="N42" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1725.36955653994)</f>
@@ -4485,52 +4485,52 @@
         <v>113</v>
       </c>
       <c r="B43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
-        <v>0.0793823941427303</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0671288961017088)</f>
+        <v>0.0671288961017088</v>
       </c>
       <c r="C43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0951861509051423)</f>
-        <v>0.0951861509051423</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0671288961017088)</f>
+        <v>0.0671288961017088</v>
       </c>
       <c r="D43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0951861509051423)</f>
-        <v>0.0951861509051423</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082960331994099)</f>
+        <v>0.082960331994099</v>
       </c>
       <c r="E43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0951861509051423)</f>
-        <v>0.0951861509051423</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994555948834204)</f>
+        <v>0.0994555948834204</v>
       </c>
       <c r="F43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
-        <v>0.0793823941427303</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100324801949947)</f>
+        <v>0.100324801949947</v>
       </c>
       <c r="G43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
-        <v>0.0793823941427303</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0970172977837637)</f>
+        <v>0.0970172977837637</v>
       </c>
       <c r="H43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
-        <v>0.0793823941427303</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0783455208911489)</f>
+        <v>0.0783455208911489</v>
       </c>
       <c r="I43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
-        <v>0.0793823941427303</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078747564791717)</f>
+        <v>0.078747564791717</v>
       </c>
       <c r="J43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
-        <v>0.0793823941427303</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0818305013673391)</f>
+        <v>0.0818305013673391</v>
       </c>
       <c r="K43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
-        <v>0.0793823941427303</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0818305013673391)</f>
+        <v>0.0818305013673391</v>
       </c>
       <c r="L43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
-        <v>0.0793823941427303</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809612943008125)</f>
+        <v>0.0809612943008125</v>
       </c>
       <c r="M43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793823941427303)</f>
-        <v>0.0793823941427303</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0842687984669957)</f>
+        <v>0.0842687984669957</v>
       </c>
       <c r="N43" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2435.83311933763)</f>
@@ -4541,8 +4541,8 @@
         <v>1</v>
       </c>
       <c r="P43" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37)</f>
-        <v>37</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39)</f>
+        <v>39</v>
       </c>
       <c r="Q43" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -4873,52 +4873,52 @@
         <v>117</v>
       </c>
       <c r="B47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
-        <v>0.0758238813821944</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0693955234457278)</f>
+        <v>0.0693955234457278</v>
       </c>
       <c r="C47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10586168918675)</f>
-        <v>0.10586168918675</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0693955234457278)</f>
+        <v>0.0693955234457278</v>
       </c>
       <c r="D47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10586168918675)</f>
-        <v>0.10586168918675</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0840431757641277)</f>
+        <v>0.0840431757641277</v>
       </c>
       <c r="E47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10586168918675)</f>
-        <v>0.10586168918675</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0941202036639783)</f>
+        <v>0.0941202036639783</v>
       </c>
       <c r="F47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
-        <v>0.0758238813821944</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0974702272576739)</f>
+        <v>0.0974702272576739</v>
       </c>
       <c r="G47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
-        <v>0.0758238813821944</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.095318136848291)</f>
+        <v>0.095318136848291</v>
       </c>
       <c r="H47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
-        <v>0.0758238813821944</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076854716143931)</f>
+        <v>0.076854716143931</v>
       </c>
       <c r="I47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
-        <v>0.0758238813821944</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0818684177142039)</f>
+        <v>0.0818684177142039</v>
       </c>
       <c r="J47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
-        <v>0.0758238813821944</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0840205081235868)</f>
+        <v>0.0840205081235868</v>
       </c>
       <c r="K47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
-        <v>0.0758238813821944</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0840205081235868)</f>
+        <v>0.0840205081235868</v>
       </c>
       <c r="L47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
-        <v>0.0758238813821944</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0806704845298912)</f>
+        <v>0.0806704845298912</v>
       </c>
       <c r="M47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758238813821944)</f>
-        <v>0.0758238813821944</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082822574939274)</f>
+        <v>0.082822574939274</v>
       </c>
       <c r="N47" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1201.24282190818)</f>
@@ -4929,8 +4929,8 @@
         <v>1</v>
       </c>
       <c r="P47" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20)</f>
-        <v>20</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19)</f>
+        <v>19</v>
       </c>
       <c r="Q47" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -4970,52 +4970,52 @@
         <v>118</v>
       </c>
       <c r="B48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
-        <v>0.0776565294661689</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0623734752667158)</f>
+        <v>0.0623734752667158</v>
       </c>
       <c r="C48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100363744934826)</f>
-        <v>0.100363744934826</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0623734752667158)</f>
+        <v>0.0623734752667158</v>
       </c>
       <c r="D48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100363744934826)</f>
-        <v>0.100363744934826</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0832322896847601)</f>
+        <v>0.0832322896847601</v>
       </c>
       <c r="E48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100363744934826)</f>
-        <v>0.100363744934826</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.102381291624983)</f>
+        <v>0.102381291624983</v>
       </c>
       <c r="F48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
-        <v>0.0776565294661689</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10297405651463)</f>
+        <v>0.10297405651463</v>
       </c>
       <c r="G48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
-        <v>0.0776565294661689</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101541503044586)</f>
+        <v>0.101541503044586</v>
       </c>
       <c r="H48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
-        <v>0.0776565294661689</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0799321707959588)</f>
+        <v>0.0799321707959588</v>
       </c>
       <c r="I48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
-        <v>0.0776565294661689</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0798429000461445)</f>
+        <v>0.0798429000461445</v>
       </c>
       <c r="J48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
-        <v>0.0776565294661689</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081275453516189)</f>
+        <v>0.081275453516189</v>
       </c>
       <c r="K48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
-        <v>0.0776565294661689</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081275453516189)</f>
+        <v>0.081275453516189</v>
       </c>
       <c r="L48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
-        <v>0.0776565294661689</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0806826886265415)</f>
+        <v>0.0806826886265415</v>
       </c>
       <c r="M48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776565294661689)</f>
-        <v>0.0776565294661689</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0821152420965861)</f>
+        <v>0.0821152420965861</v>
       </c>
       <c r="N48" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6552.91332717418)</f>
@@ -5026,8 +5026,8 @@
         <v>1</v>
       </c>
       <c r="P48" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101)</f>
-        <v>101</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103)</f>
+        <v>103</v>
       </c>
       <c r="Q48" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -5067,52 +5067,52 @@
         <v>119</v>
       </c>
       <c r="B49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
-        <v>0.0824962815446097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758899515991334)</f>
+        <v>0.0758899515991334</v>
       </c>
       <c r="C49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0858444886995043)</f>
-        <v>0.0858444886995043</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758899515991334)</f>
+        <v>0.0758899515991334</v>
       </c>
       <c r="D49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0858444886995043)</f>
-        <v>0.0858444886995043</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082635648810499)</f>
+        <v>0.082635648810499</v>
       </c>
       <c r="E49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0858444886995043)</f>
-        <v>0.0858444886995043</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0919604223371936)</f>
+        <v>0.0919604223371936</v>
       </c>
       <c r="F49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
-        <v>0.0824962815446097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.094065383152575)</f>
+        <v>0.094065383152575</v>
       </c>
       <c r="G49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
-        <v>0.0824962815446097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0890054041756688)</f>
+        <v>0.0890054041756688</v>
       </c>
       <c r="H49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
-        <v>0.0824962815446097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776256551320905)</f>
+        <v>0.0776256551320905</v>
       </c>
       <c r="I49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
-        <v>0.0824962815446097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793046888027784)</f>
+        <v>0.0793046888027784</v>
       </c>
       <c r="J49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
-        <v>0.0824962815446097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0831932092611961)</f>
+        <v>0.0831932092611961</v>
       </c>
       <c r="K49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
-        <v>0.0824962815446097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0831932092611961)</f>
+        <v>0.0831932092611961</v>
       </c>
       <c r="L49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
-        <v>0.0824962815446097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810882484458147)</f>
+        <v>0.0810882484458147</v>
       </c>
       <c r="M49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0824962815446097)</f>
-        <v>0.0824962815446097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0861482274227209)</f>
+        <v>0.0861482274227209</v>
       </c>
       <c r="N49" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2239.47576029921)</f>
@@ -5123,8 +5123,8 @@
         <v>1</v>
       </c>
       <c r="P49" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31)</f>
-        <v>31</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34)</f>
+        <v>34</v>
       </c>
       <c r="Q49" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -5164,12 +5164,12 @@
         <v>120</v>
       </c>
       <c r="B50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0909796762566006)</f>
+        <v>0.0909796762566006</v>
       </c>
       <c r="C50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0909796762566006)</f>
+        <v>0.0909796762566006</v>
       </c>
       <c r="D50" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
@@ -5184,16 +5184,16 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="G50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0756869904100661)</f>
+        <v>0.0756869904100661</v>
       </c>
       <c r="H50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0756869904100661)</f>
+        <v>0.0756869904100661</v>
       </c>
       <c r="I50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0756869904100661)</f>
+        <v>0.0756869904100661</v>
       </c>
       <c r="J50" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
@@ -5208,8 +5208,8 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="M50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0909796762566006)</f>
+        <v>0.0909796762566006</v>
       </c>
       <c r="N50" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),366.61985757759)</f>
@@ -5358,52 +5358,52 @@
         <v>122</v>
       </c>
       <c r="B52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
-        <v>0.0819169643322097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738143198706873)</f>
+        <v>0.0738143198706873</v>
       </c>
       <c r="C52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875824403367042)</f>
-        <v>0.0875824403367042</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738143198706873)</f>
+        <v>0.0738143198706873</v>
       </c>
       <c r="D52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875824403367042)</f>
-        <v>0.0875824403367042</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826227624746291)</f>
+        <v>0.0826227624746291</v>
       </c>
       <c r="E52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875824403367042)</f>
-        <v>0.0875824403367042</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0945064091827231)</f>
+        <v>0.0945064091827231</v>
       </c>
       <c r="F52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
-        <v>0.0819169643322097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0952134923111048)</f>
+        <v>0.0952134923111048</v>
       </c>
       <c r="G52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
-        <v>0.0819169643322097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0907950767238501)</f>
+        <v>0.0907950767238501</v>
       </c>
       <c r="H52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
-        <v>0.0819169643322097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771791995816322)</f>
+        <v>0.0771791995816322</v>
       </c>
       <c r="I52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
-        <v>0.0819169643322097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782753016610352)</f>
+        <v>0.0782753016610352</v>
       </c>
       <c r="J52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
-        <v>0.0819169643322097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826937172482899)</f>
+        <v>0.0826937172482899</v>
       </c>
       <c r="K52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
-        <v>0.0819169643322097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826937172482899)</f>
+        <v>0.0826937172482899</v>
       </c>
       <c r="L52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
-        <v>0.0819169643322097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819866341199082)</f>
+        <v>0.0819866341199082</v>
       </c>
       <c r="M52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819169643322097)</f>
-        <v>0.0819169643322097</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864050497071629)</f>
+        <v>0.0864050497071629</v>
       </c>
       <c r="N52" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),300.325058646191)</f>
@@ -5455,52 +5455,52 @@
         <v>123</v>
       </c>
       <c r="B53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
-        <v>0.0819175760181933</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738141230528446)</f>
+        <v>0.0738141230528446</v>
       </c>
       <c r="C53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875806052787535)</f>
-        <v>0.0875806052787535</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738141230528446)</f>
+        <v>0.0738141230528446</v>
       </c>
       <c r="D53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875806052787535)</f>
-        <v>0.0875806052787535</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826225891766349)</f>
+        <v>0.0826225891766349</v>
       </c>
       <c r="E53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875806052787535)</f>
-        <v>0.0875806052787535</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0945068249706181)</f>
+        <v>0.0945068249706181</v>
       </c>
       <c r="F53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
-        <v>0.0819175760181933</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0952136231283829)</f>
+        <v>0.0952136231283829</v>
       </c>
       <c r="G53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
-        <v>0.0819175760181933</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0907952016698743)</f>
+        <v>0.0907952016698743</v>
       </c>
       <c r="H53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
-        <v>0.0819175760181933</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.077179442745086)</f>
+        <v>0.077179442745086</v>
       </c>
       <c r="I53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
-        <v>0.0819175760181933</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782751122453402)</f>
+        <v>0.0782751122453402</v>
       </c>
       <c r="J53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
-        <v>0.0819175760181933</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826935337038488)</f>
+        <v>0.0826935337038488</v>
       </c>
       <c r="K53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
-        <v>0.0819175760181933</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826935337038488)</f>
+        <v>0.0826935337038488</v>
       </c>
       <c r="L53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
-        <v>0.0819175760181933</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081986735546084)</f>
+        <v>0.081986735546084</v>
       </c>
       <c r="M53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819175760181933)</f>
-        <v>0.0819175760181933</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864051570045927)</f>
+        <v>0.0864051570045927</v>
       </c>
       <c r="N53" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),660.71512861809)</f>
@@ -5552,52 +5552,52 @@
         <v>124</v>
       </c>
       <c r="B54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
-        <v>0.0819180495097435</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738134657732333)</f>
+        <v>0.0738134657732333</v>
       </c>
       <c r="C54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875791848041027)</f>
-        <v>0.0875791848041027</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738134657732333)</f>
+        <v>0.0738134657732333</v>
       </c>
       <c r="D54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875791848041027)</f>
-        <v>0.0875791848041027</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826224083229981)</f>
+        <v>0.0826224083229981</v>
       </c>
       <c r="E54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875791848041027)</f>
-        <v>0.0875791848041027</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0945072087101559)</f>
+        <v>0.0945072087101559</v>
       </c>
       <c r="F54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
-        <v>0.0819180495097435</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0952140122277676)</f>
+        <v>0.0952140122277676</v>
       </c>
       <c r="G54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
-        <v>0.0819180495097435</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0907957098996484)</f>
+        <v>0.0907957098996484</v>
       </c>
       <c r="H54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
-        <v>0.0819180495097435</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771794819907101)</f>
+        <v>0.0771794819907101</v>
       </c>
       <c r="I54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
-        <v>0.0819180495097435</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782752685393762)</f>
+        <v>0.0782752685393762</v>
       </c>
       <c r="J54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
-        <v>0.0819180495097435</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826935708674953)</f>
+        <v>0.0826935708674953</v>
       </c>
       <c r="K54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
-        <v>0.0819180495097435</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826935708674953)</f>
+        <v>0.0826935708674953</v>
       </c>
       <c r="L54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
-        <v>0.0819180495097435</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819867673498837)</f>
+        <v>0.0819867673498837</v>
       </c>
       <c r="M54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819180495097435)</f>
-        <v>0.0819180495097435</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864050696780028)</f>
+        <v>0.0864050696780028</v>
       </c>
       <c r="N54" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.156028161701)</f>
@@ -5608,8 +5608,8 @@
         <v>1</v>
       </c>
       <c r="P54" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2)</f>
-        <v>2</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3)</f>
+        <v>3</v>
       </c>
       <c r="Q54" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
@@ -5649,52 +5649,52 @@
         <v>125</v>
       </c>
       <c r="B55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
-        <v>0.0819179890740179</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738124965393579)</f>
+        <v>0.0738124965393579</v>
       </c>
       <c r="C55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875793661112797)</f>
-        <v>0.0875793661112797</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738124965393579)</f>
+        <v>0.0738124965393579</v>
       </c>
       <c r="D55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875793661112797)</f>
-        <v>0.0875793661112797</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826224235220467)</f>
+        <v>0.0826224235220467</v>
       </c>
       <c r="E55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0875793661112797)</f>
-        <v>0.0875793661112797</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0945083084729547)</f>
+        <v>0.0945083084729547</v>
       </c>
       <c r="F55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
-        <v>0.0819179890740179</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0952145803016424)</f>
+        <v>0.0952145803016424</v>
       </c>
       <c r="G55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
-        <v>0.0819179890740179</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0907966823883564)</f>
+        <v>0.0907966823883564</v>
       </c>
       <c r="H55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
-        <v>0.0819179890740179</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771804197218833)</f>
+        <v>0.0771804197218833</v>
       </c>
       <c r="I55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
-        <v>0.0819179890740179</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782751293210692)</f>
+        <v>0.0782751293210692</v>
       </c>
       <c r="J55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
-        <v>0.0819179890740179</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826930272343553)</f>
+        <v>0.0826930272343553</v>
       </c>
       <c r="K55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
-        <v>0.0819179890740179</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826930272343553)</f>
+        <v>0.0826930272343553</v>
       </c>
       <c r="L55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
-        <v>0.0819179890740179</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819867554056675)</f>
+        <v>0.0819867554056675</v>
       </c>
       <c r="M55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819179890740179)</f>
-        <v>0.0819179890740179</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864046533189536)</f>
+        <v>0.0864046533189536</v>
       </c>
       <c r="N55" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),96.1040185823099)</f>
@@ -5746,52 +5746,52 @@
         <v>126</v>
       </c>
       <c r="B56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1015098507676)</f>
-        <v>0.1015098507676</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0948522483704821)</f>
+        <v>0.0948522483704821</v>
       </c>
       <c r="C56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0848631221776276)</f>
-        <v>0.0848631221776276</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0815047861926023)</f>
+        <v>0.0815047861926023</v>
       </c>
       <c r="D56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0848631221776276)</f>
-        <v>0.0848631221776276</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0764490653204335)</f>
+        <v>0.0764490653204335</v>
       </c>
       <c r="E56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0848631221776276)</f>
-        <v>0.0848631221776276</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0840907184461371)</f>
+        <v>0.0840907184461371</v>
       </c>
       <c r="F56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
-        <v>0.0774844188474166</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0847724193282586)</f>
+        <v>0.0847724193282586</v>
       </c>
       <c r="G56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
-        <v>0.0774844188474166</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0839123144737292)</f>
+        <v>0.0839123144737292</v>
       </c>
       <c r="H56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
-        <v>0.0774844188474166</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0747579341668873)</f>
+        <v>0.0747579341668873</v>
       </c>
       <c r="I56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
-        <v>0.0774844188474166</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0754421691956102)</f>
+        <v>0.0754421691956102</v>
       </c>
       <c r="J56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
-        <v>0.0774844188474166</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0761698137204834)</f>
+        <v>0.0761698137204834</v>
       </c>
       <c r="K56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
-        <v>0.0774844188474166</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0761698137204834)</f>
+        <v>0.0761698137204834</v>
       </c>
       <c r="L56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0774844188474166)</f>
-        <v>0.0774844188474166</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0888355750162418)</f>
+        <v>0.0888355750162418</v>
       </c>
       <c r="M56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1015098507676)</f>
-        <v>0.1015098507676</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.103043142048651)</f>
+        <v>0.103043142048651</v>
       </c>
       <c r="N56" s="7" t="n">
         <f aca="false">SUM(N39:N55)</f>
@@ -5799,7 +5799,7 @@
       </c>
       <c r="P56" s="7" t="n">
         <f aca="false">SUM(P39:P55)</f>
-        <v>744</v>
+        <v>785</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5903,44 +5903,44 @@
         <v>0.12</v>
       </c>
       <c r="C62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955555555555556)</f>
+        <v>0.0955555555555556</v>
       </c>
       <c r="D62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="E62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="F62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="G62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="H62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="I62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="J62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="K62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
+        <v>0.0711111111111111</v>
       </c>
       <c r="L62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076)</f>
-        <v>0.076</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955555555555556)</f>
+        <v>0.0955555555555556</v>
       </c>
       <c r="M62" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.12)</f>
@@ -5952,52 +5952,52 @@
         <v>102</v>
       </c>
       <c r="B63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0540540540540541)</f>
+        <v>0.0540540540540541</v>
       </c>
       <c r="C63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0540540540540541)</f>
+        <v>0.0540540540540541</v>
       </c>
       <c r="D63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
+        <v>0.0810810810810811</v>
       </c>
       <c r="E63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.108108108108108)</f>
+        <v>0.108108108108108</v>
       </c>
       <c r="F63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.108108108108108)</f>
+        <v>0.108108108108108</v>
       </c>
       <c r="G63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.108108108108108)</f>
+        <v>0.108108108108108</v>
       </c>
       <c r="H63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
+        <v>0.0810810810810811</v>
       </c>
       <c r="I63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
+        <v>0.0810810810810811</v>
       </c>
       <c r="J63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
+        <v>0.0810810810810811</v>
       </c>
       <c r="K63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
+        <v>0.0810810810810811</v>
       </c>
       <c r="L63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
+        <v>0.0810810810810811</v>
       </c>
       <c r="M63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
+        <v>0.0810810810810811</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6005,52 +6005,52 @@
         <v>103</v>
       </c>
       <c r="B64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
-        <v>0.0269650818628408</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10126582278481)</f>
+        <v>0.10126582278481</v>
       </c>
       <c r="C64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.252438087744811)</f>
-        <v>0.252438087744811</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10126582278481)</f>
+        <v>0.10126582278481</v>
       </c>
       <c r="D64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.252438087744811)</f>
-        <v>0.252438087744811</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10126582278481)</f>
+        <v>0.10126582278481</v>
       </c>
       <c r="E64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.252438087744811)</f>
-        <v>0.252438087744811</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
       <c r="F64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
-        <v>0.0269650818628408</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
       <c r="G64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
-        <v>0.0269650818628408</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
       <c r="H64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
-        <v>0.0269650818628408</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0886075949367089)</f>
+        <v>0.0886075949367089</v>
       </c>
       <c r="I64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
-        <v>0.0269650818628408</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
       <c r="J64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
-        <v>0.0269650818628408</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
       <c r="K64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
-        <v>0.0269650818628408</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
       <c r="L64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
-        <v>0.0269650818628408</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
       <c r="M64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0269650818628408)</f>
-        <v>0.0269650818628408</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
+        <v>0.0759493670886076</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6058,52 +6058,52 @@
         <v>104</v>
       </c>
       <c r="B65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0526315789473684)</f>
+        <v>0.0526315789473684</v>
       </c>
       <c r="C65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0526315789473684)</f>
+        <v>0.0526315789473684</v>
       </c>
       <c r="D65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
+        <v>0.0789473684210526</v>
       </c>
       <c r="E65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
+        <v>0.0789473684210526</v>
       </c>
       <c r="F65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
+        <v>0.105263157894737</v>
       </c>
       <c r="G65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
+        <v>0.105263157894737</v>
       </c>
       <c r="H65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0526315789473684)</f>
+        <v>0.0526315789473684</v>
       </c>
       <c r="I65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
+        <v>0.105263157894737</v>
       </c>
       <c r="J65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
+        <v>0.105263157894737</v>
       </c>
       <c r="K65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
+        <v>0.105263157894737</v>
       </c>
       <c r="L65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
+        <v>0.0789473684210526</v>
       </c>
       <c r="M65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
+        <v>0.0789473684210526</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6164,12 +6164,12 @@
         <v>106</v>
       </c>
       <c r="B67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
+        <v>0.111111111111111</v>
       </c>
       <c r="C67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
+        <v>0.111111111111111</v>
       </c>
       <c r="D67" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
@@ -6184,16 +6184,16 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="G67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
+        <v>0.0555555555555556</v>
       </c>
       <c r="H67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
+        <v>0.0555555555555556</v>
       </c>
       <c r="I67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
+        <v>0.0555555555555556</v>
       </c>
       <c r="J67" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
@@ -6208,8 +6208,8 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="M67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
+        <v>0.111111111111111</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6217,12 +6217,12 @@
         <v>107</v>
       </c>
       <c r="B68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
+        <v>0.0555555555555556</v>
       </c>
       <c r="C68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
+        <v>0.0555555555555556</v>
       </c>
       <c r="D68" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
@@ -6233,20 +6233,20 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="F68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
+        <v>0.111111111111111</v>
       </c>
       <c r="G68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
+        <v>0.111111111111111</v>
       </c>
       <c r="H68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
+        <v>0.111111111111111</v>
       </c>
       <c r="I68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
+        <v>0.111111111111111</v>
       </c>
       <c r="J68" s="20" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
@@ -6257,12 +6257,12 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="L68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
+        <v>0.0555555555555556</v>
       </c>
       <c r="M68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
+        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
+        <v>0.0555555555555556</v>
       </c>
     </row>
   </sheetData>
@@ -6318,11 +6318,11 @@
       </c>
       <c r="B5" s="24" t="n">
         <f aca="false">MATCH(MAX(Importados!$B$22:$M$22),Importados!$B$22:$M$22,0)</f>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C5" s="24" t="n">
         <f aca="false">MATCH(MAX(Importados!$B$56:$M$56),Importados!$B$56:$M$56,0)</f>
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6331,11 +6331,11 @@
       </c>
       <c r="B6" s="25" t="str">
         <f aca="false">INDEX(Importados!$B$4:$M$4,B5)</f>
-        <v>Ene</v>
+        <v>Dic</v>
       </c>
       <c r="C6" s="25" t="str">
         <f aca="false">INDEX(Importados!$B$38:$M$38,C5)</f>
-        <v>Ene</v>
+        <v>Dic</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6344,11 +6344,11 @@
       </c>
       <c r="B7" s="26" t="n">
         <f aca="false">INDEX(Importados!$B$22:$M$22,B5)</f>
-        <v>0.101848800284409</v>
+        <v>0.102986262617071</v>
       </c>
       <c r="C7" s="26" t="n">
         <f aca="false">INDEX(Importados!$B$56:$M$56,C5)</f>
-        <v>0.1015098507676</v>
+        <v>0.103043142048651</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="F13" s="29" t="n">
         <f aca="false">Importados!$N$5*INDEX(Importados!$B$5:$M$5,$B$5)/$B$8</f>
-        <v>652.692236720059</v>
+        <v>652.618836454199</v>
       </c>
       <c r="G13" s="29" t="n">
         <f aca="false">F13*Importados!$O$5</f>
@@ -6465,11 +6465,11 @@
       </c>
       <c r="H13" s="23" t="n">
         <f aca="false">F13/$C13</f>
-        <v>9.06516995444526</v>
+        <v>9.06415050630832</v>
       </c>
       <c r="I13" s="29" t="n">
         <f aca="false">Importados!$N$39*INDEX(Importados!$B$39:$M$39,$C$5)/$C$8</f>
-        <v>339.292554289086</v>
+        <v>339.254723202532</v>
       </c>
       <c r="J13" s="29" t="n">
         <f aca="false">I13*Importados!$O$39</f>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="K13" s="23" t="n">
         <f aca="false">I13/$C13</f>
-        <v>4.71239658734841</v>
+        <v>4.71187115559072</v>
       </c>
       <c r="M13" s="5" t="s">
         <v>149</v>
@@ -6501,27 +6501,27 @@
       </c>
       <c r="F14" s="29" t="n">
         <f aca="false">Importados!$N$6*INDEX(Importados!$B$6:$M$6,$B$5)/$B$8</f>
-        <v>36.3790897941657</v>
+        <v>37.0808827424103</v>
       </c>
       <c r="G14" s="29" t="n">
         <f aca="false">F14*Importados!$O$6</f>
-        <v>36.3790897941657</v>
+        <v>37.0808827424103</v>
       </c>
       <c r="H14" s="23" t="n">
         <f aca="false">F14/$C14</f>
-        <v>1.21263632647219</v>
+        <v>1.23602942474701</v>
       </c>
       <c r="I14" s="29" t="n">
         <f aca="false">Importados!$N$40*INDEX(Importados!$B$40:$M$40,$C$5)/$C$8</f>
-        <v>18.6772059581256</v>
+        <v>19.2468348066429</v>
       </c>
       <c r="J14" s="29" t="n">
         <f aca="false">I14*Importados!$O$40</f>
-        <v>18.6772059581256</v>
+        <v>19.2468348066429</v>
       </c>
       <c r="K14" s="23" t="n">
         <f aca="false">I14/$C14</f>
-        <v>0.622573531937519</v>
+        <v>0.641561160221431</v>
       </c>
       <c r="M14" s="5" t="s">
         <v>149</v>
@@ -6545,27 +6545,27 @@
       </c>
       <c r="F15" s="29" t="n">
         <f aca="false">Importados!$N$7*INDEX(Importados!$B$7:$M$7,$B$5)/$B$8</f>
-        <v>232.796340138188</v>
+        <v>238.015237592182</v>
       </c>
       <c r="G15" s="29" t="n">
         <f aca="false">F15*Importados!$O$7</f>
-        <v>232.796340138188</v>
+        <v>238.015237592182</v>
       </c>
       <c r="H15" s="23" t="n">
         <f aca="false">F15/$C15</f>
-        <v>9.69984750575784</v>
+        <v>9.9173015663409</v>
       </c>
       <c r="I15" s="29" t="n">
         <f aca="false">Importados!$N$41*INDEX(Importados!$B$41:$M$41,$C$5)/$C$8</f>
-        <v>120.070942594702</v>
+        <v>123.883624610963</v>
       </c>
       <c r="J15" s="29" t="n">
         <f aca="false">I15*Importados!$O$41</f>
-        <v>120.070942594702</v>
+        <v>123.883624610963</v>
       </c>
       <c r="K15" s="23" t="n">
         <f aca="false">I15/$C15</f>
-        <v>5.00295594144594</v>
+        <v>5.16181769212347</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>149</v>
@@ -6589,27 +6589,27 @@
       </c>
       <c r="F16" s="29" t="n">
         <f aca="false">Importados!$N$8*INDEX(Importados!$B$8:$M$8,$B$5)/$B$8</f>
-        <v>12.9711603110206</v>
+        <v>13.8920231904653</v>
       </c>
       <c r="G16" s="29" t="n">
         <f aca="false">F16*Importados!$O$8</f>
-        <v>12.9711603110206</v>
+        <v>13.8920231904653</v>
       </c>
       <c r="H16" s="23" t="n">
         <f aca="false">F16/$C16</f>
-        <v>0.81069751943879</v>
+        <v>0.868251449404081</v>
       </c>
       <c r="I16" s="29" t="n">
         <f aca="false">Importados!$N$42*INDEX(Importados!$B$42:$M$42,$C$5)/$C$8</f>
-        <v>6.65083763296167</v>
+        <v>7.22960704153535</v>
       </c>
       <c r="J16" s="29" t="n">
         <f aca="false">I16*Importados!$O$42</f>
-        <v>6.65083763296167</v>
+        <v>7.22960704153535</v>
       </c>
       <c r="K16" s="23" t="n">
         <f aca="false">I16/$C16</f>
-        <v>0.415677352060105</v>
+        <v>0.451850440095959</v>
       </c>
       <c r="M16" s="5" t="s">
         <v>149</v>
@@ -6633,27 +6633,27 @@
       </c>
       <c r="F17" s="29" t="n">
         <f aca="false">Importados!$N$9*INDEX(Importados!$B$9:$M$9,$B$5)/$B$8</f>
-        <v>18.8029804281169</v>
+        <v>19.6998523581369</v>
       </c>
       <c r="G17" s="29" t="n">
         <f aca="false">F17*Importados!$O$9</f>
-        <v>18.8029804281169</v>
+        <v>19.6998523581369</v>
       </c>
       <c r="H17" s="23" t="n">
         <f aca="false">F17/$C17</f>
-        <v>1.17518627675731</v>
+        <v>1.23124077238356</v>
       </c>
       <c r="I17" s="29" t="n">
         <f aca="false">Importados!$N$43*INDEX(Importados!$B$43:$M$43,$C$5)/$C$8</f>
-        <v>9.6681132372588</v>
+        <v>10.2632365116348</v>
       </c>
       <c r="J17" s="29" t="n">
         <f aca="false">I17*Importados!$O$43</f>
-        <v>9.6681132372588</v>
+        <v>10.2632365116348</v>
       </c>
       <c r="K17" s="23" t="n">
         <f aca="false">I17/$C17</f>
-        <v>0.604257077328675</v>
+        <v>0.641452281977176</v>
       </c>
       <c r="M17" s="5" t="s">
         <v>149</v>
@@ -6809,27 +6809,27 @@
       </c>
       <c r="F21" s="29" t="n">
         <f aca="false">Importados!$N$13*INDEX(Importados!$B$13:$M$13,$B$5)/$B$8</f>
-        <v>8.9191989732046</v>
+        <v>9.58243351095272</v>
       </c>
       <c r="G21" s="29" t="n">
         <f aca="false">F21*Importados!$O$13</f>
-        <v>8.9191989732046</v>
+        <v>9.58243351095272</v>
       </c>
       <c r="H21" s="23" t="n">
         <f aca="false">F21/$C21</f>
-        <v>0.557449935825287</v>
+        <v>0.598902094434545</v>
       </c>
       <c r="I21" s="29" t="n">
         <f aca="false">Importados!$N$47*INDEX(Importados!$B$47:$M$47,$C$5)/$C$8</f>
-        <v>4.55414466197892</v>
+        <v>4.97450118188776</v>
       </c>
       <c r="J21" s="29" t="n">
         <f aca="false">I21*Importados!$O$47</f>
-        <v>4.55414466197892</v>
+        <v>4.97450118188776</v>
       </c>
       <c r="K21" s="23" t="n">
         <f aca="false">I21/$C21</f>
-        <v>0.284634041373682</v>
+        <v>0.310906323867985</v>
       </c>
       <c r="M21" s="5" t="s">
         <v>149</v>
@@ -6853,27 +6853,27 @@
       </c>
       <c r="F22" s="29" t="n">
         <f aca="false">Importados!$N$14*INDEX(Importados!$B$14:$M$14,$B$5)/$B$8</f>
-        <v>49.625920044755</v>
+        <v>51.7478506420602</v>
       </c>
       <c r="G22" s="29" t="n">
         <f aca="false">F22*Importados!$O$14</f>
-        <v>49.625920044755</v>
+        <v>51.7478506420602</v>
       </c>
       <c r="H22" s="23" t="n">
         <f aca="false">F22/$C22</f>
-        <v>1.65419733482517</v>
+        <v>1.72492835473534</v>
       </c>
       <c r="I22" s="29" t="n">
         <f aca="false">Importados!$N$48*INDEX(Importados!$B$48:$M$48,$C$5)/$C$8</f>
-        <v>25.4438253440476</v>
+        <v>26.9047032149427</v>
       </c>
       <c r="J22" s="29" t="n">
         <f aca="false">I22*Importados!$O$48</f>
-        <v>25.4438253440476</v>
+        <v>26.9047032149427</v>
       </c>
       <c r="K22" s="23" t="n">
         <f aca="false">I22/$C22</f>
-        <v>0.848127511468254</v>
+        <v>0.896823440498089</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>149</v>
@@ -6897,27 +6897,27 @@
       </c>
       <c r="F23" s="29" t="n">
         <f aca="false">Importados!$N$15*INDEX(Importados!$B$15:$M$15,$B$5)/$B$8</f>
-        <v>17.8150080869683</v>
+        <v>18.4793724972974</v>
       </c>
       <c r="G23" s="29" t="n">
         <f aca="false">F23*Importados!$O$15</f>
-        <v>17.8150080869683</v>
+        <v>18.4793724972974</v>
       </c>
       <c r="H23" s="23" t="n">
         <f aca="false">F23/$C23</f>
-        <v>1.11343800543552</v>
+        <v>1.15496078108109</v>
       </c>
       <c r="I23" s="29" t="n">
         <f aca="false">Importados!$N$49*INDEX(Importados!$B$49:$M$49,$C$5)/$C$8</f>
-        <v>9.23742114169862</v>
+        <v>9.64634335529636</v>
       </c>
       <c r="J23" s="29" t="n">
         <f aca="false">I23*Importados!$O$49</f>
-        <v>9.23742114169862</v>
+        <v>9.64634335529636</v>
       </c>
       <c r="K23" s="23" t="n">
         <f aca="false">I23/$C23</f>
-        <v>0.577338821356164</v>
+        <v>0.602896459706022</v>
       </c>
       <c r="M23" s="5" t="s">
         <v>149</v>
@@ -6941,27 +6941,27 @@
       </c>
       <c r="F24" s="29" t="n">
         <f aca="false">Importados!$N$16*INDEX(Importados!$B$16:$M$16,$B$5)/$B$8</f>
-        <v>2.93881852547358</v>
+        <v>3.14198698162501</v>
       </c>
       <c r="G24" s="29" t="n">
         <f aca="false">F24*Importados!$O$16</f>
-        <v>2.93881852547358</v>
+        <v>3.14198698162501</v>
       </c>
       <c r="H24" s="23" t="n">
         <f aca="false">F24/$C24</f>
-        <v>0.122450771894732</v>
+        <v>0.130916124234375</v>
       </c>
       <c r="I24" s="29" t="n">
         <f aca="false">Importados!$N$50*INDEX(Importados!$B$50:$M$50,$C$5)/$C$8</f>
-        <v>1.52758273990662</v>
+        <v>1.66774779758251</v>
       </c>
       <c r="J24" s="29" t="n">
         <f aca="false">I24*Importados!$O$50</f>
-        <v>1.52758273990662</v>
+        <v>1.66774779758251</v>
       </c>
       <c r="K24" s="23" t="n">
         <f aca="false">I24/$C24</f>
-        <v>0.0636492808294427</v>
+        <v>0.0694894915659378</v>
       </c>
       <c r="M24" s="5" t="s">
         <v>149</v>
@@ -7029,27 +7029,27 @@
       </c>
       <c r="F26" s="29" t="n">
         <f aca="false">Importados!$N$18*INDEX(Importados!$B$18:$M$18,$B$5)/$B$8</f>
-        <v>2.37711623910776</v>
+        <v>2.47992147874104</v>
       </c>
       <c r="G26" s="29" t="n">
         <f aca="false">F26*Importados!$O$18</f>
-        <v>2.37711623910776</v>
+        <v>2.47992147874104</v>
       </c>
       <c r="H26" s="23" t="n">
         <f aca="false">F26/$C26</f>
-        <v>1.18855811955388</v>
+        <v>1.23996073937052</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">Importados!$N$52*INDEX(Importados!$B$52:$M$52,$C$5)/$C$8</f>
-        <v>1.23008585585944</v>
+        <v>1.29748008103154</v>
       </c>
       <c r="J26" s="29" t="n">
         <f aca="false">I26*Importados!$O$52</f>
-        <v>1.23008585585944</v>
+        <v>1.29748008103154</v>
       </c>
       <c r="K26" s="23" t="n">
         <f aca="false">I26/$C26</f>
-        <v>0.61504292792972</v>
+        <v>0.648740040515769</v>
       </c>
       <c r="M26" s="5" t="s">
         <v>152</v>
@@ -7073,27 +7073,27 @@
       </c>
       <c r="F27" s="29" t="n">
         <f aca="false">Importados!$N$19*INDEX(Importados!$B$19:$M$19,$B$5)/$B$8</f>
-        <v>5.22964666029617</v>
+        <v>5.45582081823097</v>
       </c>
       <c r="G27" s="29" t="n">
         <f aca="false">F27*Importados!$O$19</f>
-        <v>5.22964666029617</v>
+        <v>5.45582081823097</v>
       </c>
       <c r="H27" s="23" t="n">
         <f aca="false">F27/$C27</f>
-        <v>2.61482333014809</v>
+        <v>2.72791040911549</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">Importados!$N$53*INDEX(Importados!$B$53:$M$53,$C$5)/$C$8</f>
-        <v>2.70620908874714</v>
+        <v>2.85445972117779</v>
       </c>
       <c r="J27" s="29" t="n">
         <f aca="false">I27*Importados!$O$53</f>
-        <v>2.70620908874714</v>
+        <v>2.85445972117779</v>
       </c>
       <c r="K27" s="23" t="n">
         <f aca="false">I27/$C27</f>
-        <v>1.35310454437357</v>
+        <v>1.42722986058889</v>
       </c>
       <c r="M27" s="5" t="s">
         <v>152</v>
@@ -7117,27 +7117,27 @@
       </c>
       <c r="F28" s="29" t="n">
         <f aca="false">Importados!$N$20*INDEX(Importados!$B$20:$M$20,$B$5)/$B$8</f>
-        <v>1.14101819180856</v>
+        <v>1.19036240324224</v>
       </c>
       <c r="G28" s="29" t="n">
         <f aca="false">F28*Importados!$O$20</f>
-        <v>1.14101819180856</v>
+        <v>1.19036240324224</v>
       </c>
       <c r="H28" s="23" t="n">
         <f aca="false">F28/$C28</f>
-        <v>0.57050909590428</v>
+        <v>0.595181201621121</v>
       </c>
       <c r="I28" s="29" t="n">
         <f aca="false">Importados!$N$54*INDEX(Importados!$B$54:$M$54,$C$5)/$C$8</f>
-        <v>0.59044903260391</v>
+        <v>0.622790582890795</v>
       </c>
       <c r="J28" s="29" t="n">
         <f aca="false">I28*Importados!$O$54</f>
-        <v>0.59044903260391</v>
+        <v>0.622790582890795</v>
       </c>
       <c r="K28" s="23" t="n">
         <f aca="false">I28/$C28</f>
-        <v>0.295224516301955</v>
+        <v>0.311395291445398</v>
       </c>
       <c r="M28" s="5" t="s">
         <v>152</v>
@@ -7161,27 +7161,27 @@
       </c>
       <c r="F29" s="29" t="n">
         <f aca="false">Importados!$N$21*INDEX(Importados!$B$21:$M$21,$B$5)/$B$8</f>
-        <v>0.760668657682474</v>
+        <v>0.793573755434497</v>
       </c>
       <c r="G29" s="29" t="n">
         <f aca="false">F29*Importados!$O$21</f>
-        <v>0.760668657682474</v>
+        <v>0.793573755434497</v>
       </c>
       <c r="H29" s="23" t="n">
         <f aca="false">F29/$C29</f>
-        <v>0.760668657682474</v>
+        <v>0.793573755434497</v>
       </c>
       <c r="I29" s="29" t="n">
         <f aca="false">Importados!$N$55*INDEX(Importados!$B$55:$M$55,$C$5)/$C$8</f>
-        <v>0.393632397209744</v>
+        <v>0.415191720408138</v>
       </c>
       <c r="J29" s="29" t="n">
         <f aca="false">I29*Importados!$O$55</f>
-        <v>0.393632397209744</v>
+        <v>0.415191720408138</v>
       </c>
       <c r="K29" s="23" t="n">
         <f aca="false">I29/$C29</f>
-        <v>0.393632397209744</v>
+        <v>0.415191720408138</v>
       </c>
       <c r="M29" s="5" t="s">
         <v>152</v>
@@ -7193,27 +7193,27 @@
       </c>
       <c r="F30" s="30" t="n">
         <f aca="false">SUM(F13:F29)</f>
-        <v>1050.21469306323</v>
+        <v>1061.94364471736</v>
       </c>
       <c r="G30" s="30" t="n">
         <f aca="false">SUM(G13:G29)</f>
-        <v>397.522456343171</v>
+        <v>409.324808263162</v>
       </c>
       <c r="H30" s="30" t="n">
         <f aca="false">SUM(H13:H29)</f>
-        <v>31.853123101456</v>
+        <v>32.590797446526</v>
       </c>
       <c r="I30" s="30" t="n">
         <f aca="false">SUM(I13:I29)</f>
-        <v>544.079465849846</v>
+        <v>552.297705704186</v>
       </c>
       <c r="J30" s="30" t="n">
         <f aca="false">SUM(J13:J29)</f>
-        <v>204.786911560761</v>
+        <v>213.042982501654</v>
       </c>
       <c r="K30" s="30" t="n">
         <f aca="false">SUM(K13:K29)</f>
-        <v>16.4682412406882</v>
+        <v>16.97085206833</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7222,11 +7222,11 @@
       </c>
       <c r="F31" s="11" t="n">
         <f aca="false">SUMPRODUCT(F13:F29,$B$13:$B$29)/F30</f>
-        <v>5.61010110978076</v>
+        <v>5.69116685083819</v>
       </c>
       <c r="I31" s="11" t="n">
         <f aca="false">SUMPRODUCT(I13:I29,$B$13:$B$29)/I30</f>
-        <v>5.59545821055644</v>
+        <v>5.69893065809013</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="C38" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$29:$M$29,$B$5)*SUMPRODUCT(Importados!$N$5:$N$21,Importados!$R$5:$R$21/Importados!$X$5:$X$21)/$B$8</f>
-        <v>270.443057759748</v>
+        <v>263.133785928404</v>
       </c>
       <c r="D38" s="22" t="n">
         <f aca="false">Importados!R$23</f>
@@ -7347,15 +7347,15 @@
       </c>
       <c r="E38" s="28" t="n">
         <f aca="false">2*C38/D38</f>
-        <v>36.0590743679664</v>
+        <v>35.0845047904539</v>
       </c>
       <c r="F38" s="28" t="n">
         <f aca="false">E38*(Supuestos!$B$17+Supuestos!$B$18)/60+2*C38*$B38/60</f>
-        <v>34.5566129359678</v>
+        <v>33.6226504241849</v>
       </c>
       <c r="G38" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$63:$M$63,$C$5)*SUMPRODUCT(Importados!$N$39:$N$55,Importados!$R$39:$R$55/Importados!$X$39:$X$55)/$C$8</f>
-        <v>139.979837012887</v>
+        <v>136.196598174701</v>
       </c>
       <c r="H38" s="22" t="n">
         <f aca="false">Importados!R$57</f>
@@ -7363,11 +7363,11 @@
       </c>
       <c r="I38" s="28" t="n">
         <f aca="false">2*G38/H38</f>
-        <v>18.663978268385</v>
+        <v>18.1595464232935</v>
       </c>
       <c r="J38" s="28" t="n">
         <f aca="false">I38*(Supuestos!$B$17+Supuestos!$B$18)/60+2*G38*$B38/60</f>
-        <v>17.8863125072023</v>
+        <v>17.4028986556563</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>161</v>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="C39" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$30:$M$30,$B$5)*SUMPRODUCT(Importados!$N$5:$N$21,Importados!$S$5:$S$21/Importados!$X$5:$X$21)/$B$8</f>
-        <v>8.34060470826765</v>
+        <v>21.4635570516291</v>
       </c>
       <c r="D39" s="22" t="n">
         <f aca="false">Importados!S$23</f>
@@ -7390,15 +7390,15 @@
       </c>
       <c r="E39" s="28" t="n">
         <f aca="false">2*C39/D39</f>
-        <v>1.39010078471128</v>
+        <v>3.57725950860485</v>
       </c>
       <c r="F39" s="28" t="n">
         <f aca="false">E39*(Supuestos!$B$17+Supuestos!$B$18)/60+2*C39*$B39/60</f>
-        <v>1.22792235982829</v>
+        <v>3.15991256593428</v>
       </c>
       <c r="G39" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$64:$M$64,$C$5)*SUMPRODUCT(Importados!$N$39:$N$55,Importados!$S$39:$S$55/Importados!$X$39:$X$55)/$C$8</f>
-        <v>4.72978482937001</v>
+        <v>13.3218273203531</v>
       </c>
       <c r="H39" s="22" t="n">
         <f aca="false">Importados!S$57</f>
@@ -7406,11 +7406,11 @@
       </c>
       <c r="I39" s="28" t="n">
         <f aca="false">2*G39/H39</f>
-        <v>0.788297471561669</v>
+        <v>2.22030455339218</v>
       </c>
       <c r="J39" s="28" t="n">
         <f aca="false">I39*(Supuestos!$B$17+Supuestos!$B$18)/60+2*G39*$B39/60</f>
-        <v>0.696329433212807</v>
+        <v>1.9612690221631</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>161</v>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="C40" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$31:$M$31,$B$5)*SUMPRODUCT(Importados!$N$5:$N$21,Importados!$T$5:$T$21/Importados!$X$5:$X$21)/$B$8</f>
-        <v>15.933847507444</v>
+        <v>15.0952239544206</v>
       </c>
       <c r="D40" s="22" t="n">
         <f aca="false">Importados!T$23</f>
@@ -7433,15 +7433,15 @@
       </c>
       <c r="E40" s="28" t="n">
         <f aca="false">2*C40/D40</f>
-        <v>2.89706318317163</v>
+        <v>2.74458617353102</v>
       </c>
       <c r="F40" s="28" t="n">
         <f aca="false">E40*(Supuestos!$B$17+Supuestos!$B$18)/60+2*C40*$B40/60</f>
-        <v>2.48664589888898</v>
+        <v>2.35576979894746</v>
       </c>
       <c r="G40" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$65:$M$65,$C$5)*SUMPRODUCT(Importados!$N$39:$N$55,Importados!$T$39:$T$55/Importados!$X$39:$X$55)/$C$8</f>
-        <v>9.32221450894524</v>
+        <v>8.83157164005339</v>
       </c>
       <c r="H40" s="22" t="n">
         <f aca="false">Importados!T$57</f>
@@ -7449,11 +7449,11 @@
       </c>
       <c r="I40" s="28" t="n">
         <f aca="false">2*G40/H40</f>
-        <v>1.6949480925355</v>
+        <v>1.60574029819153</v>
       </c>
       <c r="J40" s="28" t="n">
         <f aca="false">I40*(Supuestos!$B$17+Supuestos!$B$18)/60+2*G40*$B40/60</f>
-        <v>1.45483044609297</v>
+        <v>1.37826042261439</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>161</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="C42" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$33:$M$33,$B$5)*SUMPRODUCT(Importados!$N$5:$N$21,Importados!$V$5:$V$21/Importados!$X$5:$X$21)/$B$8</f>
-        <v>23.6691084679195</v>
+        <v>31.5588112905594</v>
       </c>
       <c r="D42" s="22" t="n">
         <f aca="false">Importados!V$23</f>
@@ -7519,15 +7519,15 @@
       </c>
       <c r="E42" s="28" t="n">
         <f aca="false">2*C42/D42</f>
-        <v>0.776036343210476</v>
+        <v>1.03471512428063</v>
       </c>
       <c r="F42" s="28" t="n">
         <f aca="false">E42*(Supuestos!$B$17+Supuestos!$B$18)/60+2*C42*$B42/60</f>
-        <v>1.63614329026875</v>
+        <v>2.181524387025</v>
       </c>
       <c r="G42" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$67:$M$67,$C$5)*SUMPRODUCT(Importados!$N$39:$N$55,Importados!$V$39:$V$55/Importados!$X$39:$X$55)/$C$8</f>
-        <v>13.8301471124783</v>
+        <v>18.4401961499711</v>
       </c>
       <c r="H42" s="22" t="n">
         <f aca="false">Importados!V$57</f>
@@ -7535,11 +7535,11 @@
       </c>
       <c r="I42" s="28" t="n">
         <f aca="false">2*G42/H42</f>
-        <v>0.453447446310765</v>
+        <v>0.60459659508102</v>
       </c>
       <c r="J42" s="28" t="n">
         <f aca="false">I42*(Supuestos!$B$17+Supuestos!$B$18)/60+2*G42*$B42/60</f>
-        <v>0.956018365971863</v>
+        <v>1.27469115462915</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>161</v>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="C43" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$34:$M$34,$B$5)*SUMPRODUCT(Importados!$N$5:$N$21,Importados!$W$5:$W$21/Importados!$X$5:$X$21)/$B$8</f>
-        <v>3.40742438250904</v>
+        <v>2.27161625500603</v>
       </c>
       <c r="D43" s="22" t="n">
         <f aca="false">Importados!W$23</f>
@@ -7562,15 +7562,15 @@
       </c>
       <c r="E43" s="28" t="n">
         <f aca="false">2*C43/D43</f>
-        <v>1.13580812750301</v>
+        <v>0.757205418335343</v>
       </c>
       <c r="F43" s="28" t="n">
         <f aca="false">E43*(Supuestos!$B$17+Supuestos!$B$18)/60+2*C43*$B43/60</f>
-        <v>0.776135553793726</v>
+        <v>0.517423702529151</v>
       </c>
       <c r="G43" s="29" t="n">
         <f aca="false">INDEX(Importados!$B$68:$M$68,$C$5)*SUMPRODUCT(Importados!$N$39:$N$55,Importados!$W$39:$W$55/Importados!$X$39:$X$55)/$C$8</f>
-        <v>2.12990990117672</v>
+        <v>1.41993993411782</v>
       </c>
       <c r="H43" s="22" t="n">
         <f aca="false">Importados!W$57</f>
@@ -7578,11 +7578,11 @@
       </c>
       <c r="I43" s="28" t="n">
         <f aca="false">2*G43/H43</f>
-        <v>0.709969967058907</v>
+        <v>0.473313311372605</v>
       </c>
       <c r="J43" s="28" t="n">
         <f aca="false">I43*(Supuestos!$B$17+Supuestos!$B$18)/60+2*G43*$B43/60</f>
-        <v>0.48514614415692</v>
+        <v>0.32343076277128</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>161</v>
@@ -7594,27 +7594,27 @@
       </c>
       <c r="C44" s="30" t="n">
         <f aca="false">SUM(C37:C43)</f>
-        <v>1050.21469306323</v>
+        <v>1061.94364471736</v>
       </c>
       <c r="E44" s="30" t="n">
         <f aca="false">SUM(E37:E43)</f>
-        <v>202.933635977327</v>
+        <v>203.873824185969</v>
       </c>
       <c r="F44" s="30" t="n">
         <f aca="false">SUM(F37:F43)</f>
-        <v>148.344763881951</v>
+        <v>149.498584721824</v>
       </c>
       <c r="G44" s="30" t="n">
         <f aca="false">SUM(G37:G43)</f>
-        <v>544.079465849848</v>
+        <v>552.297705704187</v>
       </c>
       <c r="I44" s="30" t="n">
         <f aca="false">SUM(I37:I43)</f>
-        <v>104.932589629389</v>
+        <v>105.685449564868</v>
       </c>
       <c r="J44" s="30" t="n">
         <f aca="false">SUM(J37:J43)</f>
-        <v>76.6725012481408</v>
+        <v>77.5344143693381</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7634,11 +7634,11 @@
       </c>
       <c r="B49" s="29" t="n">
         <f aca="false">F30</f>
-        <v>1050.21469306323</v>
+        <v>1061.94364471736</v>
       </c>
       <c r="C49" s="29" t="n">
         <f aca="false">I30</f>
-        <v>544.079465849846</v>
+        <v>552.297705704186</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7647,11 +7647,11 @@
       </c>
       <c r="B50" s="29" t="n">
         <f aca="false">G30</f>
-        <v>397.522456343171</v>
+        <v>409.324808263162</v>
       </c>
       <c r="C50" s="29" t="n">
         <f aca="false">J30</f>
-        <v>204.786911560761</v>
+        <v>213.042982501654</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7660,11 +7660,11 @@
       </c>
       <c r="B51" s="29" t="n">
         <f aca="false">B49+B50</f>
-        <v>1447.7371494064</v>
+        <v>1471.26845298052</v>
       </c>
       <c r="C51" s="29" t="n">
         <f aca="false">C49+C50</f>
-        <v>748.866377410607</v>
+        <v>765.34068820584</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7673,11 +7673,11 @@
       </c>
       <c r="B52" s="28" t="n">
         <f aca="false">F31</f>
-        <v>5.61010110978076</v>
+        <v>5.69116685083819</v>
       </c>
       <c r="C52" s="28" t="n">
         <f aca="false">I31</f>
-        <v>5.59545821055644</v>
+        <v>5.69893065809013</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7686,11 +7686,11 @@
       </c>
       <c r="B53" s="31" t="n">
         <f aca="false">H30/F30</f>
-        <v>0.0303301061314881</v>
+        <v>0.0306897617483272</v>
       </c>
       <c r="C53" s="31" t="n">
         <f aca="false">K30/I30</f>
-        <v>0.0302680808123589</v>
+        <v>0.0307277250893012</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7699,11 +7699,11 @@
       </c>
       <c r="B54" s="21" t="n">
         <f aca="false">Supuestos!$B$6/(B53*Supuestos!$B$24)</f>
-        <v>172.020212581163</v>
+        <v>170.004294824225</v>
       </c>
       <c r="C54" s="21" t="n">
         <f aca="false">Supuestos!$B$6/(C53*Supuestos!$B$24)</f>
-        <v>172.372716218515</v>
+        <v>169.794258741413</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7712,11 +7712,11 @@
       </c>
       <c r="B55" s="21" t="n">
         <f aca="false">Supuestos!$B$11/B52</f>
-        <v>249.549869530732</v>
+        <v>245.995247845142</v>
       </c>
       <c r="C55" s="21" t="n">
         <f aca="false">Supuestos!$B$11/C52</f>
-        <v>250.202923034748</v>
+        <v>245.66012187086</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7725,11 +7725,11 @@
       </c>
       <c r="B56" s="21" t="n">
         <f aca="false">MIN(B54,B55)</f>
-        <v>172.020212581163</v>
+        <v>170.004294824225</v>
       </c>
       <c r="C56" s="21" t="n">
         <f aca="false">MIN(C54,C55)</f>
-        <v>172.372716218515</v>
+        <v>169.794258741413</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7738,11 +7738,11 @@
       </c>
       <c r="B57" s="23" t="n">
         <f aca="false">B51/B56</f>
-        <v>8.41608743346555</v>
+        <v>8.65430167221207</v>
       </c>
       <c r="C57" s="23" t="n">
         <f aca="false">C51/C56</f>
-        <v>4.34446003891518</v>
+        <v>4.50745916781208</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7751,11 +7751,11 @@
       </c>
       <c r="B58" s="28" t="n">
         <f aca="false">E44</f>
-        <v>202.933635977327</v>
+        <v>203.873824185969</v>
       </c>
       <c r="C58" s="28" t="n">
         <f aca="false">I44</f>
-        <v>104.932589629389</v>
+        <v>105.685449564868</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7764,11 +7764,11 @@
       </c>
       <c r="B59" s="28" t="n">
         <f aca="false">F44</f>
-        <v>148.344763881951</v>
+        <v>149.498584721824</v>
       </c>
       <c r="C59" s="28" t="n">
         <f aca="false">J44</f>
-        <v>76.6725012481408</v>
+        <v>77.5344143693381</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7777,11 +7777,11 @@
       </c>
       <c r="B60" s="23" t="n">
         <f aca="false">B59/($B$9-Supuestos!$B$16)</f>
-        <v>24.7241273136584</v>
+        <v>24.9164307869707</v>
       </c>
       <c r="C60" s="23" t="n">
         <f aca="false">C59/($C$9-Supuestos!$B$16)</f>
-        <v>12.7787502080235</v>
+        <v>12.9224023948897</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7803,11 +7803,11 @@
       </c>
       <c r="B62" s="28" t="n">
         <f aca="false">B61*Supuestos!$B$16+B59</f>
-        <v>185.844763881951</v>
+        <v>186.998584721824</v>
       </c>
       <c r="C62" s="28" t="n">
         <f aca="false">C61*Supuestos!$B$16+C59</f>
-        <v>96.1725012481408</v>
+        <v>97.0344143693381</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7829,11 +7829,11 @@
       </c>
       <c r="B64" s="32" t="n">
         <f aca="false">B62/(B63*$B$9*Supuestos!$B$15)</f>
-        <v>0.884975066104527</v>
+        <v>0.890469451056304</v>
       </c>
       <c r="C64" s="32" t="n">
         <f aca="false">C62/(C63*$C$9*Supuestos!$B$15)</f>
-        <v>0.801437510401173</v>
+        <v>0.808620119744484</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7842,11 +7842,11 @@
       </c>
       <c r="B65" s="21" t="n">
         <f aca="false">B51*B52/B61</f>
-        <v>324.878071542227</v>
+        <v>334.92936993147</v>
       </c>
       <c r="C65" s="21" t="n">
         <f aca="false">C51*C52/C61</f>
-        <v>322.326963083987</v>
+        <v>335.509500915389</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7924,31 +7924,31 @@
       </c>
       <c r="B70" s="21" t="n">
         <f aca="false">F30*Supuestos!$B$22</f>
-        <v>525.107346531615</v>
+        <v>530.97182235868</v>
       </c>
       <c r="C70" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*H13:H29)*Supuestos!$B$22*Supuestos!$B$24</f>
-        <v>14.8076127992378</v>
+        <v>15.1040870788577</v>
       </c>
       <c r="D70" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*H13:H29)*Supuestos!$B$22</f>
-        <v>3.05037650791249</v>
+        <v>3.16140995903894</v>
       </c>
       <c r="E70" s="22" t="n">
         <f aca="false">ROUNDUP(C70,0)+ROUNDUP(D70,0)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F70" s="21" t="n">
         <f aca="false">I30*Supuestos!$B$22</f>
-        <v>272.039732924923</v>
+        <v>276.148852852093</v>
       </c>
       <c r="G70" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*K13:K29)*Supuestos!$B$22*Supuestos!$B$24</f>
-        <v>7.65268321403531</v>
+        <v>7.857991736822</v>
       </c>
       <c r="H70" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*K13:K29)*Supuestos!$B$22</f>
-        <v>1.57961347770469</v>
+        <v>1.6523897412763</v>
       </c>
       <c r="I70" s="22" t="n">
         <f aca="false">ROUNDUP(G70,0)+ROUNDUP(H70,0)</f>
@@ -7964,31 +7964,31 @@
       </c>
       <c r="B71" s="21" t="n">
         <f aca="false">F30*Supuestos!$B$23</f>
-        <v>525.107346531615</v>
+        <v>530.97182235868</v>
       </c>
       <c r="C71" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*H13:H29)*Supuestos!$B$23*Supuestos!$B$24</f>
-        <v>14.8076127992378</v>
+        <v>15.1040870788577</v>
       </c>
       <c r="D71" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*H13:H29)*Supuestos!$B$23</f>
-        <v>3.05037650791249</v>
+        <v>3.16140995903894</v>
       </c>
       <c r="E71" s="22" t="n">
         <f aca="false">ROUNDUP(C71,0)+ROUNDUP(D71,0)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F71" s="21" t="n">
         <f aca="false">I30*Supuestos!$B$23</f>
-        <v>272.039732924923</v>
+        <v>276.148852852093</v>
       </c>
       <c r="G71" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*K13:K29)*Supuestos!$B$23*Supuestos!$B$24</f>
-        <v>7.65268321403531</v>
+        <v>7.857991736822</v>
       </c>
       <c r="H71" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*K13:K29)*Supuestos!$B$23</f>
-        <v>1.57961347770469</v>
+        <v>1.6523897412763</v>
       </c>
       <c r="I71" s="22" t="n">
         <f aca="false">ROUNDUP(G71,0)+ROUNDUP(H71,0)</f>
@@ -8004,15 +8004,15 @@
       </c>
       <c r="B72" s="21" t="n">
         <f aca="false">G30</f>
-        <v>397.522456343171</v>
+        <v>409.324808263162</v>
       </c>
       <c r="C72" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*G13:G29/$C$13:$C$29)</f>
-        <v>16.6872001311857</v>
+        <v>17.2038270221398</v>
       </c>
       <c r="D72" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*G13:G29/$C$13:$C$29)</f>
-        <v>6.10075301582498</v>
+        <v>6.32281991807788</v>
       </c>
       <c r="E72" s="22" t="n">
         <f aca="false">ROUNDUP(C72/Supuestos!$B$26,0)+ROUNDUP(D72,0)</f>
@@ -8020,15 +8020,15 @@
       </c>
       <c r="F72" s="21" t="n">
         <f aca="false">J30</f>
-        <v>204.786911560761</v>
+        <v>213.042982501654</v>
       </c>
       <c r="G72" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=0)*J13:J29/$C$13:$C$29)</f>
-        <v>8.59661769793039</v>
+        <v>8.95420143018668</v>
       </c>
       <c r="H72" s="28" t="n">
         <f aca="false">SUMPRODUCT(($E$13:$E$29=1)*J13:J29/$C$13:$C$29)</f>
-        <v>3.15922695540939</v>
+        <v>3.3047794825526</v>
       </c>
       <c r="I72" s="22" t="n">
         <f aca="false">ROUNDUP(G72/Supuestos!$B$26,0)+ROUNDUP(H72,0)</f>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="E74" s="9" t="n">
         <f aca="false">SUM(E70:E73)</f>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I74" s="9" t="n">
         <f aca="false">SUM(I70:I73)</f>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="E75" s="11" t="n">
         <f aca="false">E74*Supuestos!$B$28</f>
-        <v>127.2</v>
+        <v>132</v>
       </c>
       <c r="I75" s="11" t="n">
         <f aca="false">I74*Supuestos!$B$28</f>
@@ -8104,11 +8104,11 @@
       </c>
       <c r="E76" s="7" t="n">
         <f aca="false">Importados!$P$22</f>
-        <v>1384</v>
+        <v>1498</v>
       </c>
       <c r="I76" s="7" t="n">
         <f aca="false">Importados!$P$56</f>
-        <v>744</v>
+        <v>785</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8117,11 +8117,11 @@
       </c>
       <c r="E77" s="9" t="n">
         <f aca="false">ROUNDUP(SUM(C70:C72),0)+B63*Supuestos!$B$6+E73*Supuestos!$B$27</f>
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I77" s="9" t="n">
         <f aca="false">ROUNDUP(SUM(G70:G72),0)+C63*Supuestos!$B$6+I73*Supuestos!$B$27</f>
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/salida/Recargas.xlsx
+++ b/salida/Recargas.xlsx
@@ -1848,50 +1848,17 @@
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""parametros_recargas!E55:P72"")"),0.119877958433184)</f>
         <v>0.119877958433184</v>
       </c>
-      <c r="C5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0954780457654631)</f>
-        <v>0.0954780457654631</v>
-      </c>
-      <c r="D5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711264175844748)</f>
-        <v>0.0711264175844748</v>
-      </c>
-      <c r="E5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711264175844748)</f>
-        <v>0.0711264175844748</v>
-      </c>
-      <c r="F5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711747020712071)</f>
-        <v>0.0711747020712071</v>
-      </c>
-      <c r="G5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711747020712071)</f>
-        <v>0.0711747020712071</v>
-      </c>
-      <c r="H5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0710911890912281)</f>
-        <v>0.0710911890912281</v>
-      </c>
-      <c r="I5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711747020712071)</f>
-        <v>0.0711747020712071</v>
-      </c>
-      <c r="J5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711681740744643)</f>
-        <v>0.0711681740744643</v>
-      </c>
-      <c r="K5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711681740744643)</f>
-        <v>0.0711681740744643</v>
-      </c>
-      <c r="L5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955198022554526)</f>
-        <v>0.0955198022554526</v>
-      </c>
-      <c r="M5" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.119919714923173)</f>
-        <v>0.119919714923173</v>
-      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
       <c r="N5" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""datos_base!K2:K18"")"),108842.626397553)</f>
         <v>108842.626397553</v>
@@ -1908,30 +1875,12 @@
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""PROY_Indexado!B57:H73"")"),2251135)</f>
         <v>2251135</v>
       </c>
-      <c r="R5" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S5" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T5" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3578.5)</f>
-        <v>3578.5</v>
-      </c>
-      <c r="U5" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="V5" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="W5" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),530)</f>
-        <v>530</v>
-      </c>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21"/>
+      <c r="W5" s="21"/>
       <c r="X5" s="7" t="n">
         <f aca="false">SUM(Q5:W5)</f>
         <v>2255243.5</v>
@@ -1941,94 +1890,28 @@
       <c r="A6" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0599939658092665)</f>
-        <v>0.0599939658092665</v>
-      </c>
-      <c r="C6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0599939658092665)</f>
-        <v>0.0599939658092665</v>
-      </c>
-      <c r="D6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0823418371052526)</f>
-        <v>0.0823418371052526</v>
-      </c>
-      <c r="E6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0958991878073455)</f>
-        <v>0.0958991878073455</v>
-      </c>
-      <c r="F6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10379748734495)</f>
-        <v>0.10379748734495</v>
-      </c>
-      <c r="G6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.102624553445736)</f>
-        <v>0.102624553445736</v>
-      </c>
-      <c r="H6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0742053590647476)</f>
-        <v>0.0742053590647476</v>
-      </c>
-      <c r="I6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0870020477881409)</f>
-        <v>0.0870020477881409</v>
-      </c>
-      <c r="J6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0871913152503224)</f>
-        <v>0.0871913152503224</v>
-      </c>
-      <c r="K6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0871913152503224)</f>
-        <v>0.0871913152503224</v>
-      </c>
-      <c r="L6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0792930157127176)</f>
-        <v>0.0792930157127176</v>
-      </c>
-      <c r="M6" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0804659496119317)</f>
-        <v>0.0804659496119317</v>
-      </c>
-      <c r="N6" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9216.54014430766)</f>
-        <v>9216.54014430766</v>
-      </c>
-      <c r="O6" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P6" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),146)</f>
-        <v>146</v>
-      </c>
-      <c r="Q6" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R6" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100435.9)</f>
-        <v>100435.9</v>
-      </c>
-      <c r="S6" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14173.8)</f>
-        <v>14173.8</v>
-      </c>
-      <c r="T6" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45655.1)</f>
-        <v>45655.1</v>
-      </c>
-      <c r="U6" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="V6" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7336.9)</f>
-        <v>7336.9</v>
-      </c>
-      <c r="W6" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6153)</f>
-        <v>6153</v>
-      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="21"/>
+      <c r="R6" s="21"/>
+      <c r="S6" s="21"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="21"/>
+      <c r="V6" s="21"/>
+      <c r="W6" s="21"/>
       <c r="X6" s="7" t="n">
         <f aca="false">SUM(Q6:W6)</f>
         <v>173754.7</v>
@@ -2038,94 +1921,28 @@
       <c r="A7" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0667556231939292)</f>
-        <v>0.0667556231939292</v>
-      </c>
-      <c r="C7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0651024266252983)</f>
-        <v>0.0651024266252983</v>
-      </c>
-      <c r="D7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0817858344236914)</f>
-        <v>0.0817858344236914</v>
-      </c>
-      <c r="E7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0997196200427302)</f>
-        <v>0.0997196200427302</v>
-      </c>
-      <c r="F7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100089910575874)</f>
-        <v>0.100089910575874</v>
-      </c>
-      <c r="G7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0988243995547109)</f>
-        <v>0.0988243995547109</v>
-      </c>
-      <c r="H7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0797892781627565)</f>
-        <v>0.0797892781627565</v>
-      </c>
-      <c r="I7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0795925746996675)</f>
-        <v>0.0795925746996675</v>
-      </c>
-      <c r="J7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0807139532651435)</f>
-        <v>0.0807139532651435</v>
-      </c>
-      <c r="K7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0807139532651435)</f>
-        <v>0.0807139532651435</v>
-      </c>
-      <c r="L7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819968593006307)</f>
-        <v>0.0819968593006307</v>
-      </c>
-      <c r="M7" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0849155668904246)</f>
-        <v>0.0849155668904246</v>
-      </c>
-      <c r="N7" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56059.2707104735)</f>
-        <v>56059.2707104735</v>
-      </c>
-      <c r="O7" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P7" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),855)</f>
-        <v>855</v>
-      </c>
-      <c r="Q7" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69628)</f>
-        <v>69628</v>
-      </c>
-      <c r="R7" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),732591.4)</f>
-        <v>732591.4</v>
-      </c>
-      <c r="S7" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52786.7)</f>
-        <v>52786.7</v>
-      </c>
-      <c r="T7" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8847.8)</f>
-        <v>8847.8</v>
-      </c>
-      <c r="U7" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113431.7)</f>
-        <v>113431.7</v>
-      </c>
-      <c r="V7" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46903.8)</f>
-        <v>46903.8</v>
-      </c>
-      <c r="W7" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5342)</f>
-        <v>5342</v>
-      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
+      <c r="V7" s="21"/>
+      <c r="W7" s="21"/>
       <c r="X7" s="7" t="n">
         <f aca="false">SUM(Q7:W7)</f>
         <v>1029531.4</v>
@@ -2135,94 +1952,28 @@
       <c r="A8" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.064612341974598)</f>
-        <v>0.064612341974598</v>
-      </c>
-      <c r="C8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.064612341974598)</f>
-        <v>0.064612341974598</v>
-      </c>
-      <c r="D8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0831857089056497)</f>
-        <v>0.0831857089056497</v>
-      </c>
-      <c r="E8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101329540689849)</f>
-        <v>0.101329540689849</v>
-      </c>
-      <c r="F8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10227719847342)</f>
-        <v>0.10227719847342</v>
-      </c>
-      <c r="G8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993233886074831)</f>
-        <v>0.0993233886074831</v>
-      </c>
-      <c r="H8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078066397641533)</f>
-        <v>0.078066397641533</v>
-      </c>
-      <c r="I8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078743869594065)</f>
-        <v>0.078743869594065</v>
-      </c>
-      <c r="J8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081697679460002)</f>
-        <v>0.081697679460002</v>
-      </c>
-      <c r="K8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081697679460002)</f>
-        <v>0.081697679460002</v>
-      </c>
-      <c r="L8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0807500216764314)</f>
-        <v>0.0807500216764314</v>
-      </c>
-      <c r="M8" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0837038315423683)</f>
-        <v>0.0837038315423683</v>
-      </c>
-      <c r="N8" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3319.32790518283)</f>
-        <v>3319.32790518283</v>
-      </c>
-      <c r="O8" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P8" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53)</f>
-        <v>53</v>
-      </c>
-      <c r="Q8" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R8" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44900.8)</f>
-        <v>44900.8</v>
-      </c>
-      <c r="S8" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5673.3)</f>
-        <v>5673.3</v>
-      </c>
-      <c r="T8" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2123.5)</f>
-        <v>2123.5</v>
-      </c>
-      <c r="U8" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="V8" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6270.5)</f>
-        <v>6270.5</v>
-      </c>
-      <c r="W8" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
+      <c r="V8" s="21"/>
+      <c r="W8" s="21"/>
       <c r="X8" s="7" t="n">
         <f aca="false">SUM(Q8:W8)</f>
         <v>58968.1</v>
@@ -2232,94 +1983,28 @@
       <c r="A9" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0670768247329043)</f>
-        <v>0.0670768247329043</v>
-      </c>
-      <c r="C9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0670768247329043)</f>
-        <v>0.0670768247329043</v>
-      </c>
-      <c r="D9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0827868661277296)</f>
-        <v>0.0827868661277296</v>
-      </c>
-      <c r="E9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0993493196011858)</f>
-        <v>0.0993493196011858</v>
-      </c>
-      <c r="F9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0999705290370024)</f>
-        <v>0.0999705290370024</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0970461916480882)</f>
-        <v>0.0970461916480882</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0788828581851096)</f>
-        <v>0.0788828581851096</v>
-      </c>
-      <c r="I9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0790330223001652)</f>
-        <v>0.0790330223001652</v>
-      </c>
-      <c r="J9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0817739112794073)</f>
-        <v>0.0817739112794073</v>
-      </c>
-      <c r="K9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0817739112794073)</f>
-        <v>0.0817739112794073</v>
-      </c>
-      <c r="L9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0811527018435908)</f>
-        <v>0.0811527018435908</v>
-      </c>
-      <c r="M9" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.084077039232505)</f>
-        <v>0.084077039232505</v>
-      </c>
-      <c r="N9" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4686.14321768856)</f>
-        <v>4686.14321768856</v>
-      </c>
-      <c r="O9" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P9" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73)</f>
-        <v>73</v>
-      </c>
-      <c r="Q9" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R9" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56716.8)</f>
-        <v>56716.8</v>
-      </c>
-      <c r="S9" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4876.4)</f>
-        <v>4876.4</v>
-      </c>
-      <c r="T9" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1415.6)</f>
-        <v>1415.6</v>
-      </c>
-      <c r="U9" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12568.5)</f>
-        <v>12568.5</v>
-      </c>
-      <c r="V9" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8958.8)</f>
-        <v>8958.8</v>
-      </c>
-      <c r="W9" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),562)</f>
-        <v>562</v>
-      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
+      <c r="V9" s="21"/>
+      <c r="W9" s="21"/>
       <c r="X9" s="7" t="n">
         <f aca="false">SUM(Q9:W9)</f>
         <v>85098.1</v>
@@ -2329,94 +2014,28 @@
       <c r="A10" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B10" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="C10" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="D10" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E10" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F10" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J10" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L10" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="M10" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="N10" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),889.694438407785)</f>
-        <v>889.694438407785</v>
-      </c>
-      <c r="O10" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P10" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12)</f>
-        <v>12</v>
-      </c>
-      <c r="Q10" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R10" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S10" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T10" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U10" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15671.5)</f>
-        <v>15671.5</v>
-      </c>
-      <c r="V10" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="W10" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="21"/>
+      <c r="V10" s="21"/>
+      <c r="W10" s="21"/>
       <c r="X10" s="7" t="n">
         <f aca="false">SUM(Q10:W10)</f>
         <v>15671.5</v>
@@ -2426,94 +2045,28 @@
       <c r="A11" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B11" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="C11" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="D11" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E11" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F11" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="H11" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J11" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K11" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L11" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="M11" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="N11" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),463.773030017405)</f>
-        <v>463.773030017405</v>
-      </c>
-      <c r="O11" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P11" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6)</f>
-        <v>6</v>
-      </c>
-      <c r="Q11" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R11" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S11" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T11" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U11" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9151.4)</f>
-        <v>9151.4</v>
-      </c>
-      <c r="V11" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="W11" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="21"/>
+      <c r="V11" s="21"/>
+      <c r="W11" s="21"/>
       <c r="X11" s="7" t="n">
         <f aca="false">SUM(Q11:W11)</f>
         <v>9151.4</v>
@@ -2523,94 +2076,28 @@
       <c r="A12" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="D12" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E12" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L12" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="M12" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="N12" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),268.09876141114)</f>
-        <v>268.09876141114</v>
-      </c>
-      <c r="O12" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P12" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4)</f>
-        <v>4</v>
-      </c>
-      <c r="Q12" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R12" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S12" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T12" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U12" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4634.7)</f>
-        <v>4634.7</v>
-      </c>
-      <c r="V12" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="W12" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="21"/>
+      <c r="W12" s="21"/>
       <c r="X12" s="7" t="n">
         <f aca="false">SUM(Q12:W12)</f>
         <v>4634.7</v>
@@ -2620,94 +2107,28 @@
       <c r="A13" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0695355190499093)</f>
-        <v>0.0695355190499093</v>
-      </c>
-      <c r="C13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0695355190499093)</f>
-        <v>0.0695355190499093</v>
-      </c>
-      <c r="D13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0838248196490894)</f>
-        <v>0.0838248196490894</v>
-      </c>
-      <c r="E13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0948339806026096)</f>
-        <v>0.0948339806026096</v>
-      </c>
-      <c r="F13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0972184056200527)</f>
-        <v>0.0972184056200527</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0952240073446056)</f>
-        <v>0.0952240073446056</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0780009399043672)</f>
-        <v>0.0780009399043672</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0813247334874215)</f>
-        <v>0.0813247334874215</v>
-      </c>
-      <c r="J13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833191317628686)</f>
-        <v>0.0833191317628686</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833191317628686)</f>
-        <v>0.0833191317628686</v>
-      </c>
-      <c r="L13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809347067454255)</f>
-        <v>0.0809347067454255</v>
-      </c>
-      <c r="M13" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0829291050208727)</f>
-        <v>0.0829291050208727</v>
-      </c>
-      <c r="N13" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2310.99407344162)</f>
-        <v>2310.99407344162</v>
-      </c>
-      <c r="O13" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P13" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35)</f>
-        <v>35</v>
-      </c>
-      <c r="Q13" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R13" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20087.2)</f>
-        <v>20087.2</v>
-      </c>
-      <c r="S13" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4459)</f>
-        <v>4459</v>
-      </c>
-      <c r="T13" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3539.1)</f>
-        <v>3539.1</v>
-      </c>
-      <c r="U13" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8169.7)</f>
-        <v>8169.7</v>
-      </c>
-      <c r="V13" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2804.4)</f>
-        <v>2804.4</v>
-      </c>
-      <c r="W13" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
       <c r="X13" s="7" t="n">
         <f aca="false">SUM(Q13:W13)</f>
         <v>39059.4</v>
@@ -2717,94 +2138,28 @@
       <c r="A14" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0616150736413202)</f>
-        <v>0.0616150736413202</v>
-      </c>
-      <c r="C14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0616150736413202)</f>
-        <v>0.0616150736413202</v>
-      </c>
-      <c r="D14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0829453490803136)</f>
-        <v>0.0829453490803136</v>
-      </c>
-      <c r="E14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.103007646651263)</f>
-        <v>0.103007646651263</v>
-      </c>
-      <c r="F14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.103425871740429)</f>
-        <v>0.103425871740429</v>
-      </c>
-      <c r="G14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.102109899624234)</f>
-        <v>0.102109899624234</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0801282894274162)</f>
-        <v>0.0801282894274162</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.079881877158212)</f>
-        <v>0.079881877158212</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081197849274407)</f>
-        <v>0.081197849274407</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081197849274407)</f>
-        <v>0.081197849274407</v>
-      </c>
-      <c r="L14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.080779624185241)</f>
-        <v>0.080779624185241</v>
-      </c>
-      <c r="M14" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082095596301436)</f>
-        <v>0.082095596301436</v>
-      </c>
-      <c r="N14" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12606.7299522508)</f>
-        <v>12606.7299522508</v>
-      </c>
-      <c r="O14" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P14" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),199)</f>
-        <v>199</v>
-      </c>
-      <c r="Q14" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R14" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),183147.8)</f>
-        <v>183147.8</v>
-      </c>
-      <c r="S14" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19050.2)</f>
-        <v>19050.2</v>
-      </c>
-      <c r="T14" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3539.1)</f>
-        <v>3539.1</v>
-      </c>
-      <c r="U14" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6402.2)</f>
-        <v>6402.2</v>
-      </c>
-      <c r="V14" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10549.9)</f>
-        <v>10549.9</v>
-      </c>
-      <c r="W14" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
       <c r="X14" s="7" t="n">
         <f aca="false">SUM(Q14:W14)</f>
         <v>222689.2</v>
@@ -2814,94 +2169,28 @@
       <c r="A15" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0761848278176029)</f>
-        <v>0.0761848278176029</v>
-      </c>
-      <c r="C15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0761848278176029)</f>
-        <v>0.0761848278176029</v>
-      </c>
-      <c r="D15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826686065765467)</f>
-        <v>0.0826686065765467</v>
-      </c>
-      <c r="E15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0916518877640263)</f>
-        <v>0.0916518877640263</v>
-      </c>
-      <c r="F15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0931955183643168)</f>
-        <v>0.0931955183643168</v>
-      </c>
-      <c r="G15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0888541224858191)</f>
-        <v>0.0888541224858191</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0784912986070083)</f>
-        <v>0.0784912986070083</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0795725784486681)</f>
-        <v>0.0795725784486681</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0829855493601231)</f>
-        <v>0.0829855493601231</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0829855493601231)</f>
-        <v>0.0829855493601231</v>
-      </c>
-      <c r="L15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0814419187598326)</f>
-        <v>0.0814419187598326</v>
-      </c>
-      <c r="M15" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0857833146383303)</f>
-        <v>0.0857833146383303</v>
-      </c>
-      <c r="N15" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4308.38387982745)</f>
-        <v>4308.38387982745</v>
-      </c>
-      <c r="O15" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P15" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64)</f>
-        <v>64</v>
-      </c>
-      <c r="Q15" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25995.2)</f>
-        <v>25995.2</v>
-      </c>
-      <c r="S15" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),891.8)</f>
-        <v>891.8</v>
-      </c>
-      <c r="T15" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1769.6)</f>
-        <v>1769.6</v>
-      </c>
-      <c r="U15" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32678.6)</f>
-        <v>32678.6</v>
-      </c>
-      <c r="V15" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11830.5)</f>
-        <v>11830.5</v>
-      </c>
-      <c r="W15" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2530)</f>
-        <v>2530</v>
-      </c>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="21"/>
+      <c r="V15" s="21"/>
+      <c r="W15" s="21"/>
       <c r="X15" s="7" t="n">
         <f aca="false">SUM(Q15:W15)</f>
         <v>75695.7</v>
@@ -2911,94 +2200,28 @@
       <c r="A16" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0890943915723948)</f>
-        <v>0.0890943915723948</v>
-      </c>
-      <c r="C16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0890943915723948)</f>
-        <v>0.0890943915723948</v>
-      </c>
-      <c r="D16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="G16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0775722750942719)</f>
-        <v>0.0775722750942719</v>
-      </c>
-      <c r="H16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0775722750942719)</f>
-        <v>0.0775722750942719</v>
-      </c>
-      <c r="I16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0775722750942719)</f>
-        <v>0.0775722750942719</v>
-      </c>
-      <c r="J16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="M16" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0890943915723948)</f>
-        <v>0.0890943915723948</v>
-      </c>
-      <c r="N16" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),705.316446113659)</f>
-        <v>705.316446113659</v>
-      </c>
-      <c r="O16" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P16" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11)</f>
-        <v>11</v>
-      </c>
-      <c r="Q16" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R16" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S16" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T16" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U16" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9269.4)</f>
-        <v>9269.4</v>
-      </c>
-      <c r="V16" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2425.5)</f>
-        <v>2425.5</v>
-      </c>
-      <c r="W16" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
+      <c r="V16" s="21"/>
+      <c r="W16" s="21"/>
       <c r="X16" s="7" t="n">
         <f aca="false">SUM(Q16:W16)</f>
         <v>11694.9</v>
@@ -3008,94 +2231,28 @@
       <c r="A17" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B17" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="C17" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="D17" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E17" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F17" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="G17" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="H17" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="I17" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J17" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K17" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L17" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="M17" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="N17" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),242.151440335721)</f>
-        <v>242.151440335721</v>
-      </c>
-      <c r="O17" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P17" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4)</f>
-        <v>4</v>
-      </c>
-      <c r="Q17" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R17" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S17" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T17" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U17" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3535)</f>
-        <v>3535</v>
-      </c>
-      <c r="V17" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="W17" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="21"/>
+      <c r="V17" s="21"/>
+      <c r="W17" s="21"/>
       <c r="X17" s="7" t="n">
         <f aca="false">SUM(Q17:W17)</f>
         <v>3535</v>
@@ -3105,94 +2262,28 @@
       <c r="A18" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741713639081832)</f>
-        <v>0.0741713639081832</v>
-      </c>
-      <c r="C18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741713639081832)</f>
-        <v>0.0741713639081832</v>
-      </c>
-      <c r="D18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826308825789044)</f>
-        <v>0.0826308825789044</v>
-      </c>
-      <c r="E18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0938477438743188)</f>
-        <v>0.0938477438743188</v>
-      </c>
-      <c r="F18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0943031990696216)</f>
-        <v>0.0943031990696216</v>
-      </c>
-      <c r="G18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905972862319092)</f>
-        <v>0.0905972862319092</v>
-      </c>
-      <c r="H18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782229570370311)</f>
-        <v>0.0782229570370311</v>
-      </c>
-      <c r="I18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0788873099187785)</f>
-        <v>0.0788873099187785</v>
-      </c>
-      <c r="J18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0825932227564908)</f>
-        <v>0.0825932227564908</v>
-      </c>
-      <c r="K18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0825932227564908)</f>
-        <v>0.0825932227564908</v>
-      </c>
-      <c r="L18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082137767561188)</f>
-        <v>0.082137767561188</v>
-      </c>
-      <c r="M18" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0858436803989003)</f>
-        <v>0.0858436803989003</v>
-      </c>
-      <c r="N18" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),577.776131502584)</f>
-        <v>577.776131502584</v>
-      </c>
-      <c r="O18" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P18" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9)</f>
-        <v>9</v>
-      </c>
-      <c r="Q18" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R18" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4431)</f>
-        <v>4431</v>
-      </c>
-      <c r="S18" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),199.2)</f>
-        <v>199.2</v>
-      </c>
-      <c r="T18" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177)</f>
-        <v>177</v>
-      </c>
-      <c r="U18" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4055.3)</f>
-        <v>4055.3</v>
-      </c>
-      <c r="V18" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1364.4)</f>
-        <v>1364.4</v>
-      </c>
-      <c r="W18" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="21"/>
+      <c r="V18" s="21"/>
+      <c r="W18" s="21"/>
       <c r="X18" s="7" t="n">
         <f aca="false">SUM(Q18:W18)</f>
         <v>10226.9</v>
@@ -3202,94 +2293,28 @@
       <c r="A19" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741714575622674)</f>
-        <v>0.0741714575622674</v>
-      </c>
-      <c r="C19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741714575622674)</f>
-        <v>0.0741714575622674</v>
-      </c>
-      <c r="D19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.08263095051887)</f>
-        <v>0.08263095051887</v>
-      </c>
-      <c r="E19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0938477343304375)</f>
-        <v>0.0938477343304375</v>
-      </c>
-      <c r="F19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0943030721576538)</f>
-        <v>0.0943030721576538</v>
-      </c>
-      <c r="G19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905972613831472)</f>
-        <v>0.0905972613831472</v>
-      </c>
-      <c r="H19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782232108709845)</f>
-        <v>0.0782232108709845</v>
-      </c>
-      <c r="I19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0788872954792544)</f>
-        <v>0.0788872954792544</v>
-      </c>
-      <c r="J19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082593106253761)</f>
-        <v>0.082593106253761</v>
-      </c>
-      <c r="K19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082593106253761)</f>
-        <v>0.082593106253761</v>
-      </c>
-      <c r="L19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0821377684265447)</f>
-        <v>0.0821377684265447</v>
-      </c>
-      <c r="M19" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0858435792010512)</f>
-        <v>0.0858435792010512</v>
-      </c>
-      <c r="N19" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1271.10748852936)</f>
-        <v>1271.10748852936</v>
-      </c>
-      <c r="O19" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P19" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19)</f>
-        <v>19</v>
-      </c>
-      <c r="Q19" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R19" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9748.2)</f>
-        <v>9748.2</v>
-      </c>
-      <c r="S19" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),438.3)</f>
-        <v>438.3</v>
-      </c>
-      <c r="T19" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),389.3)</f>
-        <v>389.3</v>
-      </c>
-      <c r="U19" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8921.8)</f>
-        <v>8921.8</v>
-      </c>
-      <c r="V19" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3001.6)</f>
-        <v>3001.6</v>
-      </c>
-      <c r="W19" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="21"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="21"/>
+      <c r="U19" s="21"/>
+      <c r="V19" s="21"/>
+      <c r="W19" s="21"/>
       <c r="X19" s="7" t="n">
         <f aca="false">SUM(Q19:W19)</f>
         <v>22499.2</v>
@@ -3299,94 +2324,28 @@
       <c r="A20" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741714711262728)</f>
-        <v>0.0741714711262728</v>
-      </c>
-      <c r="C20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741714711262728)</f>
-        <v>0.0741714711262728</v>
-      </c>
-      <c r="D20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826308668449537)</f>
-        <v>0.0826308668449537</v>
-      </c>
-      <c r="E20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0938479481909226)</f>
-        <v>0.0938479481909226</v>
-      </c>
-      <c r="F20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0943030828496681)</f>
-        <v>0.0943030828496681</v>
-      </c>
-      <c r="G20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905972288565807)</f>
-        <v>0.0905972288565807</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782233613395939)</f>
-        <v>0.0782233613395939</v>
-      </c>
-      <c r="I20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0788871138035579)</f>
-        <v>0.0788871138035579</v>
-      </c>
-      <c r="J20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0825929677966453)</f>
-        <v>0.0825929677966453</v>
-      </c>
-      <c r="K20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0825929677966453)</f>
-        <v>0.0825929677966453</v>
-      </c>
-      <c r="L20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0821378331378998)</f>
-        <v>0.0821378331378998</v>
-      </c>
-      <c r="M20" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0858436871309872)</f>
-        <v>0.0858436871309872</v>
-      </c>
-      <c r="N20" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),277.332543143421)</f>
-        <v>277.332543143421</v>
-      </c>
-      <c r="O20" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P20" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5)</f>
-        <v>5</v>
-      </c>
-      <c r="Q20" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R20" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2126.9)</f>
-        <v>2126.9</v>
-      </c>
-      <c r="S20" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.6)</f>
-        <v>95.6</v>
-      </c>
-      <c r="T20" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),84.9)</f>
-        <v>84.9</v>
-      </c>
-      <c r="U20" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1946.6)</f>
-        <v>1946.6</v>
-      </c>
-      <c r="V20" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),654.9)</f>
-        <v>654.9</v>
-      </c>
-      <c r="W20" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="21"/>
+      <c r="R20" s="21"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="21"/>
+      <c r="U20" s="21"/>
+      <c r="V20" s="21"/>
+      <c r="W20" s="21"/>
       <c r="X20" s="7" t="n">
         <f aca="false">SUM(Q20:W20)</f>
         <v>4908.9</v>
@@ -3396,94 +2355,28 @@
       <c r="A21" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741721346584101)</f>
-        <v>0.0741721346584101</v>
-      </c>
-      <c r="C21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0741721346584101)</f>
-        <v>0.0741721346584101</v>
-      </c>
-      <c r="D21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826312550911103)</f>
-        <v>0.0826312550911103</v>
-      </c>
-      <c r="E21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0938475454254633)</f>
-        <v>0.0938475454254633</v>
-      </c>
-      <c r="F21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0943026800842088)</f>
-        <v>0.0943026800842088</v>
-      </c>
-      <c r="G21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0905968260911214)</f>
-        <v>0.0905968260911214</v>
-      </c>
-      <c r="H21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782234917229329)</f>
-        <v>0.0782234917229329</v>
-      </c>
-      <c r="I21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0788869863240794)</f>
-        <v>0.0788869863240794</v>
-      </c>
-      <c r="J21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0825928403171668)</f>
-        <v>0.0825928403171668</v>
-      </c>
-      <c r="K21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0825928403171668)</f>
-        <v>0.0825928403171668</v>
-      </c>
-      <c r="L21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0821377056584213)</f>
-        <v>0.0821377056584213</v>
-      </c>
-      <c r="M21" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0858435596515087)</f>
-        <v>0.0858435596515087</v>
-      </c>
-      <c r="N21" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),184.888361725934)</f>
-        <v>184.888361725934</v>
-      </c>
-      <c r="O21" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P21" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3)</f>
-        <v>3</v>
-      </c>
-      <c r="Q21" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R21" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1417.9)</f>
-        <v>1417.9</v>
-      </c>
-      <c r="S21" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.8)</f>
-        <v>63.8</v>
-      </c>
-      <c r="T21" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.6)</f>
-        <v>56.6</v>
-      </c>
-      <c r="U21" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1297.7)</f>
-        <v>1297.7</v>
-      </c>
-      <c r="V21" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),436.6)</f>
-        <v>436.6</v>
-      </c>
-      <c r="W21" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="21"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="21"/>
+      <c r="R21" s="21"/>
+      <c r="S21" s="21"/>
+      <c r="T21" s="21"/>
+      <c r="U21" s="21"/>
+      <c r="V21" s="21"/>
+      <c r="W21" s="21"/>
       <c r="X21" s="7" t="n">
         <f aca="false">SUM(Q21:W21)</f>
         <v>3272.6</v>
@@ -3493,54 +2386,18 @@
       <c r="A22" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.094685974590863)</f>
-        <v>0.094685974590863</v>
-      </c>
-      <c r="C22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0813589828439731)</f>
-        <v>0.0813589828439731</v>
-      </c>
-      <c r="D22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0763711312806997)</f>
-        <v>0.0763711312806997</v>
-      </c>
-      <c r="E22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.084183445923961)</f>
-        <v>0.084183445923961</v>
-      </c>
-      <c r="F22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0847815688752799)</f>
-        <v>0.0847815688752799</v>
-      </c>
-      <c r="G22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0840164331631308)</f>
-        <v>0.0840164331631308</v>
-      </c>
-      <c r="H22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0748812526033842)</f>
-        <v>0.0748812526033842</v>
-      </c>
-      <c r="I22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0755102802186843)</f>
-        <v>0.0755102802186843</v>
-      </c>
-      <c r="J22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0761652663624608)</f>
-        <v>0.0761652663624608</v>
-      </c>
-      <c r="K22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0761652663624608)</f>
-        <v>0.0761652663624608</v>
-      </c>
-      <c r="L22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0888941351580317)</f>
-        <v>0.0888941351580317</v>
-      </c>
-      <c r="M22" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.102986262617071)</f>
-        <v>0.102986262617071</v>
-      </c>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
       <c r="N22" s="7" t="n">
         <f aca="false">SUM(N5:N21)</f>
         <v>206230.154921912</v>
@@ -3558,30 +2415,12 @@
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""sobrestock_sustitutos!B18:H18"")"),9)</f>
         <v>9</v>
       </c>
-      <c r="R23" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15)</f>
-        <v>15</v>
-      </c>
-      <c r="S23" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12)</f>
-        <v>12</v>
-      </c>
-      <c r="T23" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11)</f>
-        <v>11</v>
-      </c>
-      <c r="U23" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10)</f>
-        <v>10</v>
-      </c>
-      <c r="V23" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),61)</f>
-        <v>61</v>
-      </c>
-      <c r="W23" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6)</f>
-        <v>6</v>
-      </c>
+      <c r="R23" s="22"/>
+      <c r="S23" s="22"/>
+      <c r="T23" s="22"/>
+      <c r="U23" s="22"/>
+      <c r="V23" s="22"/>
+      <c r="W23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
@@ -3650,368 +2489,119 @@
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$4,""parametros_recargas!E35:P41"")"),0.12)</f>
         <v>0.12</v>
       </c>
-      <c r="C28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955555555555556)</f>
-        <v>0.0955555555555556</v>
-      </c>
-      <c r="D28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="E28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="G28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="H28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="I28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="J28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="K28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="L28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955555555555556)</f>
-        <v>0.0955555555555556</v>
-      </c>
-      <c r="M28" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.12)</f>
-        <v>0.12</v>
-      </c>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0540540540540541)</f>
-        <v>0.0540540540540541</v>
-      </c>
-      <c r="C29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0540540540540541)</f>
-        <v>0.0540540540540541</v>
-      </c>
-      <c r="D29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
-        <v>0.0810810810810811</v>
-      </c>
-      <c r="E29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.108108108108108)</f>
-        <v>0.108108108108108</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.108108108108108)</f>
-        <v>0.108108108108108</v>
-      </c>
-      <c r="G29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.108108108108108)</f>
-        <v>0.108108108108108</v>
-      </c>
-      <c r="H29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
-        <v>0.0810810810810811</v>
-      </c>
-      <c r="I29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
-        <v>0.0810810810810811</v>
-      </c>
-      <c r="J29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
-        <v>0.0810810810810811</v>
-      </c>
-      <c r="K29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
-        <v>0.0810810810810811</v>
-      </c>
-      <c r="L29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
-        <v>0.0810810810810811</v>
-      </c>
-      <c r="M29" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
-        <v>0.0810810810810811</v>
-      </c>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10126582278481)</f>
-        <v>0.10126582278481</v>
-      </c>
-      <c r="C30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10126582278481)</f>
-        <v>0.10126582278481</v>
-      </c>
-      <c r="D30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10126582278481)</f>
-        <v>0.10126582278481</v>
-      </c>
-      <c r="E30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
-      <c r="F30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
-      <c r="G30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
-      <c r="H30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0886075949367089)</f>
-        <v>0.0886075949367089</v>
-      </c>
-      <c r="I30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
-      <c r="J30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
-      <c r="K30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
-      <c r="L30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
-      <c r="M30" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0526315789473684)</f>
-        <v>0.0526315789473684</v>
-      </c>
-      <c r="C31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0526315789473684)</f>
-        <v>0.0526315789473684</v>
-      </c>
-      <c r="D31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
-        <v>0.0789473684210526</v>
-      </c>
-      <c r="E31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
-        <v>0.0789473684210526</v>
-      </c>
-      <c r="F31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
-        <v>0.105263157894737</v>
-      </c>
-      <c r="G31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
-        <v>0.105263157894737</v>
-      </c>
-      <c r="H31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0526315789473684)</f>
-        <v>0.0526315789473684</v>
-      </c>
-      <c r="I31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
-        <v>0.105263157894737</v>
-      </c>
-      <c r="J31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
-        <v>0.105263157894737</v>
-      </c>
-      <c r="K31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
-        <v>0.105263157894737</v>
-      </c>
-      <c r="L31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
-        <v>0.0789473684210526</v>
-      </c>
-      <c r="M31" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
-        <v>0.0789473684210526</v>
-      </c>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B32" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="C32" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="D32" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E32" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F32" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="G32" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="H32" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="I32" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J32" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K32" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L32" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="M32" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
-        <v>0.111111111111111</v>
-      </c>
-      <c r="C33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
-        <v>0.111111111111111</v>
-      </c>
-      <c r="D33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="G33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
-        <v>0.0555555555555556</v>
-      </c>
-      <c r="H33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
-        <v>0.0555555555555556</v>
-      </c>
-      <c r="I33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
-        <v>0.0555555555555556</v>
-      </c>
-      <c r="J33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="M33" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
-        <v>0.111111111111111</v>
-      </c>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
-        <v>0.0555555555555556</v>
-      </c>
-      <c r="C34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
-        <v>0.0555555555555556</v>
-      </c>
-      <c r="D34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
-        <v>0.111111111111111</v>
-      </c>
-      <c r="G34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
-        <v>0.111111111111111</v>
-      </c>
-      <c r="H34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
-        <v>0.111111111111111</v>
-      </c>
-      <c r="I34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
-        <v>0.111111111111111</v>
-      </c>
-      <c r="J34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
-        <v>0.0555555555555556</v>
-      </c>
-      <c r="M34" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
-        <v>0.0555555555555556</v>
-      </c>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
@@ -4100,50 +2690,17 @@
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""parametros_recargas!E55:P72"")"),0.119895289559294)</f>
         <v>0.119895289559294</v>
       </c>
-      <c r="C39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0954891339827875)</f>
-        <v>0.0954891339827875</v>
-      </c>
-      <c r="D39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.071124604952686)</f>
-        <v>0.071124604952686</v>
-      </c>
-      <c r="E39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.071124604952686)</f>
-        <v>0.071124604952686</v>
-      </c>
-      <c r="F39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711662314990906)</f>
-        <v>0.0711662314990906</v>
-      </c>
-      <c r="G39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711662314990906)</f>
-        <v>0.0711662314990906</v>
-      </c>
-      <c r="H39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0710984243903592)</f>
-        <v>0.0710984243903592</v>
-      </c>
-      <c r="I39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711662314990906)</f>
-        <v>0.0711662314990906</v>
-      </c>
-      <c r="J39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711585085070517)</f>
-        <v>0.0711585085070517</v>
-      </c>
-      <c r="K39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711585085070517)</f>
-        <v>0.0711585085070517</v>
-      </c>
-      <c r="L39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955230375371532)</f>
-        <v>0.0955230375371532</v>
-      </c>
-      <c r="M39" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.119929193113659)</f>
-        <v>0.119929193113659</v>
-      </c>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="20"/>
       <c r="N39" s="21" t="n">
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""datos_base!K2:K18"")"),56575.8368575054)</f>
         <v>56575.8368575054</v>
@@ -4160,30 +2717,12 @@
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""PROY_Indexado!B57:H73"")"),1188664)</f>
         <v>1188664</v>
       </c>
-      <c r="R39" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S39" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T39" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1533.8)</f>
-        <v>1533.8</v>
-      </c>
-      <c r="U39" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="V39" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="W39" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),331)</f>
-        <v>331</v>
-      </c>
+      <c r="R39" s="21"/>
+      <c r="S39" s="21"/>
+      <c r="T39" s="21"/>
+      <c r="U39" s="21"/>
+      <c r="V39" s="21"/>
+      <c r="W39" s="21"/>
       <c r="X39" s="7" t="n">
         <f aca="false">SUM(Q39:W39)</f>
         <v>1190528.8</v>
@@ -4193,94 +2732,28 @@
       <c r="A40" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0608346558815601)</f>
-        <v>0.0608346558815601</v>
-      </c>
-      <c r="C40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0608346558815601)</f>
-        <v>0.0608346558815601</v>
-      </c>
-      <c r="D40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082643351275423)</f>
-        <v>0.082643351275423</v>
-      </c>
-      <c r="E40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0953382202836263)</f>
-        <v>0.0953382202836263</v>
-      </c>
-      <c r="F40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.103308847602848)</f>
-        <v>0.103308847602848</v>
-      </c>
-      <c r="G40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10204440072004)</f>
-        <v>0.10204440072004</v>
-      </c>
-      <c r="H40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0745034484311485)</f>
-        <v>0.0745034484311485</v>
-      </c>
-      <c r="I40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0869418857625907)</f>
-        <v>0.0869418857625907</v>
-      </c>
-      <c r="J40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0870568354792096)</f>
-        <v>0.0870568354792096</v>
-      </c>
-      <c r="K40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0870568354792096)</f>
-        <v>0.0870568354792096</v>
-      </c>
-      <c r="L40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0790862081599875)</f>
-        <v>0.0790862081599875</v>
-      </c>
-      <c r="M40" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.080350655042796)</f>
-        <v>0.080350655042796</v>
-      </c>
-      <c r="N40" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4790.71011839089)</f>
-        <v>4790.71011839089</v>
-      </c>
-      <c r="O40" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P40" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76)</f>
-        <v>76</v>
-      </c>
-      <c r="Q40" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R40" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51231.6)</f>
-        <v>51231.6</v>
-      </c>
-      <c r="S40" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8719.2)</f>
-        <v>8719.2</v>
-      </c>
-      <c r="T40" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23764.4)</f>
-        <v>23764.4</v>
-      </c>
-      <c r="U40" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="V40" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4173.4)</f>
-        <v>4173.4</v>
-      </c>
-      <c r="W40" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3794)</f>
-        <v>3794</v>
-      </c>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="20"/>
+      <c r="N40" s="21"/>
+      <c r="O40" s="22"/>
+      <c r="P40" s="21"/>
+      <c r="Q40" s="21"/>
+      <c r="R40" s="21"/>
+      <c r="S40" s="21"/>
+      <c r="T40" s="21"/>
+      <c r="U40" s="21"/>
+      <c r="V40" s="21"/>
+      <c r="W40" s="21"/>
       <c r="X40" s="7" t="n">
         <f aca="false">SUM(Q40:W40)</f>
         <v>91682.6</v>
@@ -4290,94 +2763,28 @@
       <c r="A41" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0669778155176287)</f>
-        <v>0.0669778155176287</v>
-      </c>
-      <c r="C41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0652614335824934)</f>
-        <v>0.0652614335824934</v>
-      </c>
-      <c r="D41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819248891202413)</f>
-        <v>0.0819248891202413</v>
-      </c>
-      <c r="E41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0996461832727322)</f>
-        <v>0.0996461832727322</v>
-      </c>
-      <c r="F41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100150076298148)</f>
-        <v>0.100150076298148</v>
-      </c>
-      <c r="G41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0987344570187928)</f>
-        <v>0.0987344570187928</v>
-      </c>
-      <c r="H41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0795692614778467)</f>
-        <v>0.0795692614778467</v>
-      </c>
-      <c r="I41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0794428932919701)</f>
-        <v>0.0794428932919701</v>
-      </c>
-      <c r="J41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0806840028465543)</f>
-        <v>0.0806840028465543</v>
-      </c>
-      <c r="K41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0806840028465543)</f>
-        <v>0.0806840028465543</v>
-      </c>
-      <c r="L41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0818964917562743)</f>
-        <v>0.0818964917562743</v>
-      </c>
-      <c r="M41" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0850284929707643)</f>
-        <v>0.0850284929707643</v>
-      </c>
-      <c r="N41" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29139.3203107948)</f>
-        <v>29139.3203107948</v>
-      </c>
-      <c r="O41" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P41" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),446)</f>
-        <v>446</v>
-      </c>
-      <c r="Q41" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36760)</f>
-        <v>36760</v>
-      </c>
-      <c r="R41" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),373689.5)</f>
-        <v>373689.5</v>
-      </c>
-      <c r="S41" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32472.3)</f>
-        <v>32472.3</v>
-      </c>
-      <c r="T41" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6552.8)</f>
-        <v>6552.8</v>
-      </c>
-      <c r="U41" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44086.3)</f>
-        <v>44086.3</v>
-      </c>
-      <c r="V41" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26680.3)</f>
-        <v>26680.3</v>
-      </c>
-      <c r="W41" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3289)</f>
-        <v>3289</v>
-      </c>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="21"/>
+      <c r="O41" s="22"/>
+      <c r="P41" s="21"/>
+      <c r="Q41" s="21"/>
+      <c r="R41" s="21"/>
+      <c r="S41" s="21"/>
+      <c r="T41" s="21"/>
+      <c r="U41" s="21"/>
+      <c r="V41" s="21"/>
+      <c r="W41" s="21"/>
       <c r="X41" s="7" t="n">
         <f aca="false">SUM(Q41:W41)</f>
         <v>523530.2</v>
@@ -4387,94 +2794,28 @@
       <c r="A42" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0656624516770873)</f>
-        <v>0.0656624516770873</v>
-      </c>
-      <c r="C42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0656624516770873)</f>
-        <v>0.0656624516770873</v>
-      </c>
-      <c r="D42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0834634227222184)</f>
-        <v>0.0834634227222184</v>
-      </c>
-      <c r="E42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100292059397134)</f>
-        <v>0.100292059397134</v>
-      </c>
-      <c r="F42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101604548245527)</f>
-        <v>0.101604548245527</v>
-      </c>
-      <c r="G42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0984624354955731)</f>
-        <v>0.0984624354955731</v>
-      </c>
-      <c r="H42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776078419879838)</f>
-        <v>0.0776078419879838</v>
-      </c>
-      <c r="I42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0788318405488818)</f>
-        <v>0.0788318405488818</v>
-      </c>
-      <c r="J42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819739532988352)</f>
-        <v>0.0819739532988352</v>
-      </c>
-      <c r="K42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819739532988352)</f>
-        <v>0.0819739532988352</v>
-      </c>
-      <c r="L42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0806614644504421)</f>
-        <v>0.0806614644504421</v>
-      </c>
-      <c r="M42" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0838035772003955)</f>
-        <v>0.0838035772003955</v>
-      </c>
-      <c r="N42" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1725.36955653994)</f>
-        <v>1725.36955653994</v>
-      </c>
-      <c r="O42" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P42" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28)</f>
-        <v>28</v>
-      </c>
-      <c r="Q42" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R42" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22903.5)</f>
-        <v>22903.5</v>
-      </c>
-      <c r="S42" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3490)</f>
-        <v>3490</v>
-      </c>
-      <c r="T42" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1572.7)</f>
-        <v>1572.7</v>
-      </c>
-      <c r="U42" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="V42" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3566.9)</f>
-        <v>3566.9</v>
-      </c>
-      <c r="W42" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="21"/>
+      <c r="O42" s="22"/>
+      <c r="P42" s="21"/>
+      <c r="Q42" s="21"/>
+      <c r="R42" s="21"/>
+      <c r="S42" s="21"/>
+      <c r="T42" s="21"/>
+      <c r="U42" s="21"/>
+      <c r="V42" s="21"/>
+      <c r="W42" s="21"/>
       <c r="X42" s="7" t="n">
         <f aca="false">SUM(Q42:W42)</f>
         <v>31533.1</v>
@@ -4484,94 +2825,28 @@
       <c r="A43" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0671288961017088)</f>
-        <v>0.0671288961017088</v>
-      </c>
-      <c r="C43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0671288961017088)</f>
-        <v>0.0671288961017088</v>
-      </c>
-      <c r="D43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082960331994099)</f>
-        <v>0.082960331994099</v>
-      </c>
-      <c r="E43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0994555948834204)</f>
-        <v>0.0994555948834204</v>
-      </c>
-      <c r="F43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.100324801949947)</f>
-        <v>0.100324801949947</v>
-      </c>
-      <c r="G43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0970172977837637)</f>
-        <v>0.0970172977837637</v>
-      </c>
-      <c r="H43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0783455208911489)</f>
-        <v>0.0783455208911489</v>
-      </c>
-      <c r="I43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.078747564791717)</f>
-        <v>0.078747564791717</v>
-      </c>
-      <c r="J43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0818305013673391)</f>
-        <v>0.0818305013673391</v>
-      </c>
-      <c r="K43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0818305013673391)</f>
-        <v>0.0818305013673391</v>
-      </c>
-      <c r="L43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0809612943008125)</f>
-        <v>0.0809612943008125</v>
-      </c>
-      <c r="M43" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0842687984669957)</f>
-        <v>0.0842687984669957</v>
-      </c>
-      <c r="N43" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2435.83311933763)</f>
-        <v>2435.83311933763</v>
-      </c>
-      <c r="O43" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P43" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39)</f>
-        <v>39</v>
-      </c>
-      <c r="Q43" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R43" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28930.8)</f>
-        <v>28930.8</v>
-      </c>
-      <c r="S43" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2999.8)</f>
-        <v>2999.8</v>
-      </c>
-      <c r="T43" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1048.4)</f>
-        <v>1048.4</v>
-      </c>
-      <c r="U43" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4377.3)</f>
-        <v>4377.3</v>
-      </c>
-      <c r="V43" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5096)</f>
-        <v>5096</v>
-      </c>
-      <c r="W43" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),346)</f>
-        <v>346</v>
-      </c>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="21"/>
+      <c r="O43" s="22"/>
+      <c r="P43" s="21"/>
+      <c r="Q43" s="21"/>
+      <c r="R43" s="21"/>
+      <c r="S43" s="21"/>
+      <c r="T43" s="21"/>
+      <c r="U43" s="21"/>
+      <c r="V43" s="21"/>
+      <c r="W43" s="21"/>
       <c r="X43" s="7" t="n">
         <f aca="false">SUM(Q43:W43)</f>
         <v>42798.3</v>
@@ -4581,94 +2856,28 @@
       <c r="A44" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B44" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="C44" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="D44" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E44" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F44" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="G44" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="H44" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="I44" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J44" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K44" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L44" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="M44" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="N44" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),462.458588756731)</f>
-        <v>462.458588756731</v>
-      </c>
-      <c r="O44" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P44" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6)</f>
-        <v>6</v>
-      </c>
-      <c r="Q44" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R44" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S44" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T44" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U44" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6232.7)</f>
-        <v>6232.7</v>
-      </c>
-      <c r="V44" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="W44" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="21"/>
+      <c r="O44" s="22"/>
+      <c r="P44" s="21"/>
+      <c r="Q44" s="21"/>
+      <c r="R44" s="21"/>
+      <c r="S44" s="21"/>
+      <c r="T44" s="21"/>
+      <c r="U44" s="21"/>
+      <c r="V44" s="21"/>
+      <c r="W44" s="21"/>
       <c r="X44" s="7" t="n">
         <f aca="false">SUM(Q44:W44)</f>
         <v>6232.7</v>
@@ -4678,94 +2887,28 @@
       <c r="A45" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B45" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="C45" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="D45" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E45" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F45" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="G45" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="H45" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="I45" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J45" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K45" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L45" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="M45" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="N45" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),241.066833405312)</f>
-        <v>241.066833405312</v>
-      </c>
-      <c r="O45" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P45" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4)</f>
-        <v>4</v>
-      </c>
-      <c r="Q45" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R45" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S45" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T45" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U45" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3220.9)</f>
-        <v>3220.9</v>
-      </c>
-      <c r="V45" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="W45" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="20"/>
+      <c r="N45" s="21"/>
+      <c r="O45" s="22"/>
+      <c r="P45" s="21"/>
+      <c r="Q45" s="21"/>
+      <c r="R45" s="21"/>
+      <c r="S45" s="21"/>
+      <c r="T45" s="21"/>
+      <c r="U45" s="21"/>
+      <c r="V45" s="21"/>
+      <c r="W45" s="21"/>
       <c r="X45" s="7" t="n">
         <f aca="false">SUM(Q45:W45)</f>
         <v>3220.9</v>
@@ -4775,94 +2918,28 @@
       <c r="A46" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B46" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="C46" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="D46" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E46" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F46" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="G46" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="H46" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="I46" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J46" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K46" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L46" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="M46" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="N46" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),139.356355954645)</f>
-        <v>139.356355954645</v>
-      </c>
-      <c r="O46" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P46" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2)</f>
-        <v>2</v>
-      </c>
-      <c r="Q46" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R46" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S46" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T46" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U46" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1816.2)</f>
-        <v>1816.2</v>
-      </c>
-      <c r="V46" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="W46" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20"/>
+      <c r="M46" s="20"/>
+      <c r="N46" s="21"/>
+      <c r="O46" s="22"/>
+      <c r="P46" s="21"/>
+      <c r="Q46" s="21"/>
+      <c r="R46" s="21"/>
+      <c r="S46" s="21"/>
+      <c r="T46" s="21"/>
+      <c r="U46" s="21"/>
+      <c r="V46" s="21"/>
+      <c r="W46" s="21"/>
       <c r="X46" s="7" t="n">
         <f aca="false">SUM(Q46:W46)</f>
         <v>1816.2</v>
@@ -4872,94 +2949,28 @@
       <c r="A47" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0693955234457278)</f>
-        <v>0.0693955234457278</v>
-      </c>
-      <c r="C47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0693955234457278)</f>
-        <v>0.0693955234457278</v>
-      </c>
-      <c r="D47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0840431757641277)</f>
-        <v>0.0840431757641277</v>
-      </c>
-      <c r="E47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0941202036639783)</f>
-        <v>0.0941202036639783</v>
-      </c>
-      <c r="F47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0974702272576739)</f>
-        <v>0.0974702272576739</v>
-      </c>
-      <c r="G47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.095318136848291)</f>
-        <v>0.095318136848291</v>
-      </c>
-      <c r="H47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.076854716143931)</f>
-        <v>0.076854716143931</v>
-      </c>
-      <c r="I47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0818684177142039)</f>
-        <v>0.0818684177142039</v>
-      </c>
-      <c r="J47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0840205081235868)</f>
-        <v>0.0840205081235868</v>
-      </c>
-      <c r="K47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0840205081235868)</f>
-        <v>0.0840205081235868</v>
-      </c>
-      <c r="L47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0806704845298912)</f>
-        <v>0.0806704845298912</v>
-      </c>
-      <c r="M47" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082822574939274)</f>
-        <v>0.082822574939274</v>
-      </c>
-      <c r="N47" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1201.24282190818)</f>
-        <v>1201.24282190818</v>
-      </c>
-      <c r="O47" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P47" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19)</f>
-        <v>19</v>
-      </c>
-      <c r="Q47" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R47" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10246.3)</f>
-        <v>10246.3</v>
-      </c>
-      <c r="S47" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2743)</f>
-        <v>2743</v>
-      </c>
-      <c r="T47" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2621.1)</f>
-        <v>2621.1</v>
-      </c>
-      <c r="U47" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3384.2)</f>
-        <v>3384.2</v>
-      </c>
-      <c r="V47" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1595.2)</f>
-        <v>1595.2</v>
-      </c>
-      <c r="W47" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
+      <c r="M47" s="20"/>
+      <c r="N47" s="21"/>
+      <c r="O47" s="22"/>
+      <c r="P47" s="21"/>
+      <c r="Q47" s="21"/>
+      <c r="R47" s="21"/>
+      <c r="S47" s="21"/>
+      <c r="T47" s="21"/>
+      <c r="U47" s="21"/>
+      <c r="V47" s="21"/>
+      <c r="W47" s="21"/>
       <c r="X47" s="7" t="n">
         <f aca="false">SUM(Q47:W47)</f>
         <v>20589.8</v>
@@ -4969,94 +2980,28 @@
       <c r="A48" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0623734752667158)</f>
-        <v>0.0623734752667158</v>
-      </c>
-      <c r="C48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0623734752667158)</f>
-        <v>0.0623734752667158</v>
-      </c>
-      <c r="D48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0832322896847601)</f>
-        <v>0.0832322896847601</v>
-      </c>
-      <c r="E48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.102381291624983)</f>
-        <v>0.102381291624983</v>
-      </c>
-      <c r="F48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10297405651463)</f>
-        <v>0.10297405651463</v>
-      </c>
-      <c r="G48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.101541503044586)</f>
-        <v>0.101541503044586</v>
-      </c>
-      <c r="H48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0799321707959588)</f>
-        <v>0.0799321707959588</v>
-      </c>
-      <c r="I48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0798429000461445)</f>
-        <v>0.0798429000461445</v>
-      </c>
-      <c r="J48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081275453516189)</f>
-        <v>0.081275453516189</v>
-      </c>
-      <c r="K48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081275453516189)</f>
-        <v>0.081275453516189</v>
-      </c>
-      <c r="L48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0806826886265415)</f>
-        <v>0.0806826886265415</v>
-      </c>
-      <c r="M48" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0821152420965861)</f>
-        <v>0.0821152420965861</v>
-      </c>
-      <c r="N48" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6552.91332717418)</f>
-        <v>6552.91332717418</v>
-      </c>
-      <c r="O48" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P48" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103)</f>
-        <v>103</v>
-      </c>
-      <c r="Q48" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R48" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),93422.4)</f>
-        <v>93422.4</v>
-      </c>
-      <c r="S48" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11718.9)</f>
-        <v>11718.9</v>
-      </c>
-      <c r="T48" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2621.1)</f>
-        <v>2621.1</v>
-      </c>
-      <c r="U48" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2600.2)</f>
-        <v>2600.2</v>
-      </c>
-      <c r="V48" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6001.1)</f>
-        <v>6001.1</v>
-      </c>
-      <c r="W48" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
+      <c r="M48" s="20"/>
+      <c r="N48" s="21"/>
+      <c r="O48" s="22"/>
+      <c r="P48" s="21"/>
+      <c r="Q48" s="21"/>
+      <c r="R48" s="21"/>
+      <c r="S48" s="21"/>
+      <c r="T48" s="21"/>
+      <c r="U48" s="21"/>
+      <c r="V48" s="21"/>
+      <c r="W48" s="21"/>
       <c r="X48" s="7" t="n">
         <f aca="false">SUM(Q48:W48)</f>
         <v>116363.7</v>
@@ -5066,94 +3011,28 @@
       <c r="A49" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758899515991334)</f>
-        <v>0.0758899515991334</v>
-      </c>
-      <c r="C49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0758899515991334)</f>
-        <v>0.0758899515991334</v>
-      </c>
-      <c r="D49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.082635648810499)</f>
-        <v>0.082635648810499</v>
-      </c>
-      <c r="E49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0919604223371936)</f>
-        <v>0.0919604223371936</v>
-      </c>
-      <c r="F49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.094065383152575)</f>
-        <v>0.094065383152575</v>
-      </c>
-      <c r="G49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0890054041756688)</f>
-        <v>0.0890054041756688</v>
-      </c>
-      <c r="H49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0776256551320905)</f>
-        <v>0.0776256551320905</v>
-      </c>
-      <c r="I49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0793046888027784)</f>
-        <v>0.0793046888027784</v>
-      </c>
-      <c r="J49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0831932092611961)</f>
-        <v>0.0831932092611961</v>
-      </c>
-      <c r="K49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0831932092611961)</f>
-        <v>0.0831932092611961</v>
-      </c>
-      <c r="L49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810882484458147)</f>
-        <v>0.0810882484458147</v>
-      </c>
-      <c r="M49" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0861482274227209)</f>
-        <v>0.0861482274227209</v>
-      </c>
-      <c r="N49" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2239.47576029921)</f>
-        <v>2239.47576029921</v>
-      </c>
-      <c r="O49" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P49" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34)</f>
-        <v>34</v>
-      </c>
-      <c r="Q49" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R49" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13260)</f>
-        <v>13260</v>
-      </c>
-      <c r="S49" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),548.6)</f>
-        <v>548.6</v>
-      </c>
-      <c r="T49" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1310.5)</f>
-        <v>1310.5</v>
-      </c>
-      <c r="U49" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13536.8)</f>
-        <v>13536.8</v>
-      </c>
-      <c r="V49" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6729.6)</f>
-        <v>6729.6</v>
-      </c>
-      <c r="W49" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1558)</f>
-        <v>1558</v>
-      </c>
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+      <c r="K49" s="20"/>
+      <c r="L49" s="20"/>
+      <c r="M49" s="20"/>
+      <c r="N49" s="21"/>
+      <c r="O49" s="22"/>
+      <c r="P49" s="21"/>
+      <c r="Q49" s="21"/>
+      <c r="R49" s="21"/>
+      <c r="S49" s="21"/>
+      <c r="T49" s="21"/>
+      <c r="U49" s="21"/>
+      <c r="V49" s="21"/>
+      <c r="W49" s="21"/>
       <c r="X49" s="7" t="n">
         <f aca="false">SUM(Q49:W49)</f>
         <v>36943.5</v>
@@ -5163,94 +3042,28 @@
       <c r="A50" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0909796762566006)</f>
-        <v>0.0909796762566006</v>
-      </c>
-      <c r="C50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0909796762566006)</f>
-        <v>0.0909796762566006</v>
-      </c>
-      <c r="D50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="G50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0756869904100661)</f>
-        <v>0.0756869904100661</v>
-      </c>
-      <c r="H50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0756869904100661)</f>
-        <v>0.0756869904100661</v>
-      </c>
-      <c r="I50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0756869904100661)</f>
-        <v>0.0756869904100661</v>
-      </c>
-      <c r="J50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="M50" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0909796762566006)</f>
-        <v>0.0909796762566006</v>
-      </c>
-      <c r="N50" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),366.61985757759)</f>
-        <v>366.61985757759</v>
-      </c>
-      <c r="O50" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P50" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6)</f>
-        <v>6</v>
-      </c>
-      <c r="Q50" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R50" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S50" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T50" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U50" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3632.5)</f>
-        <v>3632.5</v>
-      </c>
-      <c r="V50" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1379.7)</f>
-        <v>1379.7</v>
-      </c>
-      <c r="W50" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="20"/>
+      <c r="L50" s="20"/>
+      <c r="M50" s="20"/>
+      <c r="N50" s="21"/>
+      <c r="O50" s="22"/>
+      <c r="P50" s="21"/>
+      <c r="Q50" s="21"/>
+      <c r="R50" s="21"/>
+      <c r="S50" s="21"/>
+      <c r="T50" s="21"/>
+      <c r="U50" s="21"/>
+      <c r="V50" s="21"/>
+      <c r="W50" s="21"/>
       <c r="X50" s="7" t="n">
         <f aca="false">SUM(Q50:W50)</f>
         <v>5012.2</v>
@@ -5260,94 +3073,28 @@
       <c r="A51" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B51" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="C51" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="D51" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E51" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F51" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="G51" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="H51" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="I51" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J51" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K51" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L51" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="M51" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="N51" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),125.86907204172)</f>
-        <v>125.86907204172</v>
-      </c>
-      <c r="O51" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P51" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2)</f>
-        <v>2</v>
-      </c>
-      <c r="Q51" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R51" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S51" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T51" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U51" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1568)</f>
-        <v>1568</v>
-      </c>
-      <c r="V51" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="W51" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+      <c r="M51" s="20"/>
+      <c r="N51" s="21"/>
+      <c r="O51" s="22"/>
+      <c r="P51" s="21"/>
+      <c r="Q51" s="21"/>
+      <c r="R51" s="21"/>
+      <c r="S51" s="21"/>
+      <c r="T51" s="21"/>
+      <c r="U51" s="21"/>
+      <c r="V51" s="21"/>
+      <c r="W51" s="21"/>
       <c r="X51" s="7" t="n">
         <f aca="false">SUM(Q51:W51)</f>
         <v>1568</v>
@@ -5357,94 +3104,28 @@
       <c r="A52" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738143198706873)</f>
-        <v>0.0738143198706873</v>
-      </c>
-      <c r="C52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738143198706873)</f>
-        <v>0.0738143198706873</v>
-      </c>
-      <c r="D52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826227624746291)</f>
-        <v>0.0826227624746291</v>
-      </c>
-      <c r="E52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0945064091827231)</f>
-        <v>0.0945064091827231</v>
-      </c>
-      <c r="F52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0952134923111048)</f>
-        <v>0.0952134923111048</v>
-      </c>
-      <c r="G52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0907950767238501)</f>
-        <v>0.0907950767238501</v>
-      </c>
-      <c r="H52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771791995816322)</f>
-        <v>0.0771791995816322</v>
-      </c>
-      <c r="I52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782753016610352)</f>
-        <v>0.0782753016610352</v>
-      </c>
-      <c r="J52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826937172482899)</f>
-        <v>0.0826937172482899</v>
-      </c>
-      <c r="K52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826937172482899)</f>
-        <v>0.0826937172482899</v>
-      </c>
-      <c r="L52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819866341199082)</f>
-        <v>0.0819866341199082</v>
-      </c>
-      <c r="M52" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864050497071629)</f>
-        <v>0.0864050497071629</v>
-      </c>
-      <c r="N52" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),300.325058646191)</f>
-        <v>300.325058646191</v>
-      </c>
-      <c r="O52" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P52" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5)</f>
-        <v>5</v>
-      </c>
-      <c r="Q52" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R52" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2260.2)</f>
-        <v>2260.2</v>
-      </c>
-      <c r="S52" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),122.6)</f>
-        <v>122.6</v>
-      </c>
-      <c r="T52" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),131.1)</f>
-        <v>131.1</v>
-      </c>
-      <c r="U52" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1589.2)</f>
-        <v>1589.2</v>
-      </c>
-      <c r="V52" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),776.1)</f>
-        <v>776.1</v>
-      </c>
-      <c r="W52" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="20"/>
+      <c r="N52" s="21"/>
+      <c r="O52" s="22"/>
+      <c r="P52" s="21"/>
+      <c r="Q52" s="21"/>
+      <c r="R52" s="21"/>
+      <c r="S52" s="21"/>
+      <c r="T52" s="21"/>
+      <c r="U52" s="21"/>
+      <c r="V52" s="21"/>
+      <c r="W52" s="21"/>
       <c r="X52" s="7" t="n">
         <f aca="false">SUM(Q52:W52)</f>
         <v>4879.2</v>
@@ -5454,94 +3135,28 @@
       <c r="A53" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738141230528446)</f>
-        <v>0.0738141230528446</v>
-      </c>
-      <c r="C53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738141230528446)</f>
-        <v>0.0738141230528446</v>
-      </c>
-      <c r="D53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826225891766349)</f>
-        <v>0.0826225891766349</v>
-      </c>
-      <c r="E53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0945068249706181)</f>
-        <v>0.0945068249706181</v>
-      </c>
-      <c r="F53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0952136231283829)</f>
-        <v>0.0952136231283829</v>
-      </c>
-      <c r="G53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0907952016698743)</f>
-        <v>0.0907952016698743</v>
-      </c>
-      <c r="H53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.077179442745086)</f>
-        <v>0.077179442745086</v>
-      </c>
-      <c r="I53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782751122453402)</f>
-        <v>0.0782751122453402</v>
-      </c>
-      <c r="J53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826935337038488)</f>
-        <v>0.0826935337038488</v>
-      </c>
-      <c r="K53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826935337038488)</f>
-        <v>0.0826935337038488</v>
-      </c>
-      <c r="L53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.081986735546084)</f>
-        <v>0.081986735546084</v>
-      </c>
-      <c r="M53" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864051570045927)</f>
-        <v>0.0864051570045927</v>
-      </c>
-      <c r="N53" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),660.71512861809)</f>
-        <v>660.71512861809</v>
-      </c>
-      <c r="O53" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P53" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10)</f>
-        <v>10</v>
-      </c>
-      <c r="Q53" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R53" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4972.5)</f>
-        <v>4972.5</v>
-      </c>
-      <c r="S53" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),269.6)</f>
-        <v>269.6</v>
-      </c>
-      <c r="T53" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),288.3)</f>
-        <v>288.3</v>
-      </c>
-      <c r="U53" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3496.3)</f>
-        <v>3496.3</v>
-      </c>
-      <c r="V53" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1707.4)</f>
-        <v>1707.4</v>
-      </c>
-      <c r="W53" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B53" s="20"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20"/>
+      <c r="K53" s="20"/>
+      <c r="L53" s="20"/>
+      <c r="M53" s="20"/>
+      <c r="N53" s="21"/>
+      <c r="O53" s="22"/>
+      <c r="P53" s="21"/>
+      <c r="Q53" s="21"/>
+      <c r="R53" s="21"/>
+      <c r="S53" s="21"/>
+      <c r="T53" s="21"/>
+      <c r="U53" s="21"/>
+      <c r="V53" s="21"/>
+      <c r="W53" s="21"/>
       <c r="X53" s="7" t="n">
         <f aca="false">SUM(Q53:W53)</f>
         <v>10734.1</v>
@@ -5551,94 +3166,28 @@
       <c r="A54" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738134657732333)</f>
-        <v>0.0738134657732333</v>
-      </c>
-      <c r="C54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738134657732333)</f>
-        <v>0.0738134657732333</v>
-      </c>
-      <c r="D54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826224083229981)</f>
-        <v>0.0826224083229981</v>
-      </c>
-      <c r="E54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0945072087101559)</f>
-        <v>0.0945072087101559</v>
-      </c>
-      <c r="F54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0952140122277676)</f>
-        <v>0.0952140122277676</v>
-      </c>
-      <c r="G54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0907957098996484)</f>
-        <v>0.0907957098996484</v>
-      </c>
-      <c r="H54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771794819907101)</f>
-        <v>0.0771794819907101</v>
-      </c>
-      <c r="I54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782752685393762)</f>
-        <v>0.0782752685393762</v>
-      </c>
-      <c r="J54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826935708674953)</f>
-        <v>0.0826935708674953</v>
-      </c>
-      <c r="K54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826935708674953)</f>
-        <v>0.0826935708674953</v>
-      </c>
-      <c r="L54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819867673498837)</f>
-        <v>0.0819867673498837</v>
-      </c>
-      <c r="M54" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864050696780028)</f>
-        <v>0.0864050696780028</v>
-      </c>
-      <c r="N54" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.156028161701)</f>
-        <v>144.156028161701</v>
-      </c>
-      <c r="O54" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P54" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3)</f>
-        <v>3</v>
-      </c>
-      <c r="Q54" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R54" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1084.9)</f>
-        <v>1084.9</v>
-      </c>
-      <c r="S54" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.8)</f>
-        <v>58.8</v>
-      </c>
-      <c r="T54" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),62.9)</f>
-        <v>62.9</v>
-      </c>
-      <c r="U54" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),762.8)</f>
-        <v>762.8</v>
-      </c>
-      <c r="V54" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),372.5)</f>
-        <v>372.5</v>
-      </c>
-      <c r="W54" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="20"/>
+      <c r="L54" s="20"/>
+      <c r="M54" s="20"/>
+      <c r="N54" s="21"/>
+      <c r="O54" s="22"/>
+      <c r="P54" s="21"/>
+      <c r="Q54" s="21"/>
+      <c r="R54" s="21"/>
+      <c r="S54" s="21"/>
+      <c r="T54" s="21"/>
+      <c r="U54" s="21"/>
+      <c r="V54" s="21"/>
+      <c r="W54" s="21"/>
       <c r="X54" s="7" t="n">
         <f aca="false">SUM(Q54:W54)</f>
         <v>2341.9</v>
@@ -5648,94 +3197,28 @@
       <c r="A55" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738124965393579)</f>
-        <v>0.0738124965393579</v>
-      </c>
-      <c r="C55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0738124965393579)</f>
-        <v>0.0738124965393579</v>
-      </c>
-      <c r="D55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826224235220467)</f>
-        <v>0.0826224235220467</v>
-      </c>
-      <c r="E55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0945083084729547)</f>
-        <v>0.0945083084729547</v>
-      </c>
-      <c r="F55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0952145803016424)</f>
-        <v>0.0952145803016424</v>
-      </c>
-      <c r="G55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0907966823883564)</f>
-        <v>0.0907966823883564</v>
-      </c>
-      <c r="H55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0771804197218833)</f>
-        <v>0.0771804197218833</v>
-      </c>
-      <c r="I55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0782751293210692)</f>
-        <v>0.0782751293210692</v>
-      </c>
-      <c r="J55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826930272343553)</f>
-        <v>0.0826930272343553</v>
-      </c>
-      <c r="K55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0826930272343553)</f>
-        <v>0.0826930272343553</v>
-      </c>
-      <c r="L55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0819867554056675)</f>
-        <v>0.0819867554056675</v>
-      </c>
-      <c r="M55" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0864046533189536)</f>
-        <v>0.0864046533189536</v>
-      </c>
-      <c r="N55" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),96.1040185823099)</f>
-        <v>96.1040185823099</v>
-      </c>
-      <c r="O55" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1)</f>
-        <v>1</v>
-      </c>
-      <c r="P55" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2)</f>
-        <v>2</v>
-      </c>
-      <c r="Q55" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R55" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),723.3)</f>
-        <v>723.3</v>
-      </c>
-      <c r="S55" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.2)</f>
-        <v>39.2</v>
-      </c>
-      <c r="T55" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),41.9)</f>
-        <v>41.9</v>
-      </c>
-      <c r="U55" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),508.5)</f>
-        <v>508.5</v>
-      </c>
-      <c r="V55" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),248.3)</f>
-        <v>248.3</v>
-      </c>
-      <c r="W55" s="21" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0)</f>
-        <v>0</v>
-      </c>
+      <c r="B55" s="20"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="20"/>
+      <c r="K55" s="20"/>
+      <c r="L55" s="20"/>
+      <c r="M55" s="20"/>
+      <c r="N55" s="21"/>
+      <c r="O55" s="22"/>
+      <c r="P55" s="21"/>
+      <c r="Q55" s="21"/>
+      <c r="R55" s="21"/>
+      <c r="S55" s="21"/>
+      <c r="T55" s="21"/>
+      <c r="U55" s="21"/>
+      <c r="V55" s="21"/>
+      <c r="W55" s="21"/>
       <c r="X55" s="7" t="n">
         <f aca="false">SUM(Q55:W55)</f>
         <v>1561.2</v>
@@ -5745,54 +3228,18 @@
       <c r="A56" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0948522483704821)</f>
-        <v>0.0948522483704821</v>
-      </c>
-      <c r="C56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0815047861926023)</f>
-        <v>0.0815047861926023</v>
-      </c>
-      <c r="D56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0764490653204335)</f>
-        <v>0.0764490653204335</v>
-      </c>
-      <c r="E56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0840907184461371)</f>
-        <v>0.0840907184461371</v>
-      </c>
-      <c r="F56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0847724193282586)</f>
-        <v>0.0847724193282586</v>
-      </c>
-      <c r="G56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0839123144737292)</f>
-        <v>0.0839123144737292</v>
-      </c>
-      <c r="H56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0747579341668873)</f>
-        <v>0.0747579341668873</v>
-      </c>
-      <c r="I56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0754421691956102)</f>
-        <v>0.0754421691956102</v>
-      </c>
-      <c r="J56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0761698137204834)</f>
-        <v>0.0761698137204834</v>
-      </c>
-      <c r="K56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0761698137204834)</f>
-        <v>0.0761698137204834</v>
-      </c>
-      <c r="L56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0888355750162418)</f>
-        <v>0.0888355750162418</v>
-      </c>
-      <c r="M56" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.103043142048651)</f>
-        <v>0.103043142048651</v>
-      </c>
+      <c r="B56" s="20"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20"/>
+      <c r="K56" s="20"/>
+      <c r="L56" s="20"/>
+      <c r="M56" s="20"/>
       <c r="N56" s="7" t="n">
         <f aca="false">SUM(N39:N55)</f>
         <v>107197.372813695</v>
@@ -5810,30 +3257,12 @@
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""sobrestock_sustitutos!B18:H18"")"),9)</f>
         <v>9</v>
       </c>
-      <c r="R57" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15)</f>
-        <v>15</v>
-      </c>
-      <c r="S57" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12)</f>
-        <v>12</v>
-      </c>
-      <c r="T57" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11)</f>
-        <v>11</v>
-      </c>
-      <c r="U57" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10)</f>
-        <v>10</v>
-      </c>
-      <c r="V57" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),61)</f>
-        <v>61</v>
-      </c>
-      <c r="W57" s="22" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6)</f>
-        <v>6</v>
-      </c>
+      <c r="R57" s="22"/>
+      <c r="S57" s="22"/>
+      <c r="T57" s="22"/>
+      <c r="U57" s="22"/>
+      <c r="V57" s="22"/>
+      <c r="W57" s="22"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
@@ -5902,368 +3331,119 @@
         <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(Links!$B$5,""parametros_recargas!E35:P41"")"),0.12)</f>
         <v>0.12</v>
       </c>
-      <c r="C62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955555555555556)</f>
-        <v>0.0955555555555556</v>
-      </c>
-      <c r="D62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="E62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="F62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="G62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="H62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="I62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="J62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="K62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0711111111111111)</f>
-        <v>0.0711111111111111</v>
-      </c>
-      <c r="L62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0955555555555556)</f>
-        <v>0.0955555555555556</v>
-      </c>
-      <c r="M62" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.12)</f>
-        <v>0.12</v>
-      </c>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+      <c r="K62" s="20"/>
+      <c r="L62" s="20"/>
+      <c r="M62" s="20"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0540540540540541)</f>
-        <v>0.0540540540540541</v>
-      </c>
-      <c r="C63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0540540540540541)</f>
-        <v>0.0540540540540541</v>
-      </c>
-      <c r="D63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
-        <v>0.0810810810810811</v>
-      </c>
-      <c r="E63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.108108108108108)</f>
-        <v>0.108108108108108</v>
-      </c>
-      <c r="F63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.108108108108108)</f>
-        <v>0.108108108108108</v>
-      </c>
-      <c r="G63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.108108108108108)</f>
-        <v>0.108108108108108</v>
-      </c>
-      <c r="H63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
-        <v>0.0810810810810811</v>
-      </c>
-      <c r="I63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
-        <v>0.0810810810810811</v>
-      </c>
-      <c r="J63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
-        <v>0.0810810810810811</v>
-      </c>
-      <c r="K63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
-        <v>0.0810810810810811</v>
-      </c>
-      <c r="L63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
-        <v>0.0810810810810811</v>
-      </c>
-      <c r="M63" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0810810810810811)</f>
-        <v>0.0810810810810811</v>
-      </c>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+      <c r="K63" s="20"/>
+      <c r="L63" s="20"/>
+      <c r="M63" s="20"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10126582278481)</f>
-        <v>0.10126582278481</v>
-      </c>
-      <c r="C64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10126582278481)</f>
-        <v>0.10126582278481</v>
-      </c>
-      <c r="D64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.10126582278481)</f>
-        <v>0.10126582278481</v>
-      </c>
-      <c r="E64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
-      <c r="F64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
-      <c r="G64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
-      <c r="H64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0886075949367089)</f>
-        <v>0.0886075949367089</v>
-      </c>
-      <c r="I64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
-      <c r="J64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
-      <c r="K64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
-      <c r="L64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
-      <c r="M64" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0759493670886076)</f>
-        <v>0.0759493670886076</v>
-      </c>
+      <c r="B64" s="20"/>
+      <c r="C64" s="20"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="20"/>
+      <c r="K64" s="20"/>
+      <c r="L64" s="20"/>
+      <c r="M64" s="20"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0526315789473684)</f>
-        <v>0.0526315789473684</v>
-      </c>
-      <c r="C65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0526315789473684)</f>
-        <v>0.0526315789473684</v>
-      </c>
-      <c r="D65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
-        <v>0.0789473684210526</v>
-      </c>
-      <c r="E65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
-        <v>0.0789473684210526</v>
-      </c>
-      <c r="F65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
-        <v>0.105263157894737</v>
-      </c>
-      <c r="G65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
-        <v>0.105263157894737</v>
-      </c>
-      <c r="H65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0526315789473684)</f>
-        <v>0.0526315789473684</v>
-      </c>
-      <c r="I65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
-        <v>0.105263157894737</v>
-      </c>
-      <c r="J65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
-        <v>0.105263157894737</v>
-      </c>
-      <c r="K65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.105263157894737)</f>
-        <v>0.105263157894737</v>
-      </c>
-      <c r="L65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
-        <v>0.0789473684210526</v>
-      </c>
-      <c r="M65" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0789473684210526)</f>
-        <v>0.0789473684210526</v>
-      </c>
+      <c r="B65" s="20"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="20"/>
+      <c r="K65" s="20"/>
+      <c r="L65" s="20"/>
+      <c r="M65" s="20"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B66" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="C66" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="D66" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E66" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F66" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="G66" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="H66" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="I66" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J66" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K66" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L66" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="M66" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
+      <c r="B66" s="20"/>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
+      <c r="H66" s="20"/>
+      <c r="I66" s="20"/>
+      <c r="J66" s="20"/>
+      <c r="K66" s="20"/>
+      <c r="L66" s="20"/>
+      <c r="M66" s="20"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
-        <v>0.111111111111111</v>
-      </c>
-      <c r="C67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
-        <v>0.111111111111111</v>
-      </c>
-      <c r="D67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="G67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
-        <v>0.0555555555555556</v>
-      </c>
-      <c r="H67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
-        <v>0.0555555555555556</v>
-      </c>
-      <c r="I67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
-        <v>0.0555555555555556</v>
-      </c>
-      <c r="J67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="M67" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
-        <v>0.111111111111111</v>
-      </c>
+      <c r="B67" s="20"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="20"/>
+      <c r="H67" s="20"/>
+      <c r="I67" s="20"/>
+      <c r="J67" s="20"/>
+      <c r="K67" s="20"/>
+      <c r="L67" s="20"/>
+      <c r="M67" s="20"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
-        <v>0.0555555555555556</v>
-      </c>
-      <c r="C68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
-        <v>0.0555555555555556</v>
-      </c>
-      <c r="D68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="E68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
-        <v>0.111111111111111</v>
-      </c>
-      <c r="G68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
-        <v>0.111111111111111</v>
-      </c>
-      <c r="H68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
-        <v>0.111111111111111</v>
-      </c>
-      <c r="I68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.111111111111111)</f>
-        <v>0.111111111111111</v>
-      </c>
-      <c r="J68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="K68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0833333333333333)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="L68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
-        <v>0.0555555555555556</v>
-      </c>
-      <c r="M68" s="20" t="n">
-        <f aca="false">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0555555555555556)</f>
-        <v>0.0555555555555556</v>
-      </c>
+      <c r="B68" s="20"/>
+      <c r="C68" s="20"/>
+      <c r="D68" s="20"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="20"/>
+      <c r="G68" s="20"/>
+      <c r="H68" s="20"/>
+      <c r="I68" s="20"/>
+      <c r="J68" s="20"/>
+      <c r="K68" s="20"/>
+      <c r="L68" s="20"/>
+      <c r="M68" s="20"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
